--- a/daily/2026-04-02.xlsx
+++ b/daily/2026-04-02.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X84"/>
+  <dimension ref="A1:X86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -714,7 +714,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Grayson Allen</t>
+          <t>LaMelo Ball</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -728,71 +728,75 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.5</v>
+        <v>20.5</v>
       </c>
       <c r="E4" t="n">
-        <v>16.7</v>
+        <v>17.7</v>
       </c>
       <c r="F4" t="n">
-        <v>15.6</v>
+        <v>19</v>
       </c>
       <c r="G4" t="n">
-        <v>16.9</v>
+        <v>22.1</v>
       </c>
       <c r="H4" t="n">
-        <v>18.4</v>
+        <v>20.9</v>
       </c>
       <c r="I4" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="J4" t="n">
-        <v>27.1</v>
+        <v>28.5</v>
       </c>
       <c r="K4" t="n">
-        <v>28.8</v>
+        <v>28.1</v>
       </c>
       <c r="L4" t="n">
-        <v>39.9</v>
+        <v>43.4</v>
       </c>
       <c r="M4" t="n">
-        <v>38.8</v>
+        <v>40.1</v>
       </c>
       <c r="N4" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="O4" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="P4" t="n">
-        <v>80</v>
+        <v>33</v>
       </c>
       <c r="Q4" t="n">
-        <v>5</v>
+        <v>-0.5</v>
       </c>
       <c r="R4" t="n">
-        <v>-1.9</v>
+        <v>-1</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.7</v>
+        <v>0.4</v>
       </c>
       <c r="U4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="V4" t="n">
-        <v>19</v>
-      </c>
-      <c r="W4" t="inlineStr"/>
+        <v>21</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>26.3 (3g)</t>
+        </is>
+      </c>
       <c r="X4" t="n">
-        <v>12.8</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LaMelo Ball</t>
+          <t>Devin Booker</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -806,75 +810,75 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>19.5</v>
+        <v>25.5</v>
       </c>
       <c r="E5" t="n">
-        <v>17.7</v>
+        <v>32</v>
       </c>
       <c r="F5" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="G5" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H5" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="I5" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>33</v>
+      </c>
+      <c r="K5" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="L5" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="M5" t="n">
+        <v>45</v>
+      </c>
+      <c r="N5" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="O5" t="n">
+        <v>60</v>
+      </c>
+      <c r="P5" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U5" t="n">
+        <v>9</v>
+      </c>
+      <c r="V5" t="n">
         <v>19</v>
       </c>
-      <c r="G5" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="H5" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="I5" t="n">
-        <v>20</v>
-      </c>
-      <c r="J5" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="K5" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>43.4</v>
-      </c>
-      <c r="M5" t="n">
-        <v>40.1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="O5" t="n">
-        <v>70</v>
-      </c>
-      <c r="P5" t="n">
-        <v>53</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="U5" t="n">
-        <v>4</v>
-      </c>
-      <c r="V5" t="n">
-        <v>21</v>
-      </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>26.3 (3g)</t>
+          <t>33.0 (3g)</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>-1.4</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Jalen Green</t>
+          <t>Ryan Kalkbrenner</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -884,79 +888,75 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.5</v>
+        <v>5.5</v>
       </c>
       <c r="E6" t="n">
-        <v>20</v>
+        <v>4.7</v>
       </c>
       <c r="F6" t="n">
-        <v>20.2</v>
+        <v>4.8</v>
       </c>
       <c r="G6" t="n">
-        <v>20.6</v>
+        <v>6.9</v>
       </c>
       <c r="H6" t="n">
-        <v>19.9</v>
+        <v>6.7</v>
       </c>
       <c r="I6" t="n">
-        <v>17.1</v>
+        <v>6.7</v>
       </c>
       <c r="J6" t="n">
-        <v>29</v>
+        <v>17.6</v>
       </c>
       <c r="K6" t="n">
-        <v>25.3</v>
+        <v>18.3</v>
       </c>
       <c r="L6" t="n">
-        <v>43.6</v>
+        <v>83</v>
       </c>
       <c r="M6" t="n">
-        <v>38.8</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>8.199999999999999</v>
+        <v>4</v>
       </c>
       <c r="O6" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="P6" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="R6" t="n">
-        <v>3.1</v>
+        <v>-1.9</v>
       </c>
       <c r="S6" t="n">
-        <v>4.8</v>
+        <v>12.9</v>
       </c>
       <c r="T6" t="n">
-        <v>3.7</v>
+        <v>-0.6</v>
       </c>
       <c r="U6" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="V6" t="n">
-        <v>19</v>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>19.3 (3g)</t>
-        </is>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="W6" t="inlineStr"/>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Devin Booker</t>
+          <t>Moussa Diabaté</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -966,79 +966,75 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>25.5</v>
+        <v>7.5</v>
       </c>
       <c r="E7" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F7" t="n">
-        <v>28.6</v>
+        <v>8.6</v>
       </c>
       <c r="G7" t="n">
-        <v>28.4</v>
+        <v>7.1</v>
       </c>
       <c r="H7" t="n">
-        <v>26.8</v>
+        <v>7.5</v>
       </c>
       <c r="I7" t="n">
-        <v>26.1</v>
+        <v>8</v>
       </c>
       <c r="J7" t="n">
-        <v>33</v>
+        <v>27.4</v>
       </c>
       <c r="K7" t="n">
-        <v>32.4</v>
+        <v>27.9</v>
       </c>
       <c r="L7" t="n">
-        <v>48.4</v>
+        <v>60.5</v>
       </c>
       <c r="M7" t="n">
-        <v>45</v>
+        <v>61.9</v>
       </c>
       <c r="N7" t="n">
-        <v>7.9</v>
+        <v>4.9</v>
       </c>
       <c r="O7" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="P7" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="Q7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R7" t="n">
         <v>0.6</v>
       </c>
-      <c r="R7" t="n">
-        <v>2.5</v>
-      </c>
       <c r="S7" t="n">
-        <v>3.4</v>
+        <v>-1.4</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5</v>
+        <v>-0.5</v>
       </c>
       <c r="U7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V7" t="n">
-        <v>19</v>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>33.0 (3g)</t>
-        </is>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="W7" t="inlineStr"/>
       <c r="X7" t="n">
-        <v>6.5</v>
+        <v>-35.6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ryan Kalkbrenner</t>
+          <t>Coby White</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1048,75 +1044,79 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>5.5</v>
+        <v>13.5</v>
       </c>
       <c r="E8" t="n">
-        <v>4.7</v>
+        <v>14.3</v>
       </c>
       <c r="F8" t="n">
-        <v>4.8</v>
+        <v>17.4</v>
       </c>
       <c r="G8" t="n">
-        <v>6.9</v>
+        <v>17.7</v>
       </c>
       <c r="H8" t="n">
-        <v>6.7</v>
+        <v>15.8</v>
       </c>
       <c r="I8" t="n">
-        <v>6.7</v>
+        <v>16.1</v>
       </c>
       <c r="J8" t="n">
-        <v>17.6</v>
+        <v>20.9</v>
       </c>
       <c r="K8" t="n">
-        <v>18.3</v>
+        <v>24.1</v>
       </c>
       <c r="L8" t="n">
-        <v>83</v>
+        <v>47.7</v>
       </c>
       <c r="M8" t="n">
-        <v>70.09999999999999</v>
+        <v>41.9</v>
       </c>
       <c r="N8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="O8" t="n">
+        <v>70</v>
+      </c>
+      <c r="P8" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-3.2</v>
+      </c>
+      <c r="U8" t="n">
         <v>4</v>
-      </c>
-      <c r="O8" t="n">
-        <v>60</v>
-      </c>
-      <c r="P8" t="n">
-        <v>63</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="R8" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="S8" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="T8" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="U8" t="n">
-        <v>16</v>
       </c>
       <c r="V8" t="n">
         <v>21</v>
       </c>
-      <c r="W8" t="inlineStr"/>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>17.0 (3g)</t>
+        </is>
+      </c>
       <c r="X8" t="n">
-        <v>-11</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Moussa Diabaté</t>
+          <t>Kon Knueppel</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1126,75 +1126,75 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>8.5</v>
+        <v>16.5</v>
       </c>
       <c r="E9" t="n">
-        <v>8</v>
+        <v>10.7</v>
       </c>
       <c r="F9" t="n">
-        <v>8.6</v>
+        <v>14.4</v>
       </c>
       <c r="G9" t="n">
-        <v>7.1</v>
+        <v>16.4</v>
       </c>
       <c r="H9" t="n">
-        <v>7.5</v>
+        <v>18.7</v>
       </c>
       <c r="I9" t="n">
-        <v>8</v>
+        <v>18.7</v>
       </c>
       <c r="J9" t="n">
-        <v>27.4</v>
+        <v>28.7</v>
       </c>
       <c r="K9" t="n">
-        <v>27.9</v>
+        <v>30.5</v>
       </c>
       <c r="L9" t="n">
-        <v>60.5</v>
+        <v>43.2</v>
       </c>
       <c r="M9" t="n">
-        <v>61.9</v>
+        <v>47.6</v>
       </c>
       <c r="N9" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="O9" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="P9" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.5</v>
+        <v>2.2</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6</v>
+        <v>-4.3</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.4</v>
+        <v>-4.4</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5</v>
+        <v>-1.8</v>
       </c>
       <c r="U9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="V9" t="n">
         <v>21</v>
       </c>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="n">
-        <v>-35.6</v>
+        <v>-9.199999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Coby White</t>
+          <t>Brandon Miller</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1204,79 +1204,79 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.5</v>
+        <v>19.5</v>
       </c>
       <c r="E10" t="n">
-        <v>14.3</v>
+        <v>22.3</v>
       </c>
       <c r="F10" t="n">
-        <v>17.4</v>
+        <v>20.2</v>
       </c>
       <c r="G10" t="n">
-        <v>17.7</v>
+        <v>19</v>
       </c>
       <c r="H10" t="n">
-        <v>15.8</v>
+        <v>20.1</v>
       </c>
       <c r="I10" t="n">
-        <v>16.1</v>
+        <v>20.8</v>
       </c>
       <c r="J10" t="n">
-        <v>20.9</v>
+        <v>30.5</v>
       </c>
       <c r="K10" t="n">
-        <v>24.1</v>
+        <v>30.2</v>
       </c>
       <c r="L10" t="n">
-        <v>47.7</v>
+        <v>45.6</v>
       </c>
       <c r="M10" t="n">
-        <v>41.9</v>
+        <v>46.3</v>
       </c>
       <c r="N10" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="O10" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="P10" t="n">
         <v>60</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3</v>
+        <v>-0.6</v>
       </c>
       <c r="S10" t="n">
-        <v>5.8</v>
+        <v>-0.7</v>
       </c>
       <c r="T10" t="n">
-        <v>-3.2</v>
+        <v>0.3</v>
       </c>
       <c r="U10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="V10" t="n">
         <v>21</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>17.0 (3g)</t>
+          <t>14.3 (3g)</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>-2.7</v>
+        <v>-10.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Kon Knueppel</t>
+          <t>Royce O'Neale</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1286,75 +1286,75 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.5</v>
+        <v>7.5</v>
       </c>
       <c r="E11" t="n">
-        <v>10.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>14.4</v>
+        <v>11</v>
       </c>
       <c r="G11" t="n">
-        <v>16.4</v>
+        <v>10.6</v>
       </c>
       <c r="H11" t="n">
-        <v>18.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>18.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>28.7</v>
+        <v>27.3</v>
       </c>
       <c r="K11" t="n">
-        <v>30.5</v>
+        <v>28.2</v>
       </c>
       <c r="L11" t="n">
-        <v>43.2</v>
+        <v>43.9</v>
       </c>
       <c r="M11" t="n">
-        <v>47.6</v>
+        <v>39.2</v>
       </c>
       <c r="N11" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="O11" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="P11" t="n">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="R11" t="n">
-        <v>-4.3</v>
+        <v>1.7</v>
       </c>
       <c r="S11" t="n">
-        <v>-4.4</v>
+        <v>4.7</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.8</v>
+        <v>-0.9</v>
       </c>
       <c r="U11" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="V11" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="n">
-        <v>-9.199999999999999</v>
+        <v>-13.4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Brandon Miller</t>
+          <t>Collin Gillespie</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1364,79 +1364,75 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>19.5</v>
+        <v>10.5</v>
       </c>
       <c r="E12" t="n">
-        <v>22.3</v>
+        <v>7.3</v>
       </c>
       <c r="F12" t="n">
-        <v>20.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G12" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="I12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="K12" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="L12" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="N12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="O12" t="n">
+        <v>70</v>
+      </c>
+      <c r="P12" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="U12" t="n">
+        <v>9</v>
+      </c>
+      <c r="V12" t="n">
         <v>19</v>
       </c>
-      <c r="H12" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="I12" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="J12" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="K12" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="L12" t="n">
-        <v>45.6</v>
-      </c>
-      <c r="M12" t="n">
-        <v>46.3</v>
-      </c>
-      <c r="N12" t="n">
-        <v>7</v>
-      </c>
-      <c r="O12" t="n">
-        <v>60</v>
-      </c>
-      <c r="P12" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R12" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="S12" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="U12" t="n">
-        <v>8</v>
-      </c>
-      <c r="V12" t="n">
-        <v>21</v>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>14.3 (3g)</t>
-        </is>
-      </c>
+      <c r="W12" t="inlineStr"/>
       <c r="X12" t="n">
-        <v>-10.9</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Dillon Brooks</t>
+          <t>Miles Bridges</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1446,75 +1442,79 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="E13" t="n">
-        <v>12.3</v>
+        <v>14.7</v>
       </c>
       <c r="F13" t="n">
-        <v>17.6</v>
+        <v>14</v>
       </c>
       <c r="G13" t="n">
-        <v>21.2</v>
+        <v>15.6</v>
       </c>
       <c r="H13" t="n">
-        <v>19.9</v>
+        <v>14.2</v>
       </c>
       <c r="I13" t="n">
-        <v>19.9</v>
+        <v>14</v>
       </c>
       <c r="J13" t="n">
-        <v>27.8</v>
+        <v>28.4</v>
       </c>
       <c r="K13" t="n">
-        <v>30.1</v>
+        <v>28.5</v>
       </c>
       <c r="L13" t="n">
-        <v>41.6</v>
+        <v>55.4</v>
       </c>
       <c r="M13" t="n">
-        <v>42.8</v>
+        <v>46.6</v>
       </c>
       <c r="N13" t="n">
-        <v>10.3</v>
+        <v>5.4</v>
       </c>
       <c r="O13" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="P13" t="n">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.4</v>
+        <v>0.5</v>
       </c>
       <c r="R13" t="n">
-        <v>-2.3</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.3</v>
+        <v>-0.1</v>
       </c>
       <c r="U13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V13" t="n">
-        <v>19</v>
-      </c>
-      <c r="W13" t="inlineStr"/>
+        <v>21</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>19.3 (3g)</t>
+        </is>
+      </c>
       <c r="X13" t="n">
-        <v>-38</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Royce O'Neale</t>
+          <t>Grayson Allen</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1524,75 +1524,75 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>7.5</v>
+        <v>12.5</v>
       </c>
       <c r="E14" t="n">
-        <v>9.699999999999999</v>
+        <v>16.7</v>
       </c>
       <c r="F14" t="n">
-        <v>11</v>
+        <v>15.6</v>
       </c>
       <c r="G14" t="n">
-        <v>10.6</v>
+        <v>16.9</v>
       </c>
       <c r="H14" t="n">
-        <v>9.300000000000001</v>
+        <v>18.4</v>
       </c>
       <c r="I14" t="n">
-        <v>9.300000000000001</v>
+        <v>17.5</v>
       </c>
       <c r="J14" t="n">
-        <v>27.3</v>
+        <v>27.1</v>
       </c>
       <c r="K14" t="n">
-        <v>28.2</v>
+        <v>28.8</v>
       </c>
       <c r="L14" t="n">
-        <v>43.9</v>
+        <v>39.9</v>
       </c>
       <c r="M14" t="n">
-        <v>39.2</v>
+        <v>38.8</v>
       </c>
       <c r="N14" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="O14" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="P14" t="n">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.8</v>
+        <v>5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.7</v>
+        <v>-1.9</v>
       </c>
       <c r="S14" t="n">
-        <v>4.7</v>
+        <v>1.1</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9</v>
+        <v>-1.7</v>
       </c>
       <c r="U14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V14" t="n">
         <v>19</v>
       </c>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="n">
-        <v>-13.4</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Collin Gillespie</t>
+          <t>Jalen Green</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1606,55 +1606,55 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10.5</v>
+        <v>16.5</v>
       </c>
       <c r="E15" t="n">
-        <v>7.3</v>
+        <v>20</v>
       </c>
       <c r="F15" t="n">
-        <v>9.800000000000001</v>
+        <v>20.2</v>
       </c>
       <c r="G15" t="n">
-        <v>10.6</v>
+        <v>20.6</v>
       </c>
       <c r="H15" t="n">
-        <v>12.7</v>
+        <v>19.9</v>
       </c>
       <c r="I15" t="n">
-        <v>12.5</v>
+        <v>17.1</v>
       </c>
       <c r="J15" t="n">
-        <v>28.9</v>
+        <v>29</v>
       </c>
       <c r="K15" t="n">
-        <v>29.8</v>
+        <v>25.3</v>
       </c>
       <c r="L15" t="n">
-        <v>32.1</v>
+        <v>43.6</v>
       </c>
       <c r="M15" t="n">
-        <v>37.2</v>
+        <v>38.8</v>
       </c>
       <c r="N15" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="P15" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="Q15" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="R15" t="n">
-        <v>-2.7</v>
+        <v>3.1</v>
       </c>
       <c r="S15" t="n">
-        <v>-5.1</v>
+        <v>4.8</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9</v>
+        <v>3.7</v>
       </c>
       <c r="U15" t="n">
         <v>9</v>
@@ -1662,15 +1662,19 @@
       <c r="V15" t="n">
         <v>19</v>
       </c>
-      <c r="W15" t="inlineStr"/>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>19.3 (3g)</t>
+        </is>
+      </c>
       <c r="X15" t="n">
-        <v>16.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Miles Bridges</t>
+          <t>Dillon Brooks</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1680,73 +1684,69 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="E16" t="n">
-        <v>14.7</v>
+        <v>12.3</v>
       </c>
       <c r="F16" t="n">
-        <v>14</v>
+        <v>17.6</v>
       </c>
       <c r="G16" t="n">
-        <v>15.6</v>
+        <v>21.2</v>
       </c>
       <c r="H16" t="n">
-        <v>14.2</v>
+        <v>19.9</v>
       </c>
       <c r="I16" t="n">
-        <v>14</v>
+        <v>19.9</v>
       </c>
       <c r="J16" t="n">
-        <v>28.4</v>
+        <v>27.8</v>
       </c>
       <c r="K16" t="n">
-        <v>28.5</v>
+        <v>30.1</v>
       </c>
       <c r="L16" t="n">
-        <v>55.4</v>
+        <v>41.6</v>
       </c>
       <c r="M16" t="n">
-        <v>46.6</v>
+        <v>42.8</v>
       </c>
       <c r="N16" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="O16" t="n">
+        <v>70</v>
+      </c>
+      <c r="P16" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q16" t="n">
         <v>5.4</v>
       </c>
-      <c r="O16" t="n">
-        <v>60</v>
-      </c>
-      <c r="P16" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0.5</v>
-      </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>-2.3</v>
       </c>
       <c r="S16" t="n">
-        <v>8.800000000000001</v>
+        <v>-1.2</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1</v>
+        <v>-2.3</v>
       </c>
       <c r="U16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V16" t="n">
-        <v>21</v>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>19.3 (3g)</t>
-        </is>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="W16" t="inlineStr"/>
       <c r="X16" t="n">
-        <v>1.5</v>
+        <v>-38</v>
       </c>
     </row>
     <row r="17">
@@ -2168,7 +2168,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="E22" t="n">
         <v>18</v>
@@ -2204,10 +2204,10 @@
         <v>50</v>
       </c>
       <c r="P22" t="n">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.9</v>
+        <v>-0.1</v>
       </c>
       <c r="R22" t="n">
         <v>3.6</v>
@@ -2652,7 +2652,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>26.5</v>
+        <v>25.5</v>
       </c>
       <c r="E28" t="n">
         <v>26</v>
@@ -2688,10 +2688,10 @@
         <v>50</v>
       </c>
       <c r="P28" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="R28" t="n">
         <v>-3.5</v>
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="E32" t="n">
         <v>13</v>
@@ -3012,10 +3012,10 @@
         <v>60</v>
       </c>
       <c r="P32" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="R32" t="n">
         <v>-1.3</v>
@@ -3126,7 +3126,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Alex Caruso</t>
+          <t>Ajay Mitchell</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3140,55 +3140,55 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>4.5</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="n">
-        <v>5</v>
+        <v>12.3</v>
       </c>
       <c r="F34" t="n">
-        <v>5.6</v>
+        <v>11.8</v>
       </c>
       <c r="G34" t="n">
-        <v>5.8</v>
+        <v>13.5</v>
       </c>
       <c r="H34" t="n">
-        <v>6.8</v>
+        <v>14</v>
       </c>
       <c r="I34" t="n">
-        <v>6.3</v>
+        <v>13.4</v>
       </c>
       <c r="J34" t="n">
-        <v>19.2</v>
+        <v>26.3</v>
       </c>
       <c r="K34" t="n">
-        <v>18.3</v>
+        <v>26</v>
       </c>
       <c r="L34" t="n">
-        <v>40.5</v>
+        <v>49.9</v>
       </c>
       <c r="M34" t="n">
-        <v>41.2</v>
+        <v>52.1</v>
       </c>
       <c r="N34" t="n">
         <v>4.7</v>
       </c>
       <c r="O34" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="P34" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="R34" t="n">
-        <v>-0.7</v>
+        <v>-1.6</v>
       </c>
       <c r="S34" t="n">
-        <v>-0.7</v>
+        <v>-2.2</v>
       </c>
       <c r="T34" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="U34" t="n">
         <v>13</v>
@@ -3196,19 +3196,15 @@
       <c r="V34" t="n">
         <v>18</v>
       </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>10.8 (4g)</t>
-        </is>
-      </c>
+      <c r="W34" t="inlineStr"/>
       <c r="X34" t="n">
-        <v>11</v>
+        <v>-7.3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Ajay Mitchell</t>
+          <t>Jalen Williams</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3222,55 +3218,55 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>18.5</v>
       </c>
       <c r="E35" t="n">
-        <v>12.3</v>
+        <v>15.7</v>
       </c>
       <c r="F35" t="n">
-        <v>11.8</v>
+        <v>18.6</v>
       </c>
       <c r="G35" t="n">
-        <v>13.5</v>
+        <v>16.8</v>
       </c>
       <c r="H35" t="n">
-        <v>14</v>
+        <v>16.9</v>
       </c>
       <c r="I35" t="n">
-        <v>13.4</v>
+        <v>17.3</v>
       </c>
       <c r="J35" t="n">
-        <v>26.3</v>
+        <v>24.7</v>
       </c>
       <c r="K35" t="n">
-        <v>26</v>
+        <v>28.5</v>
       </c>
       <c r="L35" t="n">
-        <v>49.9</v>
+        <v>52.7</v>
       </c>
       <c r="M35" t="n">
-        <v>52.1</v>
+        <v>48.4</v>
       </c>
       <c r="N35" t="n">
-        <v>4.7</v>
+        <v>7.4</v>
       </c>
       <c r="O35" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="P35" t="n">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.9</v>
+        <v>-1.2</v>
       </c>
       <c r="R35" t="n">
-        <v>-1.6</v>
+        <v>1.3</v>
       </c>
       <c r="S35" t="n">
-        <v>-2.2</v>
+        <v>4.3</v>
       </c>
       <c r="T35" t="n">
-        <v>0.3</v>
+        <v>-3.8</v>
       </c>
       <c r="U35" t="n">
         <v>13</v>
@@ -3278,15 +3274,19 @@
       <c r="V35" t="n">
         <v>18</v>
       </c>
-      <c r="W35" t="inlineStr"/>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>21.0 (4g)</t>
+        </is>
+      </c>
       <c r="X35" t="n">
-        <v>-7.3</v>
+        <v>-6.3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Jalen Williams</t>
+          <t>Cason Wallace</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3300,55 +3300,55 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>18.5</v>
+        <v>6.5</v>
       </c>
       <c r="E36" t="n">
-        <v>15.7</v>
+        <v>11.7</v>
       </c>
       <c r="F36" t="n">
-        <v>18.6</v>
+        <v>9.4</v>
       </c>
       <c r="G36" t="n">
-        <v>16.8</v>
+        <v>7.4</v>
       </c>
       <c r="H36" t="n">
-        <v>16.9</v>
+        <v>10</v>
       </c>
       <c r="I36" t="n">
-        <v>17.3</v>
+        <v>10.4</v>
       </c>
       <c r="J36" t="n">
-        <v>24.7</v>
+        <v>24.1</v>
       </c>
       <c r="K36" t="n">
-        <v>28.5</v>
+        <v>27.3</v>
       </c>
       <c r="L36" t="n">
-        <v>52.7</v>
+        <v>44.7</v>
       </c>
       <c r="M36" t="n">
-        <v>48.4</v>
+        <v>42.9</v>
       </c>
       <c r="N36" t="n">
-        <v>7.4</v>
+        <v>5.1</v>
       </c>
       <c r="O36" t="n">
         <v>40</v>
       </c>
       <c r="P36" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="Q36" t="n">
-        <v>-1.2</v>
+        <v>3.9</v>
       </c>
       <c r="R36" t="n">
-        <v>1.3</v>
+        <v>-1</v>
       </c>
       <c r="S36" t="n">
-        <v>4.3</v>
+        <v>1.8</v>
       </c>
       <c r="T36" t="n">
-        <v>-3.8</v>
+        <v>-3.2</v>
       </c>
       <c r="U36" t="n">
         <v>13</v>
@@ -3358,17 +3358,17 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>21.0 (4g)</t>
+          <t>7.8 (5g)</t>
         </is>
       </c>
       <c r="X36" t="n">
-        <v>-6.3</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cason Wallace</t>
+          <t>Shai Gilgeous-Alexander</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3382,55 +3382,55 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>6.5</v>
+        <v>30.5</v>
       </c>
       <c r="E37" t="n">
-        <v>11.7</v>
+        <v>34</v>
       </c>
       <c r="F37" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="G37" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="H37" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="I37" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="J37" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="K37" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="L37" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="M37" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="N37" t="n">
         <v>9.4</v>
       </c>
-      <c r="G37" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="H37" t="n">
-        <v>10</v>
-      </c>
-      <c r="I37" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="J37" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="K37" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="L37" t="n">
-        <v>44.7</v>
-      </c>
-      <c r="M37" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="N37" t="n">
-        <v>5.1</v>
-      </c>
       <c r="O37" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="P37" t="n">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.9</v>
+        <v>0.6</v>
       </c>
       <c r="R37" t="n">
-        <v>-1</v>
+        <v>0.3</v>
       </c>
       <c r="S37" t="n">
-        <v>1.8</v>
+        <v>3.7</v>
       </c>
       <c r="T37" t="n">
-        <v>-3.2</v>
+        <v>-0.2</v>
       </c>
       <c r="U37" t="n">
         <v>13</v>
@@ -3440,17 +3440,17 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>7.8 (5g)</t>
+          <t>33.5 (4g)</t>
         </is>
       </c>
       <c r="X37" t="n">
-        <v>-0.2</v>
+        <v>-3.7</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Shai Gilgeous-Alexander</t>
+          <t>Rui Hachimura</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3460,79 +3460,79 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>30.5</v>
+        <v>8.5</v>
       </c>
       <c r="E38" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F38" t="n">
-        <v>31.4</v>
+        <v>9</v>
       </c>
       <c r="G38" t="n">
-        <v>31.2</v>
+        <v>8.9</v>
       </c>
       <c r="H38" t="n">
-        <v>30.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>31.1</v>
+        <v>10.3</v>
       </c>
       <c r="J38" t="n">
-        <v>33.9</v>
+        <v>23.7</v>
       </c>
       <c r="K38" t="n">
-        <v>34.1</v>
+        <v>25.8</v>
       </c>
       <c r="L38" t="n">
-        <v>60.1</v>
+        <v>57</v>
       </c>
       <c r="M38" t="n">
-        <v>56.4</v>
+        <v>50.8</v>
       </c>
       <c r="N38" t="n">
-        <v>9.4</v>
+        <v>4.2</v>
       </c>
       <c r="O38" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="P38" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="R38" t="n">
-        <v>0.3</v>
+        <v>-1.3</v>
       </c>
       <c r="S38" t="n">
-        <v>3.7</v>
+        <v>6.2</v>
       </c>
       <c r="T38" t="n">
-        <v>-0.2</v>
+        <v>-2.1</v>
       </c>
       <c r="U38" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="V38" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>33.5 (4g)</t>
+          <t>11.0 (4g)</t>
         </is>
       </c>
       <c r="X38" t="n">
-        <v>-3.7</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Rui Hachimura</t>
+          <t>Luka Dončić</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3546,55 +3546,55 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>7.5</v>
+        <v>31.5</v>
       </c>
       <c r="E39" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="F39" t="n">
-        <v>9</v>
+        <v>38.2</v>
       </c>
       <c r="G39" t="n">
-        <v>8.9</v>
+        <v>40.8</v>
       </c>
       <c r="H39" t="n">
-        <v>9.300000000000001</v>
+        <v>35.7</v>
       </c>
       <c r="I39" t="n">
-        <v>10.3</v>
+        <v>34.4</v>
       </c>
       <c r="J39" t="n">
-        <v>23.7</v>
+        <v>38.3</v>
       </c>
       <c r="K39" t="n">
-        <v>25.8</v>
+        <v>35.6</v>
       </c>
       <c r="L39" t="n">
-        <v>57</v>
+        <v>49.1</v>
       </c>
       <c r="M39" t="n">
-        <v>50.8</v>
+        <v>49</v>
       </c>
       <c r="N39" t="n">
-        <v>4.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O39" t="n">
+        <v>90</v>
+      </c>
+      <c r="P39" t="n">
         <v>60</v>
       </c>
-      <c r="P39" t="n">
-        <v>67</v>
-      </c>
       <c r="Q39" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="R39" t="n">
-        <v>-1.3</v>
+        <v>3.8</v>
       </c>
       <c r="S39" t="n">
-        <v>6.2</v>
+        <v>0.1</v>
       </c>
       <c r="T39" t="n">
-        <v>-2.1</v>
+        <v>2.7</v>
       </c>
       <c r="U39" t="n">
         <v>8</v>
@@ -3604,17 +3604,17 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>11.0 (4g)</t>
+          <t>22.0 (4g)</t>
         </is>
       </c>
       <c r="X39" t="n">
-        <v>-2.2</v>
+        <v>-5.2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Luka Dončić</t>
+          <t>LeBron James</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3628,55 +3628,55 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>32.5</v>
+        <v>17.5</v>
       </c>
       <c r="E40" t="n">
-        <v>42</v>
+        <v>16.3</v>
       </c>
       <c r="F40" t="n">
-        <v>38.2</v>
+        <v>16.8</v>
       </c>
       <c r="G40" t="n">
-        <v>40.8</v>
+        <v>18</v>
       </c>
       <c r="H40" t="n">
-        <v>35.7</v>
+        <v>18.9</v>
       </c>
       <c r="I40" t="n">
-        <v>34.4</v>
+        <v>19.3</v>
       </c>
       <c r="J40" t="n">
-        <v>38.3</v>
+        <v>35.4</v>
       </c>
       <c r="K40" t="n">
-        <v>35.6</v>
+        <v>33.8</v>
       </c>
       <c r="L40" t="n">
-        <v>49.1</v>
+        <v>54.4</v>
       </c>
       <c r="M40" t="n">
-        <v>49</v>
+        <v>51.6</v>
       </c>
       <c r="N40" t="n">
-        <v>9.199999999999999</v>
+        <v>5.6</v>
       </c>
       <c r="O40" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="P40" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="R40" t="n">
-        <v>3.8</v>
+        <v>-2.5</v>
       </c>
       <c r="S40" t="n">
-        <v>0.1</v>
+        <v>2.8</v>
       </c>
       <c r="T40" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="U40" t="n">
         <v>8</v>
@@ -3686,17 +3686,17 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>22.0 (4g)</t>
+          <t>20.2 (4g)</t>
         </is>
       </c>
       <c r="X40" t="n">
-        <v>-5.2</v>
+        <v>-4.2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>LeBron James</t>
+          <t>Austin Reaves</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3706,79 +3706,79 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="E41" t="n">
-        <v>16.3</v>
+        <v>21.3</v>
       </c>
       <c r="F41" t="n">
-        <v>16.8</v>
+        <v>22.6</v>
       </c>
       <c r="G41" t="n">
-        <v>18</v>
+        <v>21.8</v>
       </c>
       <c r="H41" t="n">
-        <v>18.9</v>
+        <v>20.8</v>
       </c>
       <c r="I41" t="n">
-        <v>19.3</v>
+        <v>20.1</v>
       </c>
       <c r="J41" t="n">
-        <v>35.4</v>
+        <v>38.7</v>
       </c>
       <c r="K41" t="n">
-        <v>33.8</v>
+        <v>33.4</v>
       </c>
       <c r="L41" t="n">
-        <v>54.4</v>
+        <v>43.9</v>
       </c>
       <c r="M41" t="n">
-        <v>51.6</v>
+        <v>46.9</v>
       </c>
       <c r="N41" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="O41" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="P41" t="n">
-        <v>73</v>
+        <v>33</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="R41" t="n">
-        <v>-2.5</v>
+        <v>2.5</v>
       </c>
       <c r="S41" t="n">
-        <v>2.8</v>
+        <v>-3</v>
       </c>
       <c r="T41" t="n">
-        <v>1.6</v>
+        <v>5.3</v>
       </c>
       <c r="U41" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V41" t="n">
         <v>28</v>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>20.2 (4g)</t>
+          <t>16.8 (5g)</t>
         </is>
       </c>
       <c r="X41" t="n">
-        <v>-4.2</v>
+        <v>-7.3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Austin Reaves</t>
+          <t>Deandre Ayton</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3788,73 +3788,73 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>19.5</v>
+        <v>9.5</v>
       </c>
       <c r="E42" t="n">
-        <v>21.3</v>
+        <v>13</v>
       </c>
       <c r="F42" t="n">
-        <v>22.6</v>
+        <v>12.2</v>
       </c>
       <c r="G42" t="n">
-        <v>21.8</v>
+        <v>12.2</v>
       </c>
       <c r="H42" t="n">
-        <v>20.8</v>
+        <v>10.6</v>
       </c>
       <c r="I42" t="n">
-        <v>20.1</v>
+        <v>10.3</v>
       </c>
       <c r="J42" t="n">
-        <v>38.7</v>
+        <v>28.2</v>
       </c>
       <c r="K42" t="n">
-        <v>33.4</v>
+        <v>25</v>
       </c>
       <c r="L42" t="n">
-        <v>43.9</v>
+        <v>75.3</v>
       </c>
       <c r="M42" t="n">
-        <v>46.9</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="N42" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="O42" t="n">
         <v>50</v>
       </c>
       <c r="P42" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="R42" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="S42" t="n">
-        <v>-3</v>
+        <v>10.7</v>
       </c>
       <c r="T42" t="n">
-        <v>5.3</v>
+        <v>3.2</v>
       </c>
       <c r="U42" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V42" t="n">
         <v>28</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>16.8 (5g)</t>
+          <t>8.7 (3g)</t>
         </is>
       </c>
       <c r="X42" t="n">
-        <v>-7.3</v>
+        <v>-6.2</v>
       </c>
     </row>
     <row r="43">
@@ -4024,7 +4024,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Deandre Ayton</t>
+          <t>Alex Caruso</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4034,73 +4034,73 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>9.5</v>
+        <v>4.5</v>
       </c>
       <c r="E45" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F45" t="n">
-        <v>12.2</v>
+        <v>5.6</v>
       </c>
       <c r="G45" t="n">
-        <v>12.2</v>
+        <v>5.8</v>
       </c>
       <c r="H45" t="n">
-        <v>10.6</v>
+        <v>6.8</v>
       </c>
       <c r="I45" t="n">
-        <v>10.3</v>
+        <v>6.3</v>
       </c>
       <c r="J45" t="n">
-        <v>28.2</v>
+        <v>19.2</v>
       </c>
       <c r="K45" t="n">
-        <v>25</v>
+        <v>18.3</v>
       </c>
       <c r="L45" t="n">
-        <v>75.3</v>
+        <v>40.5</v>
       </c>
       <c r="M45" t="n">
-        <v>64.59999999999999</v>
+        <v>41.2</v>
       </c>
       <c r="N45" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="O45" t="n">
         <v>50</v>
       </c>
       <c r="P45" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="Q45" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R45" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="S45" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="T45" t="n">
         <v>0.8</v>
       </c>
-      <c r="R45" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="S45" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="T45" t="n">
-        <v>3.2</v>
-      </c>
       <c r="U45" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="V45" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>8.7 (3g)</t>
+          <t>10.8 (4g)</t>
         </is>
       </c>
       <c r="X45" t="n">
-        <v>-6.2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="46">
@@ -4120,7 +4120,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="E46" t="n">
         <v>11</v>
@@ -4156,10 +4156,10 @@
         <v>60</v>
       </c>
       <c r="P46" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.2</v>
+        <v>-0.8</v>
       </c>
       <c r="R46" t="n">
         <v>1.5</v>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>10.5</v>
+        <v>9.5</v>
       </c>
       <c r="E53" t="n">
         <v>17</v>
@@ -4718,10 +4718,10 @@
         <v>60</v>
       </c>
       <c r="P53" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="R53" t="n">
         <v>0.2</v>
@@ -4906,12 +4906,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Saddiq Bey</t>
+          <t>De'Anthony Melton</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NOP @ POR</t>
+          <t>CLE @ GSW</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4920,76 +4920,76 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>17.5</v>
+        <v>13.5</v>
       </c>
       <c r="E56" t="n">
-        <v>18</v>
+        <v>4.7</v>
       </c>
       <c r="F56" t="n">
-        <v>18.2</v>
+        <v>9.6</v>
       </c>
       <c r="G56" t="n">
-        <v>17.3</v>
+        <v>13.7</v>
       </c>
       <c r="H56" t="n">
-        <v>19.6</v>
+        <v>13.9</v>
       </c>
       <c r="I56" t="n">
-        <v>20.4</v>
+        <v>14.3</v>
       </c>
       <c r="J56" t="n">
-        <v>32</v>
+        <v>24.8</v>
       </c>
       <c r="K56" t="n">
-        <v>32.6</v>
+        <v>23.9</v>
       </c>
       <c r="L56" t="n">
-        <v>43.1</v>
+        <v>34.3</v>
       </c>
       <c r="M56" t="n">
-        <v>45.4</v>
+        <v>39.7</v>
       </c>
       <c r="N56" t="n">
-        <v>6</v>
+        <v>9.6</v>
       </c>
       <c r="O56" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="P56" t="n">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="R56" t="n">
-        <v>-2.2</v>
+        <v>-4.7</v>
       </c>
       <c r="S56" t="n">
-        <v>-2.3</v>
+        <v>-5.4</v>
       </c>
       <c r="T56" t="n">
-        <v>-0.6</v>
+        <v>0.9</v>
       </c>
       <c r="U56" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="V56" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="W56" t="inlineStr"/>
       <c r="X56" t="n">
-        <v>0.7</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Herbert Jones</t>
+          <t>Gui Santos</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NOP @ POR</t>
+          <t>CLE @ GSW</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4998,75 +4998,75 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>9.5</v>
+        <v>14.5</v>
       </c>
       <c r="E57" t="n">
-        <v>7.7</v>
+        <v>22.3</v>
       </c>
       <c r="F57" t="n">
-        <v>9.6</v>
+        <v>17</v>
       </c>
       <c r="G57" t="n">
-        <v>10</v>
+        <v>16.6</v>
       </c>
       <c r="H57" t="n">
-        <v>9.300000000000001</v>
+        <v>15.9</v>
       </c>
       <c r="I57" t="n">
-        <v>8.699999999999999</v>
+        <v>14.8</v>
       </c>
       <c r="J57" t="n">
-        <v>30.9</v>
+        <v>31.3</v>
       </c>
       <c r="K57" t="n">
-        <v>29.7</v>
+        <v>30.1</v>
       </c>
       <c r="L57" t="n">
-        <v>40.5</v>
+        <v>46.9</v>
       </c>
       <c r="M57" t="n">
-        <v>36.7</v>
+        <v>52.2</v>
       </c>
       <c r="N57" t="n">
-        <v>3.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O57" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="P57" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="Q57" t="n">
-        <v>-0.8</v>
+        <v>0.3</v>
       </c>
       <c r="R57" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="S57" t="n">
-        <v>3.8</v>
+        <v>-5.3</v>
       </c>
       <c r="T57" t="n">
         <v>1.2</v>
       </c>
       <c r="U57" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="V57" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>7.0 (5g)</t>
+          <t>5.7 (3g)</t>
         </is>
       </c>
       <c r="X57" t="n">
-        <v>-3.4</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Scoot Henderson</t>
+          <t>Saddiq Bey</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5083,72 +5083,68 @@
         <v>17.5</v>
       </c>
       <c r="E58" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F58" t="n">
-        <v>16.2</v>
+        <v>18.2</v>
       </c>
       <c r="G58" t="n">
-        <v>14.1</v>
+        <v>17.3</v>
       </c>
       <c r="H58" t="n">
-        <v>14.2</v>
+        <v>19.6</v>
       </c>
       <c r="I58" t="n">
-        <v>13.5</v>
+        <v>20.4</v>
       </c>
       <c r="J58" t="n">
-        <v>24.5</v>
+        <v>32</v>
       </c>
       <c r="K58" t="n">
-        <v>23.7</v>
+        <v>32.6</v>
       </c>
       <c r="L58" t="n">
-        <v>41.2</v>
+        <v>43.1</v>
       </c>
       <c r="M58" t="n">
-        <v>40.3</v>
+        <v>45.4</v>
       </c>
       <c r="N58" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="O58" t="n">
+        <v>70</v>
+      </c>
+      <c r="P58" t="n">
+        <v>73</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R58" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="S58" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="T58" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="U58" t="n">
         <v>20</v>
       </c>
-      <c r="P58" t="n">
-        <v>23</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>-4</v>
-      </c>
-      <c r="R58" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="S58" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T58" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="U58" t="n">
-        <v>23</v>
-      </c>
       <c r="V58" t="n">
-        <v>7</v>
-      </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>10.5 (4g)</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="W58" t="inlineStr"/>
       <c r="X58" t="n">
-        <v>-6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Deni Avdija</t>
+          <t>Herbert Jones</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5162,75 +5158,75 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>26.5</v>
+        <v>9.5</v>
       </c>
       <c r="E59" t="n">
-        <v>22.7</v>
+        <v>7.7</v>
       </c>
       <c r="F59" t="n">
-        <v>20.8</v>
+        <v>9.6</v>
       </c>
       <c r="G59" t="n">
-        <v>22.7</v>
+        <v>10</v>
       </c>
       <c r="H59" t="n">
-        <v>19.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I59" t="n">
-        <v>22.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J59" t="n">
-        <v>31.8</v>
+        <v>30.9</v>
       </c>
       <c r="K59" t="n">
-        <v>31.1</v>
+        <v>29.7</v>
       </c>
       <c r="L59" t="n">
-        <v>43.7</v>
+        <v>40.5</v>
       </c>
       <c r="M59" t="n">
-        <v>43.9</v>
+        <v>36.7</v>
       </c>
       <c r="N59" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="O59" t="n">
+        <v>70</v>
+      </c>
+      <c r="P59" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="S59" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="U59" t="n">
         <v>20</v>
       </c>
-      <c r="P59" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>-4.4</v>
-      </c>
-      <c r="R59" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="S59" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="T59" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="U59" t="n">
-        <v>22</v>
-      </c>
       <c r="V59" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>18.3 (7g)</t>
+          <t>7.0 (5g)</t>
         </is>
       </c>
       <c r="X59" t="n">
-        <v>-0.5</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Yves Missi</t>
+          <t>Scoot Henderson</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5240,79 +5236,79 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>5.5</v>
+        <v>16.5</v>
       </c>
       <c r="E60" t="n">
-        <v>5.7</v>
+        <v>15</v>
       </c>
       <c r="F60" t="n">
-        <v>5</v>
+        <v>16.2</v>
       </c>
       <c r="G60" t="n">
-        <v>5.5</v>
+        <v>14.1</v>
       </c>
       <c r="H60" t="n">
-        <v>5.2</v>
+        <v>14.2</v>
       </c>
       <c r="I60" t="n">
-        <v>5.8</v>
+        <v>13.5</v>
       </c>
       <c r="J60" t="n">
-        <v>22.5</v>
+        <v>24.5</v>
       </c>
       <c r="K60" t="n">
-        <v>21.1</v>
+        <v>23.7</v>
       </c>
       <c r="L60" t="n">
-        <v>48.6</v>
+        <v>41.2</v>
       </c>
       <c r="M60" t="n">
-        <v>53.8</v>
+        <v>40.3</v>
       </c>
       <c r="N60" t="n">
-        <v>2.8</v>
+        <v>4.8</v>
       </c>
       <c r="O60" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="P60" t="n">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.3</v>
+        <v>-3</v>
       </c>
       <c r="R60" t="n">
-        <v>-0.8</v>
+        <v>2.7</v>
       </c>
       <c r="S60" t="n">
-        <v>-5.2</v>
+        <v>0.9</v>
       </c>
       <c r="T60" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="U60" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="V60" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>4.1 (7g)</t>
+          <t>10.5 (4g)</t>
         </is>
       </c>
       <c r="X60" t="n">
-        <v>0.5</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Donovan Clingan</t>
+          <t>Deni Avdija</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5322,79 +5318,79 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>13.5</v>
+        <v>26.5</v>
       </c>
       <c r="E61" t="n">
-        <v>5.3</v>
+        <v>22.7</v>
       </c>
       <c r="F61" t="n">
-        <v>7.4</v>
+        <v>20.8</v>
       </c>
       <c r="G61" t="n">
-        <v>12.9</v>
+        <v>22.7</v>
       </c>
       <c r="H61" t="n">
-        <v>13.3</v>
+        <v>19.2</v>
       </c>
       <c r="I61" t="n">
-        <v>13.2</v>
+        <v>22.1</v>
       </c>
       <c r="J61" t="n">
-        <v>26.3</v>
+        <v>31.8</v>
       </c>
       <c r="K61" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="L61" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="M61" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="N61" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O61" t="n">
+        <v>20</v>
+      </c>
+      <c r="P61" t="n">
         <v>27</v>
       </c>
-      <c r="L61" t="n">
-        <v>49</v>
-      </c>
-      <c r="M61" t="n">
-        <v>50.1</v>
-      </c>
-      <c r="N61" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="O61" t="n">
-        <v>50</v>
-      </c>
-      <c r="P61" t="n">
-        <v>50</v>
-      </c>
       <c r="Q61" t="n">
-        <v>-0.3</v>
+        <v>-4.4</v>
       </c>
       <c r="R61" t="n">
-        <v>-5.8</v>
+        <v>-1.3</v>
       </c>
       <c r="S61" t="n">
-        <v>-1.1</v>
+        <v>-0.2</v>
       </c>
       <c r="T61" t="n">
-        <v>-0.7</v>
+        <v>0.8</v>
       </c>
       <c r="U61" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="V61" t="n">
         <v>7</v>
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>7.4 (5g)</t>
+          <t>18.3 (7g)</t>
         </is>
       </c>
       <c r="X61" t="n">
-        <v>2.3</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Derik Queen</t>
+          <t>Yves Missi</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5408,55 +5404,55 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>8.5</v>
+        <v>5.5</v>
       </c>
       <c r="E62" t="n">
-        <v>12.3</v>
+        <v>5.7</v>
       </c>
       <c r="F62" t="n">
-        <v>10.2</v>
+        <v>5</v>
       </c>
       <c r="G62" t="n">
-        <v>8.199999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="H62" t="n">
-        <v>9.1</v>
+        <v>5.2</v>
       </c>
       <c r="I62" t="n">
-        <v>9.800000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="J62" t="n">
-        <v>18.2</v>
+        <v>22.5</v>
       </c>
       <c r="K62" t="n">
-        <v>22.1</v>
+        <v>21.1</v>
       </c>
       <c r="L62" t="n">
-        <v>38.4</v>
+        <v>48.6</v>
       </c>
       <c r="M62" t="n">
-        <v>42.2</v>
+        <v>53.8</v>
       </c>
       <c r="N62" t="n">
-        <v>4.8</v>
+        <v>2.8</v>
       </c>
       <c r="O62" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="P62" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="Q62" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="R62" t="n">
-        <v>0.4</v>
+        <v>-0.8</v>
       </c>
       <c r="S62" t="n">
-        <v>-3.8</v>
+        <v>-5.2</v>
       </c>
       <c r="T62" t="n">
-        <v>-3.9</v>
+        <v>1.4</v>
       </c>
       <c r="U62" t="n">
         <v>28</v>
@@ -5464,15 +5460,19 @@
       <c r="V62" t="n">
         <v>20</v>
       </c>
-      <c r="W62" t="inlineStr"/>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>4.1 (7g)</t>
+        </is>
+      </c>
       <c r="X62" t="n">
-        <v>14.2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Jrue Holiday</t>
+          <t>Donovan Clingan</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5482,79 +5482,79 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>17.5</v>
+        <v>13.5</v>
       </c>
       <c r="E63" t="n">
-        <v>21.3</v>
+        <v>5.3</v>
       </c>
       <c r="F63" t="n">
-        <v>17.6</v>
+        <v>7.4</v>
       </c>
       <c r="G63" t="n">
-        <v>14</v>
+        <v>12.9</v>
       </c>
       <c r="H63" t="n">
-        <v>16.6</v>
+        <v>13.3</v>
       </c>
       <c r="I63" t="n">
-        <v>16.6</v>
+        <v>13.2</v>
       </c>
       <c r="J63" t="n">
-        <v>28.6</v>
+        <v>26.3</v>
       </c>
       <c r="K63" t="n">
-        <v>28.9</v>
+        <v>27</v>
       </c>
       <c r="L63" t="n">
-        <v>40.7</v>
+        <v>49</v>
       </c>
       <c r="M63" t="n">
-        <v>45.7</v>
+        <v>50.1</v>
       </c>
       <c r="N63" t="n">
-        <v>7.3</v>
+        <v>7.7</v>
       </c>
       <c r="O63" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="P63" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="Q63" t="n">
-        <v>-0.9</v>
+        <v>-0.3</v>
       </c>
       <c r="R63" t="n">
-        <v>1</v>
+        <v>-5.8</v>
       </c>
       <c r="S63" t="n">
-        <v>-5</v>
+        <v>-1.1</v>
       </c>
       <c r="T63" t="n">
-        <v>-0.3</v>
+        <v>-0.7</v>
       </c>
       <c r="U63" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="V63" t="n">
         <v>7</v>
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>9.7 (3g)</t>
+          <t>7.4 (5g)</t>
         </is>
       </c>
       <c r="X63" t="n">
-        <v>-2.5</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Robert Williams III</t>
+          <t>Derik Queen</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5568,75 +5568,71 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>5.5</v>
+        <v>8.5</v>
       </c>
       <c r="E64" t="n">
-        <v>4.7</v>
+        <v>12.3</v>
       </c>
       <c r="F64" t="n">
-        <v>7.2</v>
+        <v>10.2</v>
       </c>
       <c r="G64" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H64" t="n">
-        <v>7.8</v>
+        <v>9.1</v>
       </c>
       <c r="I64" t="n">
-        <v>7.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J64" t="n">
-        <v>17.5</v>
+        <v>18.2</v>
       </c>
       <c r="K64" t="n">
-        <v>17.4</v>
+        <v>22.1</v>
       </c>
       <c r="L64" t="n">
-        <v>61.6</v>
+        <v>38.4</v>
       </c>
       <c r="M64" t="n">
-        <v>69.7</v>
+        <v>42.2</v>
       </c>
       <c r="N64" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="O64" t="n">
         <v>60</v>
       </c>
       <c r="P64" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="Q64" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="R64" t="n">
-        <v>-0.2</v>
+        <v>0.4</v>
       </c>
       <c r="S64" t="n">
-        <v>-8.1</v>
+        <v>-3.8</v>
       </c>
       <c r="T64" t="n">
-        <v>0.1</v>
+        <v>-3.9</v>
       </c>
       <c r="U64" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="V64" t="n">
-        <v>7</v>
-      </c>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t>4.7 (3g)</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="W64" t="inlineStr"/>
       <c r="X64" t="n">
-        <v>-7</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Trey Murphy III</t>
+          <t>Jrue Holiday</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5646,75 +5642,79 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>20.5</v>
+        <v>17.5</v>
       </c>
       <c r="E65" t="n">
-        <v>17.7</v>
+        <v>21.3</v>
       </c>
       <c r="F65" t="n">
-        <v>18.6</v>
+        <v>17.6</v>
       </c>
       <c r="G65" t="n">
-        <v>20.2</v>
+        <v>14</v>
       </c>
       <c r="H65" t="n">
-        <v>20.6</v>
+        <v>16.6</v>
       </c>
       <c r="I65" t="n">
-        <v>22.8</v>
+        <v>16.6</v>
       </c>
       <c r="J65" t="n">
-        <v>35.8</v>
+        <v>28.6</v>
       </c>
       <c r="K65" t="n">
-        <v>35.6</v>
+        <v>28.9</v>
       </c>
       <c r="L65" t="n">
-        <v>44.6</v>
+        <v>40.7</v>
       </c>
       <c r="M65" t="n">
-        <v>44.8</v>
+        <v>45.7</v>
       </c>
       <c r="N65" t="n">
-        <v>5.8</v>
+        <v>7.3</v>
       </c>
       <c r="O65" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="P65" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="Q65" t="n">
-        <v>2.3</v>
+        <v>-0.9</v>
       </c>
       <c r="R65" t="n">
-        <v>-4.2</v>
+        <v>1</v>
       </c>
       <c r="S65" t="n">
-        <v>-0.2</v>
+        <v>-5</v>
       </c>
       <c r="T65" t="n">
-        <v>0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="U65" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="V65" t="n">
-        <v>20</v>
-      </c>
-      <c r="W65" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>9.7 (3g)</t>
+        </is>
+      </c>
       <c r="X65" t="n">
-        <v>5</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Zion Williamson</t>
+          <t>Robert Williams III</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5724,79 +5724,79 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>20.5</v>
+        <v>6.5</v>
       </c>
       <c r="E66" t="n">
-        <v>20.3</v>
+        <v>4.7</v>
       </c>
       <c r="F66" t="n">
-        <v>21.6</v>
+        <v>7.2</v>
       </c>
       <c r="G66" t="n">
-        <v>20.4</v>
+        <v>6.4</v>
       </c>
       <c r="H66" t="n">
-        <v>20.9</v>
+        <v>7.8</v>
       </c>
       <c r="I66" t="n">
-        <v>20.1</v>
+        <v>7.4</v>
       </c>
       <c r="J66" t="n">
-        <v>30.9</v>
+        <v>17.5</v>
       </c>
       <c r="K66" t="n">
-        <v>30.2</v>
+        <v>17.4</v>
       </c>
       <c r="L66" t="n">
-        <v>71.59999999999999</v>
+        <v>61.6</v>
       </c>
       <c r="M66" t="n">
-        <v>62.4</v>
+        <v>69.7</v>
       </c>
       <c r="N66" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="O66" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="P66" t="n">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="Q66" t="n">
-        <v>-0.4</v>
+        <v>0.9</v>
       </c>
       <c r="R66" t="n">
-        <v>1.5</v>
+        <v>-0.2</v>
       </c>
       <c r="S66" t="n">
-        <v>9.199999999999999</v>
+        <v>-8.1</v>
       </c>
       <c r="T66" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="U66" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="V66" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>21.7 (3g)</t>
+          <t>4.7 (3g)</t>
         </is>
       </c>
       <c r="X66" t="n">
-        <v>-14.6</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Dejounte Murray</t>
+          <t>Trey Murphy III</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5806,59 +5806,59 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="E67" t="n">
-        <v>12.7</v>
+        <v>17.7</v>
       </c>
       <c r="F67" t="n">
-        <v>13.4</v>
+        <v>18.6</v>
       </c>
       <c r="G67" t="n">
-        <v>17.8</v>
+        <v>20.2</v>
       </c>
       <c r="H67" t="n">
-        <v>18.4</v>
+        <v>20.6</v>
       </c>
       <c r="I67" t="n">
-        <v>18</v>
+        <v>22.8</v>
       </c>
       <c r="J67" t="n">
-        <v>28.9</v>
+        <v>35.8</v>
       </c>
       <c r="K67" t="n">
-        <v>30.3</v>
+        <v>35.6</v>
       </c>
       <c r="L67" t="n">
-        <v>47.8</v>
+        <v>44.6</v>
       </c>
       <c r="M67" t="n">
-        <v>43.9</v>
+        <v>44.8</v>
       </c>
       <c r="N67" t="n">
-        <v>8.1</v>
+        <v>5.8</v>
       </c>
       <c r="O67" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="P67" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="Q67" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="R67" t="n">
-        <v>-4.6</v>
+        <v>-4.2</v>
       </c>
       <c r="S67" t="n">
-        <v>3.9</v>
+        <v>-0.2</v>
       </c>
       <c r="T67" t="n">
-        <v>-1.3</v>
+        <v>0.2</v>
       </c>
       <c r="U67" t="n">
         <v>20</v>
@@ -5868,13 +5868,13 @@
       </c>
       <c r="W67" t="inlineStr"/>
       <c r="X67" t="n">
-        <v>15.6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Toumani Camara</t>
+          <t>Zion Williamson</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5888,75 +5888,75 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>13.5</v>
+        <v>20.5</v>
       </c>
       <c r="E68" t="n">
-        <v>16</v>
+        <v>20.3</v>
       </c>
       <c r="F68" t="n">
-        <v>18.6</v>
+        <v>21.6</v>
       </c>
       <c r="G68" t="n">
-        <v>15.7</v>
+        <v>20.4</v>
       </c>
       <c r="H68" t="n">
-        <v>13.2</v>
+        <v>20.9</v>
       </c>
       <c r="I68" t="n">
-        <v>13.1</v>
+        <v>20.1</v>
       </c>
       <c r="J68" t="n">
         <v>30.9</v>
       </c>
       <c r="K68" t="n">
-        <v>31.8</v>
+        <v>30.2</v>
       </c>
       <c r="L68" t="n">
-        <v>53</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="M68" t="n">
-        <v>44.2</v>
+        <v>62.4</v>
       </c>
       <c r="N68" t="n">
-        <v>8.800000000000001</v>
+        <v>4.1</v>
       </c>
       <c r="O68" t="n">
         <v>60</v>
       </c>
       <c r="P68" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="Q68" t="n">
         <v>-0.4</v>
       </c>
       <c r="R68" t="n">
-        <v>5.5</v>
+        <v>1.5</v>
       </c>
       <c r="S68" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="T68" t="n">
-        <v>-1</v>
+        <v>0.7</v>
       </c>
       <c r="U68" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V68" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>12.9 (7g)</t>
+          <t>21.7 (3g)</t>
         </is>
       </c>
       <c r="X68" t="n">
-        <v>7.1</v>
+        <v>-14.6</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Matisse Thybulle</t>
+          <t>Dejounte Murray</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5970,76 +5970,76 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>7.5</v>
+        <v>16.5</v>
       </c>
       <c r="E69" t="n">
-        <v>6.3</v>
+        <v>12.7</v>
       </c>
       <c r="F69" t="n">
-        <v>8.6</v>
+        <v>13.4</v>
       </c>
       <c r="G69" t="n">
-        <v>6.7</v>
+        <v>17.8</v>
       </c>
       <c r="H69" t="n">
-        <v>5.5</v>
+        <v>18.4</v>
       </c>
       <c r="I69" t="n">
-        <v>6.2</v>
+        <v>18</v>
       </c>
       <c r="J69" t="n">
-        <v>18.6</v>
+        <v>28.9</v>
       </c>
       <c r="K69" t="n">
-        <v>16.8</v>
+        <v>30.3</v>
       </c>
       <c r="L69" t="n">
-        <v>43.1</v>
+        <v>47.8</v>
       </c>
       <c r="M69" t="n">
-        <v>44</v>
+        <v>43.9</v>
       </c>
       <c r="N69" t="n">
-        <v>3.5</v>
+        <v>8.1</v>
       </c>
       <c r="O69" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="P69" t="n">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="Q69" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R69" t="n">
+        <v>-4.6</v>
+      </c>
+      <c r="S69" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T69" t="n">
         <v>-1.3</v>
       </c>
-      <c r="R69" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S69" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="T69" t="n">
-        <v>1.7</v>
-      </c>
       <c r="U69" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="V69" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="W69" t="inlineStr"/>
       <c r="X69" t="n">
-        <v>0</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Keldon Johnson</t>
+          <t>Toumani Camara</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SAS @ LAC</t>
+          <t>NOP @ POR</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -6048,80 +6048,80 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="E70" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F70" t="n">
-        <v>15.6</v>
+        <v>18.6</v>
       </c>
       <c r="G70" t="n">
-        <v>14.7</v>
+        <v>15.7</v>
       </c>
       <c r="H70" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="I70" t="n">
-        <v>12.3</v>
+        <v>13.1</v>
       </c>
       <c r="J70" t="n">
-        <v>23</v>
+        <v>30.9</v>
       </c>
       <c r="K70" t="n">
-        <v>22.1</v>
+        <v>31.8</v>
       </c>
       <c r="L70" t="n">
-        <v>52.8</v>
+        <v>53</v>
       </c>
       <c r="M70" t="n">
-        <v>47.4</v>
+        <v>44.2</v>
       </c>
       <c r="N70" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="O70" t="n">
+        <v>60</v>
+      </c>
+      <c r="P70" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="R70" t="n">
         <v>5.5</v>
       </c>
-      <c r="O70" t="n">
-        <v>70</v>
-      </c>
-      <c r="P70" t="n">
-        <v>53</v>
-      </c>
-      <c r="Q70" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="R70" t="n">
-        <v>3.3</v>
-      </c>
       <c r="S70" t="n">
-        <v>5.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="T70" t="n">
-        <v>0.9</v>
+        <v>-1</v>
       </c>
       <c r="U70" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="V70" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="W70" t="inlineStr">
         <is>
-          <t>11.0 (6g)</t>
+          <t>12.9 (7g)</t>
         </is>
       </c>
       <c r="X70" t="n">
-        <v>-1</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Devin Vassell</t>
+          <t>Matisse Thybulle</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SAS @ LAC</t>
+          <t>NOP @ POR</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -6130,75 +6130,71 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>12.5</v>
+        <v>6.5</v>
       </c>
       <c r="E71" t="n">
-        <v>10</v>
+        <v>6.3</v>
       </c>
       <c r="F71" t="n">
-        <v>11</v>
+        <v>8.6</v>
       </c>
       <c r="G71" t="n">
-        <v>12.8</v>
+        <v>6.7</v>
       </c>
       <c r="H71" t="n">
-        <v>13.8</v>
+        <v>5.5</v>
       </c>
       <c r="I71" t="n">
-        <v>12.7</v>
+        <v>6.2</v>
       </c>
       <c r="J71" t="n">
-        <v>29.6</v>
+        <v>18.6</v>
       </c>
       <c r="K71" t="n">
-        <v>28.9</v>
+        <v>16.8</v>
       </c>
       <c r="L71" t="n">
-        <v>43.4</v>
+        <v>43.1</v>
       </c>
       <c r="M71" t="n">
-        <v>44.2</v>
+        <v>44</v>
       </c>
       <c r="N71" t="n">
-        <v>5.4</v>
+        <v>3.5</v>
       </c>
       <c r="O71" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="P71" t="n">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="R71" t="n">
-        <v>-1.7</v>
+        <v>2.4</v>
       </c>
       <c r="S71" t="n">
-        <v>-0.8</v>
+        <v>-0.9</v>
       </c>
       <c r="T71" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="U71" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="V71" t="n">
-        <v>26</v>
-      </c>
-      <c r="W71" t="inlineStr">
-        <is>
-          <t>13.0 (5g)</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="W71" t="inlineStr"/>
       <c r="X71" t="n">
-        <v>-7.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Dylan Harper</t>
+          <t>Keldon Johnson</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6208,38 +6204,38 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D72" t="n">
         <v>11.5</v>
       </c>
       <c r="E72" t="n">
-        <v>13.3</v>
+        <v>14</v>
       </c>
       <c r="F72" t="n">
-        <v>14.2</v>
+        <v>15.6</v>
       </c>
       <c r="G72" t="n">
-        <v>13.7</v>
+        <v>14.7</v>
       </c>
       <c r="H72" t="n">
-        <v>13.1</v>
+        <v>11.8</v>
       </c>
       <c r="I72" t="n">
-        <v>12.6</v>
+        <v>12.3</v>
       </c>
       <c r="J72" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K72" t="n">
-        <v>23.3</v>
+        <v>22.1</v>
       </c>
       <c r="L72" t="n">
-        <v>56.4</v>
+        <v>52.8</v>
       </c>
       <c r="M72" t="n">
-        <v>55.5</v>
+        <v>47.4</v>
       </c>
       <c r="N72" t="n">
         <v>5.5</v>
@@ -6248,35 +6244,39 @@
         <v>70</v>
       </c>
       <c r="P72" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="Q72" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="R72" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="S72" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="T72" t="n">
         <v>0.9</v>
       </c>
-      <c r="T72" t="n">
-        <v>0.7</v>
-      </c>
       <c r="U72" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="V72" t="n">
         <v>26</v>
       </c>
-      <c r="W72" t="inlineStr"/>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>11.0 (6g)</t>
+        </is>
+      </c>
       <c r="X72" t="n">
-        <v>8</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>De'Aaron Fox</t>
+          <t>Devin Vassell</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6290,55 +6290,55 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="E73" t="n">
         <v>10</v>
       </c>
       <c r="F73" t="n">
-        <v>11.6</v>
+        <v>11</v>
       </c>
       <c r="G73" t="n">
-        <v>15.8</v>
+        <v>12.8</v>
       </c>
       <c r="H73" t="n">
-        <v>16.6</v>
+        <v>13.8</v>
       </c>
       <c r="I73" t="n">
-        <v>16.1</v>
+        <v>12.7</v>
       </c>
       <c r="J73" t="n">
-        <v>27.8</v>
+        <v>29.6</v>
       </c>
       <c r="K73" t="n">
         <v>28.9</v>
       </c>
       <c r="L73" t="n">
-        <v>47.5</v>
+        <v>43.4</v>
       </c>
       <c r="M73" t="n">
-        <v>50.3</v>
+        <v>44.2</v>
       </c>
       <c r="N73" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="O73" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="P73" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="R73" t="n">
-        <v>-4.5</v>
+        <v>-1.7</v>
       </c>
       <c r="S73" t="n">
-        <v>-2.8</v>
+        <v>-0.8</v>
       </c>
       <c r="T73" t="n">
-        <v>-1.1</v>
+        <v>0.7</v>
       </c>
       <c r="U73" t="n">
         <v>20</v>
@@ -6348,17 +6348,17 @@
       </c>
       <c r="W73" t="inlineStr">
         <is>
-          <t>24.2 (4g)</t>
+          <t>13.0 (5g)</t>
         </is>
       </c>
       <c r="X73" t="n">
-        <v>4</v>
+        <v>-7.8</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Stephon Castle</t>
+          <t>Dylan Harper</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6372,55 +6372,55 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="E74" t="n">
-        <v>19.3</v>
+        <v>13.3</v>
       </c>
       <c r="F74" t="n">
-        <v>18.4</v>
+        <v>14.2</v>
       </c>
       <c r="G74" t="n">
-        <v>18.1</v>
+        <v>13.7</v>
       </c>
       <c r="H74" t="n">
-        <v>16.7</v>
+        <v>13.1</v>
       </c>
       <c r="I74" t="n">
-        <v>16.1</v>
+        <v>12.6</v>
       </c>
       <c r="J74" t="n">
-        <v>30.1</v>
+        <v>24</v>
       </c>
       <c r="K74" t="n">
-        <v>28.6</v>
+        <v>23.3</v>
       </c>
       <c r="L74" t="n">
-        <v>48.3</v>
+        <v>56.4</v>
       </c>
       <c r="M74" t="n">
-        <v>48.8</v>
+        <v>55.5</v>
       </c>
       <c r="N74" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="O74" t="n">
+        <v>70</v>
+      </c>
+      <c r="P74" t="n">
         <v>60</v>
       </c>
-      <c r="P74" t="n">
-        <v>53</v>
-      </c>
       <c r="Q74" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="R74" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="S74" t="n">
-        <v>-0.5</v>
+        <v>0.9</v>
       </c>
       <c r="T74" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="U74" t="n">
         <v>20</v>
@@ -6428,19 +6428,15 @@
       <c r="V74" t="n">
         <v>26</v>
       </c>
-      <c r="W74" t="inlineStr">
-        <is>
-          <t>15.7 (6g)</t>
-        </is>
-      </c>
+      <c r="W74" t="inlineStr"/>
       <c r="X74" t="n">
-        <v>4.6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Harrison Barnes</t>
+          <t>De'Aaron Fox</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6450,79 +6446,79 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>7.5</v>
+        <v>15.5</v>
       </c>
       <c r="E75" t="n">
-        <v>6.3</v>
+        <v>10</v>
       </c>
       <c r="F75" t="n">
-        <v>8.6</v>
+        <v>11.6</v>
       </c>
       <c r="G75" t="n">
-        <v>8.699999999999999</v>
+        <v>15.8</v>
       </c>
       <c r="H75" t="n">
-        <v>8.699999999999999</v>
+        <v>16.6</v>
       </c>
       <c r="I75" t="n">
-        <v>8.699999999999999</v>
+        <v>16.1</v>
       </c>
       <c r="J75" t="n">
-        <v>21.5</v>
+        <v>27.8</v>
       </c>
       <c r="K75" t="n">
-        <v>22.7</v>
+        <v>28.9</v>
       </c>
       <c r="L75" t="n">
-        <v>44.6</v>
+        <v>47.5</v>
       </c>
       <c r="M75" t="n">
-        <v>46</v>
+        <v>50.3</v>
       </c>
       <c r="N75" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="O75" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="P75" t="n">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="Q75" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="R75" t="n">
-        <v>-0.1</v>
+        <v>-4.5</v>
       </c>
       <c r="S75" t="n">
-        <v>-1.4</v>
+        <v>-2.8</v>
       </c>
       <c r="T75" t="n">
-        <v>-1.2</v>
+        <v>-1.1</v>
       </c>
       <c r="U75" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="V75" t="n">
         <v>26</v>
       </c>
       <c r="W75" t="inlineStr">
         <is>
-          <t>12.4 (5g)</t>
+          <t>24.2 (4g)</t>
         </is>
       </c>
       <c r="X75" t="n">
-        <v>13.8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Bennedict Mathurin</t>
+          <t>Stephon Castle</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6536,75 +6532,75 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="E76" t="n">
-        <v>16.3</v>
+        <v>19.3</v>
       </c>
       <c r="F76" t="n">
-        <v>17.6</v>
+        <v>18.4</v>
       </c>
       <c r="G76" t="n">
-        <v>20.9</v>
+        <v>18.1</v>
       </c>
       <c r="H76" t="n">
-        <v>19.5</v>
+        <v>16.7</v>
       </c>
       <c r="I76" t="n">
-        <v>18.3</v>
+        <v>16.1</v>
       </c>
       <c r="J76" t="n">
-        <v>29.9</v>
+        <v>30.1</v>
       </c>
       <c r="K76" t="n">
-        <v>29.6</v>
+        <v>28.6</v>
       </c>
       <c r="L76" t="n">
-        <v>45</v>
+        <v>48.3</v>
       </c>
       <c r="M76" t="n">
-        <v>42.9</v>
+        <v>48.8</v>
       </c>
       <c r="N76" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="O76" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="P76" t="n">
         <v>53</v>
       </c>
       <c r="Q76" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="R76" t="n">
-        <v>-0.7</v>
+        <v>2.3</v>
       </c>
       <c r="S76" t="n">
-        <v>2.1</v>
+        <v>-0.5</v>
       </c>
       <c r="T76" t="n">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="U76" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="V76" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="W76" t="inlineStr">
         <is>
-          <t>12.6 (5g)</t>
+          <t>15.7 (6g)</t>
         </is>
       </c>
       <c r="X76" t="n">
-        <v>-4.3</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>John Collins</t>
+          <t>Harrison Barnes</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6618,75 +6614,75 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.5</v>
+        <v>7.5</v>
       </c>
       <c r="E77" t="n">
-        <v>14.7</v>
+        <v>6.3</v>
       </c>
       <c r="F77" t="n">
-        <v>10.4</v>
+        <v>8.6</v>
       </c>
       <c r="G77" t="n">
-        <v>12.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H77" t="n">
-        <v>14.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I77" t="n">
-        <v>14.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J77" t="n">
-        <v>26.1</v>
+        <v>21.5</v>
       </c>
       <c r="K77" t="n">
-        <v>28.4</v>
+        <v>22.7</v>
       </c>
       <c r="L77" t="n">
-        <v>46.3</v>
+        <v>44.6</v>
       </c>
       <c r="M77" t="n">
-        <v>56.2</v>
+        <v>46</v>
       </c>
       <c r="N77" t="n">
-        <v>6.8</v>
+        <v>5</v>
       </c>
       <c r="O77" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="P77" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="R77" t="n">
-        <v>-4.2</v>
+        <v>-0.1</v>
       </c>
       <c r="S77" t="n">
-        <v>-9.9</v>
+        <v>-1.4</v>
       </c>
       <c r="T77" t="n">
-        <v>-2.4</v>
+        <v>-1.2</v>
       </c>
       <c r="U77" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="V77" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="W77" t="inlineStr">
         <is>
-          <t>15.6 (5g)</t>
+          <t>12.4 (5g)</t>
         </is>
       </c>
       <c r="X77" t="n">
-        <v>-3.6</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Julian Champagnie</t>
+          <t>Bennedict Mathurin</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6696,79 +6692,79 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>9.5</v>
+        <v>16.5</v>
       </c>
       <c r="E78" t="n">
-        <v>13</v>
+        <v>16.3</v>
       </c>
       <c r="F78" t="n">
-        <v>11</v>
+        <v>17.6</v>
       </c>
       <c r="G78" t="n">
-        <v>11.2</v>
+        <v>20.9</v>
       </c>
       <c r="H78" t="n">
-        <v>11.7</v>
+        <v>19.5</v>
       </c>
       <c r="I78" t="n">
-        <v>10.3</v>
+        <v>18.3</v>
       </c>
       <c r="J78" t="n">
-        <v>27.1</v>
+        <v>29.9</v>
       </c>
       <c r="K78" t="n">
-        <v>26.1</v>
+        <v>29.6</v>
       </c>
       <c r="L78" t="n">
-        <v>45.9</v>
+        <v>45</v>
       </c>
       <c r="M78" t="n">
-        <v>44.8</v>
+        <v>42.9</v>
       </c>
       <c r="N78" t="n">
-        <v>4.1</v>
+        <v>7.2</v>
       </c>
       <c r="O78" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="P78" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="R78" t="n">
-        <v>0.7</v>
+        <v>-0.7</v>
       </c>
       <c r="S78" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="T78" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="U78" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="V78" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="W78" t="inlineStr">
         <is>
-          <t>11.3 (6g)</t>
+          <t>12.6 (5g)</t>
         </is>
       </c>
       <c r="X78" t="n">
-        <v>2.9</v>
+        <v>-4.3</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Brook Lopez</t>
+          <t>John Collins</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6778,79 +6774,79 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="E79" t="n">
-        <v>14</v>
+        <v>14.7</v>
       </c>
       <c r="F79" t="n">
-        <v>15</v>
+        <v>10.4</v>
       </c>
       <c r="G79" t="n">
-        <v>10.5</v>
+        <v>12.4</v>
       </c>
       <c r="H79" t="n">
-        <v>11.1</v>
+        <v>14.1</v>
       </c>
       <c r="I79" t="n">
-        <v>10.5</v>
+        <v>14.6</v>
       </c>
       <c r="J79" t="n">
-        <v>28.3</v>
+        <v>26.1</v>
       </c>
       <c r="K79" t="n">
-        <v>27.1</v>
+        <v>28.4</v>
       </c>
       <c r="L79" t="n">
-        <v>45.7</v>
+        <v>46.3</v>
       </c>
       <c r="M79" t="n">
-        <v>45.6</v>
+        <v>56.2</v>
       </c>
       <c r="N79" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="O79" t="n">
         <v>50</v>
       </c>
       <c r="P79" t="n">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="Q79" t="n">
-        <v>-0</v>
+        <v>3.1</v>
       </c>
       <c r="R79" t="n">
-        <v>4.5</v>
+        <v>-4.2</v>
       </c>
       <c r="S79" t="n">
-        <v>0.1</v>
+        <v>-9.9</v>
       </c>
       <c r="T79" t="n">
-        <v>1.2</v>
+        <v>-2.4</v>
       </c>
       <c r="U79" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="V79" t="n">
         <v>9</v>
       </c>
       <c r="W79" t="inlineStr">
         <is>
-          <t>14.2 (4g)</t>
+          <t>15.6 (5g)</t>
         </is>
       </c>
       <c r="X79" t="n">
-        <v>4.3</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Darius Garland</t>
+          <t>Julian Champagnie</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6860,41 +6856,41 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>19.5</v>
+        <v>9.5</v>
       </c>
       <c r="E80" t="n">
-        <v>21.7</v>
+        <v>13</v>
       </c>
       <c r="F80" t="n">
-        <v>20.8</v>
+        <v>11</v>
       </c>
       <c r="G80" t="n">
-        <v>22.9</v>
+        <v>11.2</v>
       </c>
       <c r="H80" t="n">
-        <v>21.1</v>
+        <v>11.7</v>
       </c>
       <c r="I80" t="n">
-        <v>20.7</v>
+        <v>10.3</v>
       </c>
       <c r="J80" t="n">
-        <v>29.9</v>
+        <v>27.1</v>
       </c>
       <c r="K80" t="n">
-        <v>30.1</v>
+        <v>26.1</v>
       </c>
       <c r="L80" t="n">
-        <v>53.9</v>
+        <v>45.9</v>
       </c>
       <c r="M80" t="n">
-        <v>50.9</v>
+        <v>44.8</v>
       </c>
       <c r="N80" t="n">
-        <v>8.300000000000001</v>
+        <v>4.1</v>
       </c>
       <c r="O80" t="n">
         <v>70</v>
@@ -6903,36 +6899,36 @@
         <v>57</v>
       </c>
       <c r="Q80" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="R80" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="S80" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="T80" t="n">
-        <v>-0.2</v>
+        <v>1</v>
       </c>
       <c r="U80" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="V80" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="W80" t="inlineStr">
         <is>
-          <t>17.2 (4g)</t>
+          <t>11.3 (6g)</t>
         </is>
       </c>
       <c r="X80" t="n">
-        <v>-11</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Victor Wembanyama</t>
+          <t>Brook Lopez</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6942,79 +6938,79 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>24.5</v>
+        <v>10.5</v>
       </c>
       <c r="E81" t="n">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="F81" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G81" t="n">
-        <v>27.5</v>
+        <v>10.5</v>
       </c>
       <c r="H81" t="n">
-        <v>25.8</v>
+        <v>11.1</v>
       </c>
       <c r="I81" t="n">
-        <v>25</v>
+        <v>10.5</v>
       </c>
       <c r="J81" t="n">
-        <v>29.1</v>
+        <v>28.3</v>
       </c>
       <c r="K81" t="n">
-        <v>29.7</v>
+        <v>27.1</v>
       </c>
       <c r="L81" t="n">
-        <v>51.6</v>
+        <v>45.7</v>
       </c>
       <c r="M81" t="n">
-        <v>50.2</v>
+        <v>45.6</v>
       </c>
       <c r="N81" t="n">
-        <v>8.9</v>
+        <v>6.4</v>
       </c>
       <c r="O81" t="n">
         <v>50</v>
       </c>
       <c r="P81" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.5</v>
+        <v>-0</v>
       </c>
       <c r="R81" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="S81" t="n">
-        <v>1.4</v>
+        <v>0.1</v>
       </c>
       <c r="T81" t="n">
-        <v>-0.6</v>
+        <v>1.2</v>
       </c>
       <c r="U81" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="V81" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="W81" t="inlineStr">
         <is>
-          <t>24.4 (5g)</t>
+          <t>14.2 (4g)</t>
         </is>
       </c>
       <c r="X81" t="n">
-        <v>-3.1</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Kris Dunn</t>
+          <t>Darius Garland</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7028,55 +7024,55 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>4.5</v>
+        <v>19.5</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>21.7</v>
       </c>
       <c r="F82" t="n">
-        <v>4.4</v>
+        <v>20.8</v>
       </c>
       <c r="G82" t="n">
-        <v>5.4</v>
+        <v>22.9</v>
       </c>
       <c r="H82" t="n">
-        <v>6.2</v>
+        <v>21.1</v>
       </c>
       <c r="I82" t="n">
-        <v>6.7</v>
+        <v>20.7</v>
       </c>
       <c r="J82" t="n">
-        <v>26.1</v>
+        <v>29.9</v>
       </c>
       <c r="K82" t="n">
-        <v>27.5</v>
+        <v>30.1</v>
       </c>
       <c r="L82" t="n">
-        <v>40.6</v>
+        <v>53.9</v>
       </c>
       <c r="M82" t="n">
-        <v>47.3</v>
+        <v>50.9</v>
       </c>
       <c r="N82" t="n">
-        <v>3.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O82" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="P82" t="n">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="Q82" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="R82" t="n">
-        <v>-2.3</v>
+        <v>0.1</v>
       </c>
       <c r="S82" t="n">
-        <v>-6.7</v>
+        <v>3</v>
       </c>
       <c r="T82" t="n">
-        <v>-1.5</v>
+        <v>-0.2</v>
       </c>
       <c r="U82" t="n">
         <v>8</v>
@@ -7086,17 +7082,17 @@
       </c>
       <c r="W82" t="inlineStr">
         <is>
-          <t>7.4 (5g)</t>
+          <t>17.2 (4g)</t>
         </is>
       </c>
       <c r="X82" t="n">
-        <v>0.4</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Kawhi Leonard</t>
+          <t>Victor Wembanyama</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7110,71 +7106,75 @@
         </is>
       </c>
       <c r="D83" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E83" t="n">
+        <v>35</v>
+      </c>
+      <c r="F83" t="n">
+        <v>30</v>
+      </c>
+      <c r="G83" t="n">
         <v>27.5</v>
       </c>
-      <c r="E83" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="F83" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="G83" t="n">
-        <v>28.9</v>
-      </c>
       <c r="H83" t="n">
-        <v>28.4</v>
+        <v>25.8</v>
       </c>
       <c r="I83" t="n">
-        <v>27.9</v>
+        <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>30.4</v>
+        <v>29.1</v>
       </c>
       <c r="K83" t="n">
-        <v>30.5</v>
+        <v>29.7</v>
       </c>
       <c r="L83" t="n">
-        <v>53.6</v>
+        <v>51.6</v>
       </c>
       <c r="M83" t="n">
-        <v>51.2</v>
+        <v>50.2</v>
       </c>
       <c r="N83" t="n">
-        <v>6.9</v>
+        <v>8.9</v>
       </c>
       <c r="O83" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="P83" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.4</v>
+        <v>-0.5</v>
       </c>
       <c r="R83" t="n">
-        <v>-2.7</v>
+        <v>5</v>
       </c>
       <c r="S83" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="T83" t="n">
-        <v>-0.1</v>
+        <v>-0.6</v>
       </c>
       <c r="U83" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="V83" t="n">
-        <v>9</v>
-      </c>
-      <c r="W83" t="inlineStr"/>
+        <v>26</v>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>24.4 (5g)</t>
+        </is>
+      </c>
       <c r="X83" t="n">
-        <v>2.4</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Derrick Jones Jr.</t>
+          <t>Kawhi Leonard</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7188,55 +7188,55 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>8.5</v>
+        <v>27.5</v>
       </c>
       <c r="E84" t="n">
-        <v>6</v>
+        <v>23.7</v>
       </c>
       <c r="F84" t="n">
-        <v>5.4</v>
+        <v>25.2</v>
       </c>
       <c r="G84" t="n">
-        <v>8</v>
+        <v>28.9</v>
       </c>
       <c r="H84" t="n">
-        <v>10.4</v>
+        <v>28.4</v>
       </c>
       <c r="I84" t="n">
-        <v>10.8</v>
+        <v>27.9</v>
       </c>
       <c r="J84" t="n">
-        <v>28.2</v>
+        <v>30.4</v>
       </c>
       <c r="K84" t="n">
-        <v>28.7</v>
+        <v>30.5</v>
       </c>
       <c r="L84" t="n">
-        <v>40</v>
+        <v>53.6</v>
       </c>
       <c r="M84" t="n">
-        <v>50</v>
+        <v>51.2</v>
       </c>
       <c r="N84" t="n">
         <v>6.9</v>
       </c>
       <c r="O84" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="P84" t="n">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="Q84" t="n">
-        <v>2.3</v>
+        <v>0.4</v>
       </c>
       <c r="R84" t="n">
-        <v>-5.4</v>
+        <v>-2.7</v>
       </c>
       <c r="S84" t="n">
-        <v>-10</v>
+        <v>2.4</v>
       </c>
       <c r="T84" t="n">
-        <v>-0.4</v>
+        <v>-0.1</v>
       </c>
       <c r="U84" t="n">
         <v>8</v>
@@ -7244,13 +7244,173 @@
       <c r="V84" t="n">
         <v>9</v>
       </c>
-      <c r="W84" t="inlineStr">
+      <c r="W84" t="inlineStr"/>
+      <c r="X84" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Derrick Jones Jr.</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>SAS @ LAC</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Forward</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E85" t="n">
+        <v>6</v>
+      </c>
+      <c r="F85" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="G85" t="n">
+        <v>8</v>
+      </c>
+      <c r="H85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="I85" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="J85" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="K85" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="L85" t="n">
+        <v>40</v>
+      </c>
+      <c r="M85" t="n">
+        <v>50</v>
+      </c>
+      <c r="N85" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="O85" t="n">
+        <v>40</v>
+      </c>
+      <c r="P85" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R85" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="S85" t="n">
+        <v>-10</v>
+      </c>
+      <c r="T85" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="U85" t="n">
+        <v>8</v>
+      </c>
+      <c r="V85" t="n">
+        <v>9</v>
+      </c>
+      <c r="W85" t="inlineStr">
         <is>
           <t>10.5 (6g)</t>
         </is>
       </c>
-      <c r="X84" t="n">
+      <c r="X85" t="n">
         <v>-14.5</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Kris Dunn</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>SAS @ LAC</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Guard</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E86" t="n">
+        <v>5</v>
+      </c>
+      <c r="F86" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G86" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H86" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I86" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="J86" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="K86" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="L86" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="M86" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="N86" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O86" t="n">
+        <v>60</v>
+      </c>
+      <c r="P86" t="n">
+        <v>73</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R86" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="S86" t="n">
+        <v>-6.7</v>
+      </c>
+      <c r="T86" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="U86" t="n">
+        <v>8</v>
+      </c>
+      <c r="V86" t="n">
+        <v>9</v>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>7.4 (5g)</t>
+        </is>
+      </c>
+      <c r="X86" t="n">
+        <v>0.4</v>
       </c>
     </row>
   </sheetData>
@@ -7264,7 +7424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L84"/>
+  <dimension ref="A1:L86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="12" max="12"/>
@@ -7369,10 +7529,10 @@
         <v>0.2</v>
       </c>
       <c r="J2" t="n">
-        <v>1.909</v>
+        <v>2.75</v>
       </c>
       <c r="K2" t="n">
-        <v>1.826</v>
+        <v>1.417</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -7417,10 +7577,10 @@
         <v>0.6</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="K3" t="n">
-        <v>1.385</v>
+        <v>1.435</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
@@ -7431,7 +7591,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Grayson Allen</t>
+          <t>LaMelo Ball</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -7450,36 +7610,36 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.582</v>
+        <v>0.522</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>14.4</v>
+        <v>20.9</v>
       </c>
       <c r="I4" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="J4" t="n">
-        <v>1.806</v>
+        <v>3.1</v>
       </c>
       <c r="K4" t="n">
-        <v>1.926</v>
+        <v>1.345</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>Allen's L30 of 17.5 pts sits 5.0 above the 12.5 line — marginally supports the OVER. Opponent is strong defense (#9) at moderate pace (#19). Mixed signals: 5/10 agree (Volume, HR L30, HR L10); counter-signals: Trend, Defense, H2H. Projection model targets 14.4 pts (1.9 pts above line; 58% blended confidence [T3]).</t>
+          <t>Ball averages 26.3 pts in 3 meetings (+5.8 vs line) — marginally supports the OVER. H2H avg 6.3 pts above season L30; FG% +3.3% trending (L10 vs L30). Opponent is elite defense (#4) at slow pace (#21). Mixed signals: 4/10 agree (Context, H2H, FG Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 20.9 pts (0.4 pts above line; 52% blended confidence [T3]). Risk: only 33% hit rate over L30 suggests the line may be set fairly.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LaMelo Ball</t>
+          <t>Devin Booker</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -7494,40 +7654,40 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.544</v>
+        <v>0.746</v>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>20.9</v>
+        <v>34.7</v>
       </c>
       <c r="I5" t="n">
-        <v>1.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K5" t="n">
-        <v>1.345</v>
+        <v>1.357</v>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>Ball averages 26.3 pts in 3 meetings (+6.8 vs line) — supports the OVER. H2H avg 6.3 pts above season L30; FG% +3.3% trending (L10 vs L30). Opponent is elite defense (#4) at slow pace (#21). 7/10 signals agree — Volume, HR L30, HR L10, Context support the OVER; Trend, Defense, Pace dissent. Projection model targets 20.9 pts (1.4 pts above line; 54% blended confidence [T3]).</t>
+          <t>Booker averages 33.0 pts in 3 meetings (+7.5 vs line) — supports the OVER. H2H avg 6.9 pts above season L30; TS% shifts +6.5% in this matchup. Opponent is strong defense (#9) at moderate pace (#19). 8/10 signals agree — Volume, HR L30, HR L10, Trend support the OVER; Defense, Pace dissent. Projection model targets 34.7 pts (9.2 pts above line; 74% blended confidence [T2]). Risk: high variance (σ=7.9) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Jalen Green</t>
+          <t>Ryan Kalkbrenner</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -7537,7 +7697,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -7546,36 +7706,36 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.532</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>14.3</v>
+        <v>6.3</v>
       </c>
       <c r="I6" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J6" t="n">
-        <v>1.775</v>
+        <v>2.9</v>
       </c>
       <c r="K6" t="n">
-        <v>1.962</v>
+        <v>1.385</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>Green averages 19.3 pts in 3 meetings (+3.8 vs line) — marginally supports the UNDER. H2H avg 2.2 pts above season L30; FG% +4.8% trending (L10 vs L30). Opponent is strong defense (#9) at moderate pace (#19). Mixed signals: 2/10 agree (Defense, Pace); counter-signals: Volume, HR L30, HR L10. Projection model targets 14.3 pts (1.2 pts below line; 55% blended confidence [T3]). Risk: high variance (σ=8.2) makes the outcome difficult to call with confidence.</t>
+          <t>Low scoring variance (σ=4.0) — highly predictable output near line — supports the OVER. FG% +12.9% trending (L10 vs L30). Opponent is below-average defense (#16) at slow pace (#21). 6/10 signals agree — Volume, HR L30, HR L10, Context support the OVER; Trend, H2H, Pace dissent. Projection model targets 6.3 pts (0.8 pts above line; 53% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Devin Booker</t>
+          <t>Moussa Diabaté</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -7585,28 +7745,28 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.746</v>
+        <v>0.615</v>
       </c>
       <c r="F7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>34.7</v>
+        <v>2.8</v>
       </c>
       <c r="I7" t="n">
-        <v>9.199999999999999</v>
+        <v>4.7</v>
       </c>
       <c r="J7" t="n">
         <v>2.9</v>
@@ -7616,14 +7776,14 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>Booker averages 33.0 pts in 3 meetings (+7.5 vs line) — supports the OVER. H2H avg 6.9 pts above season L30; TS% shifts +6.5% in this matchup. Opponent is strong defense (#9) at moderate pace (#19). 8/10 signals agree — Volume, HR L30, HR L10, Trend support the OVER; Defense, Pace dissent. Projection model targets 34.7 pts (9.2 pts above line; 74% blended confidence [T2]). Risk: high variance (σ=7.9) makes the outcome difficult to call with confidence.</t>
+          <t>Low scoring variance (σ=4.9) — highly predictable output near line — marginally supports the UNDER. Opponent is strong defense (#8) at slow pace (#21). Mixed signals: 5/10 agree (Context, Defense, Pace); counter-signals: Volume, HR L30, HR L10. Projection model targets 2.8 pts (4.7 pts below line; 61% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ryan Kalkbrenner</t>
+          <t>Coby White</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -7642,19 +7802,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.532</v>
+        <v>0.54</v>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>6.3</v>
+        <v>13.9</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J8" t="n">
         <v>3</v>
@@ -7664,14 +7824,14 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Low scoring variance (σ=4.0) — highly predictable output near line — supports the OVER. FG% +12.9% trending (L10 vs L30). Opponent is below-average defense (#16) at slow pace (#21). 6/10 signals agree — Volume, HR L30, HR L10, Context support the OVER; Trend, H2H, Pace dissent. Projection model targets 6.3 pts (0.8 pts above line; 53% blended confidence [T3]).</t>
+          <t>White averages 17.0 pts in 3 meetings (+3.5 vs line) — supports the OVER. FG% +5.8% trending (L10 vs L30); Minutes down 3.2 recently (L10=20.9 vs L30=24.1). Opponent is elite defense (#4) at slow pace (#21). 7/10 signals agree — Volume, HR L30, HR L10, Trend support the OVER; Defense, Pace, Min Trend dissent. Projection model targets 13.9 pts (0.4 pts above line; 53% blended confidence [T3]). Risk: minutes trending down (20.9 L10 vs 24.1 L30) — role reduction would suppress counting stats.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Moussa Diabaté</t>
+          <t>Kon Knueppel</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -7686,40 +7846,40 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>T1_PREMIUM</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.653</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>5.7</v>
+        <v>7.3</v>
       </c>
       <c r="J9" t="n">
-        <v>3.05</v>
+        <v>2.75</v>
       </c>
       <c r="K9" t="n">
-        <v>1.357</v>
+        <v>1.417</v>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>Low scoring variance (σ=4.9) — highly predictable output near line — supports the UNDER. Opponent is strong defense (#8) at slow pace (#21). 7/10 signals agree — Volume, HR L10, Context, Defense support the UNDER; HR L30, Trend, H2H dissent. Projection model targets 2.8 pts (5.7 pts below line; 65% blended confidence [T1_PREMIUM]).</t>
+          <t>Recent scoring trending down 4.3 pts (L5 vs L30) — marginally supports the UNDER. FG% -4.4% trending (L10 vs L30). Opponent is elite defense (#4) at slow pace (#21). Mixed signals: 5/10 agree (Trend, Defense, Pace); counter-signals: Volume, HR L30, HR L10. Projection model targets 9.2 pts (7.3 pts below line; 69% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Coby White</t>
+          <t>Brandon Miller</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -7738,36 +7898,36 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.533</v>
+        <v>0.644</v>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>13.9</v>
+        <v>13.5</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6</v>
+        <v>6</v>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="K10" t="n">
-        <v>1.364</v>
+        <v>1.408</v>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>White averages 17.0 pts in 3 meetings (+2.5 vs line) — marginally supports the UNDER. FG% +5.8% trending (L10 vs L30); Minutes down 3.2 recently (L10=20.9 vs L30=24.1). Opponent is elite defense (#4) at slow pace (#21). Mixed signals: 3/10 agree (Defense, Pace, Min Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 13.9 pts (0.6 pts below line; 53% blended confidence [T3]). Risk: 60% over-rate on L30 suggests scoring tendency that could threaten the under.</t>
+          <t>Miller averages 14.3 pts in 3 meetings (-5.2 vs line) — marginally supports the UNDER. H2H avg 6.5 pts below season L30; TS% shifts -10.9% in this matchup. Opponent is strong defense (#8) at slow pace (#21). Mixed signals: 5/10 agree (Trend, Defense, H2H); counter-signals: Volume, HR L30, HR L10. Projection model targets 13.5 pts (6.0 pts below line; 64% blended confidence [T3]). Risk: 60% over-rate on L30 suggests scoring tendency that could threaten the under.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Kon Knueppel</t>
+          <t>Royce O'Neale</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -7786,36 +7946,36 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.608</v>
       </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>9.199999999999999</v>
+        <v>4</v>
       </c>
       <c r="I11" t="n">
-        <v>7.3</v>
+        <v>3.5</v>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="K11" t="n">
-        <v>1.364</v>
+        <v>1.408</v>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending down 4.3 pts (L5 vs L30) — marginally supports the UNDER. FG% -4.4% trending (L10 vs L30). Opponent is elite defense (#4) at slow pace (#21). Mixed signals: 5/10 agree (Trend, Defense, Pace); counter-signals: Volume, HR L30, HR L10. Projection model targets 9.2 pts (7.3 pts below line; 69% blended confidence [T3]).</t>
+          <t>O'Neale's L30 average of 9.3 pts vs the 7.5 line — marginally supports the UNDER. FG% +4.7% trending (L10 vs L30). Opponent is strong defense (#8) at moderate pace (#19). Mixed signals: 3/10 agree (Defense, Pace, Min Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 4.0 pts (3.5 pts below line; 60% blended confidence [T3]). Risk: 67% over-rate on L30 suggests scoring tendency that could threaten the under.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Brandon Miller</t>
+          <t>Collin Gillespie</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -7825,7 +7985,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -7834,36 +7994,36 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.644</v>
+        <v>0.668</v>
       </c>
       <c r="F12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>13.5</v>
+        <v>17.3</v>
       </c>
       <c r="I12" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="J12" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="K12" t="n">
-        <v>1.385</v>
+        <v>1.345</v>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>Miller averages 14.3 pts in 3 meetings (-5.2 vs line) — marginally supports the UNDER. H2H avg 6.5 pts below season L30; TS% shifts -10.9% in this matchup. Opponent is strong defense (#8) at slow pace (#21). Mixed signals: 5/10 agree (Trend, Defense, H2H); counter-signals: Volume, HR L30, HR L10. Projection model targets 13.5 pts (6.0 pts below line; 64% blended confidence [T3]). Risk: 60% over-rate on L30 suggests scoring tendency that could threaten the under.</t>
+          <t>Gillespie's L30 of 12.5 pts sits 2.0 above the 10.5 line — marginally supports the OVER. FG% -5.1% trending (L10 vs L30). Opponent is strong defense (#9) at moderate pace (#19). Mixed signals: 4/10 agree (Volume, HR L30, HR L10); counter-signals: Trend, Defense, H2H. Projection model targets 17.3 pts (6.8 pts above line; 66% blended confidence [T3]). Risk: L3 has dropped to 7.3 (5.2 below L30) — deepening slump makes the over vulnerable.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Dillon Brooks</t>
+          <t>Miles Bridges</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -7873,7 +8033,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -7882,7 +8042,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.759</v>
+        <v>0.537</v>
       </c>
       <c r="F13" t="n">
         <v>5</v>
@@ -7891,27 +8051,27 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1.9</v>
+        <v>14.4</v>
       </c>
       <c r="I13" t="n">
-        <v>12.6</v>
+        <v>0.9</v>
       </c>
       <c r="J13" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="K13" t="n">
-        <v>1.435</v>
+        <v>1.385</v>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>Brooks's L30 of 19.9 pts sits 5.4 above the 14.5 line — marginally supports the UNDER. Minutes down 2.3 recently (L10=27.8 vs L30=30.1). Opponent is strong defense (#9) at moderate pace (#19). Mixed signals: 5/10 agree (Trend, Defense, Pace); counter-signals: Volume, HR L30, HR L10. Projection model targets 1.9 pts (12.6 pts below line; 75% blended confidence [T3]). Risk: high variance (σ=10.3) makes the outcome difficult to call with confidence.</t>
+          <t>Bridges averages 19.3 pts in 3 meetings (+5.8 vs line) — marginally supports the OVER. H2H avg 5.3 pts above season L30; FG% +8.8% trending (L10 vs L30). Opponent is strong defense (#8) at slow pace (#21). Mixed signals: 5/10 agree (Volume, HR L10, Context); counter-signals: HR L30, Trend, Defense. Projection model targets 14.4 pts (0.9 pts above line; 53% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Royce O'Neale</t>
+          <t>Grayson Allen</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -7921,7 +8081,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -7930,36 +8090,36 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.608</v>
+        <v>0.582</v>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>14.4</v>
       </c>
       <c r="I14" t="n">
-        <v>3.5</v>
+        <v>1.9</v>
       </c>
       <c r="J14" t="n">
-        <v>1.917</v>
+        <v>3.1</v>
       </c>
       <c r="K14" t="n">
-        <v>1.82</v>
+        <v>1.345</v>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>O'Neale's L30 average of 9.3 pts vs the 7.5 line — marginally supports the UNDER. FG% +4.7% trending (L10 vs L30). Opponent is strong defense (#8) at moderate pace (#19). Mixed signals: 3/10 agree (Defense, Pace, Min Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 4.0 pts (3.5 pts below line; 60% blended confidence [T3]). Risk: 67% over-rate on L30 suggests scoring tendency that could threaten the under.</t>
+          <t>Allen's L30 of 17.5 pts sits 5.0 above the 12.5 line — marginally supports the OVER. Opponent is strong defense (#9) at moderate pace (#19). Mixed signals: 5/10 agree (Volume, HR L30, HR L10); counter-signals: Trend, Defense, H2H. Projection model targets 14.4 pts (1.9 pts above line; 58% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Collin Gillespie</t>
+          <t>Jalen Green</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -7969,7 +8129,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -7978,36 +8138,36 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.668</v>
+        <v>0.572</v>
       </c>
       <c r="F15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>17.3</v>
+        <v>14.3</v>
       </c>
       <c r="I15" t="n">
-        <v>6.8</v>
+        <v>2.2</v>
       </c>
       <c r="J15" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="K15" t="n">
-        <v>1.385</v>
+        <v>1.364</v>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>Gillespie's L30 of 12.5 pts sits 2.0 above the 10.5 line — marginally supports the OVER. FG% -5.1% trending (L10 vs L30). Opponent is strong defense (#9) at moderate pace (#19). Mixed signals: 4/10 agree (Volume, HR L30, HR L10); counter-signals: Trend, Defense, H2H. Projection model targets 17.3 pts (6.8 pts above line; 66% blended confidence [T3]). Risk: L3 has dropped to 7.3 (5.2 below L30) — deepening slump makes the over vulnerable.</t>
+          <t>Recent scoring trending up 3.1 pts (L5 vs L30) — marginally supports the UNDER. H2H avg 2.2 pts above season L30; FG% +4.8% trending (L10 vs L30). Opponent is strong defense (#9) at moderate pace (#19). Mixed signals: 3/10 agree (Context, Defense, Pace); counter-signals: Volume, HR L30, HR L10. Projection model targets 14.3 pts (2.2 pts below line; 57% blended confidence [T3]). Risk: high variance (σ=8.2) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Miles Bridges</t>
+          <t>Dillon Brooks</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -8017,7 +8177,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -8026,7 +8186,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.537</v>
+        <v>0.759</v>
       </c>
       <c r="F16" t="n">
         <v>5</v>
@@ -8035,20 +8195,20 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>14.4</v>
+        <v>1.9</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9</v>
+        <v>12.6</v>
       </c>
       <c r="J16" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="K16" t="n">
-        <v>1.417</v>
+        <v>1.4</v>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>Bridges averages 19.3 pts in 3 meetings (+5.8 vs line) — marginally supports the OVER. H2H avg 5.3 pts above season L30; FG% +8.8% trending (L10 vs L30). Opponent is strong defense (#8) at slow pace (#21). Mixed signals: 5/10 agree (Volume, HR L10, Context); counter-signals: HR L30, Trend, Defense. Projection model targets 14.4 pts (0.9 pts above line; 53% blended confidence [T3]).</t>
+          <t>Brooks's L30 of 19.9 pts sits 5.4 above the 14.5 line — marginally supports the UNDER. Minutes down 2.3 recently (L10=27.8 vs L30=30.1). Opponent is strong defense (#9) at moderate pace (#19). Mixed signals: 5/10 agree (Trend, Defense, Pace); counter-signals: Volume, HR L30, HR L10. Projection model targets 1.9 pts (12.6 pts below line; 75% blended confidence [T3]). Risk: high variance (σ=10.3) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
@@ -8089,10 +8249,10 @@
         <v>6.7</v>
       </c>
       <c r="J17" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="K17" t="n">
-        <v>1.357</v>
+        <v>1.408</v>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
@@ -8137,10 +8297,10 @@
         <v>0.1</v>
       </c>
       <c r="J18" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="K18" t="n">
-        <v>1.935</v>
+        <v>1.465</v>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
@@ -8185,10 +8345,10 @@
         <v>1.7</v>
       </c>
       <c r="J19" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="K19" t="n">
-        <v>1.408</v>
+        <v>1.364</v>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
@@ -8233,10 +8393,10 @@
         <v>3.2</v>
       </c>
       <c r="J20" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="K20" t="n">
-        <v>1.417</v>
+        <v>1.385</v>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
@@ -8281,10 +8441,10 @@
         <v>1.7</v>
       </c>
       <c r="J21" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="K21" t="n">
-        <v>1.385</v>
+        <v>1.345</v>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
@@ -8314,10 +8474,10 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.521</v>
+        <v>0.543</v>
       </c>
       <c r="F22" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -8326,17 +8486,17 @@
         <v>9.9</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J22" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="K22" t="n">
-        <v>1.408</v>
+        <v>1.435</v>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending up 3.6 pts (L5 vs L30) — marginally supports the UNDER. Opponent is elite defense (#4) at moderate pace (#17). Mixed signals: 4/10 agree (Context, Defense, Pace); counter-signals: Volume, HR L30, HR L10. Projection model targets 9.9 pts (0.6 pts below line; 52% blended confidence [T3]). Risk: L3 has surged to 18.0 after a 3-pt outing (6.6 above L30) — momentum could push over the under line.</t>
+          <t>Recent scoring trending up 3.6 pts (L5 vs L30) — supports the UNDER. Opponent is elite defense (#4) at moderate pace (#17). 7/10 signals agree — Volume, HR L30, Context, Defense support the UNDER; HR L10, Trend, Min Trend dissent. Projection model targets 9.9 pts (1.6 pts below line; 54% blended confidence [T3]). Risk: L3 has surged to 18.0 after a 3-pt outing (6.6 above L30) — momentum could push over the under line.</t>
         </is>
       </c>
     </row>
@@ -8473,10 +8633,10 @@
         <v>5.5</v>
       </c>
       <c r="J25" t="n">
-        <v>1.98</v>
+        <v>1.901</v>
       </c>
       <c r="K25" t="n">
-        <v>1.787</v>
+        <v>1.833</v>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
@@ -8521,10 +8681,10 @@
         <v>3.6</v>
       </c>
       <c r="J26" t="n">
-        <v>1.73</v>
+        <v>2.9</v>
       </c>
       <c r="K26" t="n">
-        <v>2.03</v>
+        <v>1.385</v>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
@@ -8569,10 +8729,10 @@
         <v>0.4</v>
       </c>
       <c r="J27" t="n">
-        <v>2.85</v>
+        <v>3.15</v>
       </c>
       <c r="K27" t="n">
-        <v>1.4</v>
+        <v>1.333</v>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
@@ -8602,7 +8762,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.672</v>
+        <v>0.697</v>
       </c>
       <c r="F28" t="n">
         <v>4</v>
@@ -8614,7 +8774,7 @@
         <v>34</v>
       </c>
       <c r="I28" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="J28" t="n">
         <v>3</v>
@@ -8624,7 +8784,7 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>Edwards's L30 of 29.1 pts sits 2.6 above the 26.5 line — marginally supports the OVER. Opponent is elite defense (#4) at moderate pace (#17). Mixed signals: 4/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 34.0 pts (7.5 pts above line; 67% blended confidence [T3]). Risk: high variance (σ=10.3) makes the outcome difficult to call with confidence.</t>
+          <t>Edwards's L30 of 29.1 pts sits 3.6 above the 25.5 line — marginally supports the OVER. Opponent is elite defense (#4) at moderate pace (#17). Mixed signals: 4/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 34.0 pts (8.5 pts above line; 69% blended confidence [T3]). Risk: high variance (σ=10.3) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
@@ -8665,10 +8825,10 @@
         <v>0.2</v>
       </c>
       <c r="J29" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K29" t="n">
-        <v>1.357</v>
+        <v>1.345</v>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
@@ -8790,33 +8950,33 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.539</v>
+        <v>0.574</v>
       </c>
       <c r="F32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
         <v>13</v>
       </c>
       <c r="I32" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J32" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="K32" t="n">
-        <v>1.408</v>
+        <v>1.364</v>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>Holmgren averages 12.0 pts in 4 meetings (-2.5 vs line) — marginally supports the UNDER. H2H avg 4.1 pts below season L30. Opponent is strong defense (#6) at moderate pace (#18). Mixed signals: 5/10 agree (Trend, Defense, H2H); counter-signals: Volume, HR L30, HR L10. Projection model targets 13.0 pts (1.5 pts below line; 53% blended confidence [T3]). Risk: 60% over-rate on L30 suggests scoring tendency that could threaten the under.</t>
+          <t>Holmgren averages 12.0 pts in 4 meetings (-3.5 vs line) — supports the UNDER. H2H avg 4.1 pts below season L30. Opponent is strong defense (#6) at moderate pace (#18). 6/10 signals agree — Trend, Context, Defense, H2H support the UNDER; Volume, HR L30, HR L10 dissent. Projection model targets 13.0 pts (2.5 pts below line; 57% blended confidence [T2]).</t>
         </is>
       </c>
     </row>
@@ -8857,10 +9017,10 @@
         <v>2.7</v>
       </c>
       <c r="J33" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="K33" t="n">
-        <v>1.385</v>
+        <v>1.357</v>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
@@ -8871,7 +9031,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Alex Caruso</t>
+          <t>Ajay Mitchell</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -8881,7 +9041,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -8890,7 +9050,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.643</v>
+        <v>0.575</v>
       </c>
       <c r="F34" t="n">
         <v>5</v>
@@ -8899,27 +9059,27 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>9.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="I34" t="n">
-        <v>5.2</v>
+        <v>3</v>
       </c>
       <c r="J34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K34" t="n">
-        <v>1.746</v>
+        <v>1.364</v>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>Caruso averages 10.8 pts in 4 meetings (+6.3 vs line) — marginally supports the OVER. H2H avg 4.5 pts above season L30; TS% shifts +11.0% in this matchup. Opponent is average defense (#13) at moderate pace (#18). Mixed signals: 5/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 9.7 pts (5.2 pts above line; 64% blended confidence [T3]).</t>
+          <t>Low scoring variance (σ=4.7) — highly predictable output near line — marginally supports the UNDER. Opponent is average defense (#13) at moderate pace (#18). Mixed signals: 5/10 agree (Trend, Context, Defense); counter-signals: Volume, HR L30, HR L10. Projection model targets 9.5 pts (3.0 pts below line; 57% blended confidence [T3]). Risk: 60% over-rate on L30 suggests scoring tendency that could threaten the under.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Ajay Mitchell</t>
+          <t>Jalen Williams</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -8934,40 +9094,40 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.575</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="F35" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>9.5</v>
+        <v>16.3</v>
       </c>
       <c r="I35" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="J35" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="K35" t="n">
-        <v>1.385</v>
+        <v>1.4</v>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>Low scoring variance (σ=4.7) — highly predictable output near line — marginally supports the UNDER. Opponent is average defense (#13) at moderate pace (#18). Mixed signals: 5/10 agree (Trend, Context, Defense); counter-signals: Volume, HR L30, HR L10. Projection model targets 9.5 pts (3.0 pts below line; 57% blended confidence [T3]). Risk: 60% over-rate on L30 suggests scoring tendency that could threaten the under.</t>
+          <t>Williams averages 21.0 pts in 4 meetings (+2.5 vs line) — supports the UNDER. H2H avg 3.7 pts above season L30; TS% shifts -6.3% in this matchup. Opponent is average defense (#13) at moderate pace (#18). 7/10 signals agree — Volume, HR L30, HR L10, Context support the UNDER; Trend, H2H, FG Trend dissent. Projection model targets 16.3 pts (2.2 pts below line; 56% blended confidence [T2]). Risk: high variance (σ=7.4) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Jalen Williams</t>
+          <t>Cason Wallace</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -8977,45 +9137,45 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F36" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>16.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J36" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="K36" t="n">
-        <v>1.385</v>
+        <v>1.435</v>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>Williams averages 21.0 pts in 4 meetings (+2.5 vs line) — supports the UNDER. H2H avg 3.7 pts above season L30; TS% shifts -6.3% in this matchup. Opponent is average defense (#13) at moderate pace (#18). 7/10 signals agree — Volume, HR L30, HR L10, Context support the UNDER; Trend, H2H, FG Trend dissent. Projection model targets 16.3 pts (2.2 pts below line; 56% blended confidence [T2]). Risk: high variance (σ=7.4) makes the outcome difficult to call with confidence.</t>
+          <t>Wallace's L30 of 10.4 pts sits 3.9 above the 6.5 line — marginally supports the OVER. H2H avg 2.6 pts below season L30; Minutes down 3.2 recently (L10=24.1 vs L30=27.3). Opponent is average defense (#13) at moderate pace (#18). Mixed signals: 5/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 8.3 pts (1.8 pts above line; 55% blended confidence [T3]). Risk: minutes trending down (24.1 L10 vs 27.3 L30) — role reduction would suppress counting stats.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cason Wallace</t>
+          <t>Shai Gilgeous-Alexander</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -9034,7 +9194,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.547</v>
       </c>
       <c r="F37" t="n">
         <v>5</v>
@@ -9043,27 +9203,27 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>8.300000000000001</v>
+        <v>32.6</v>
       </c>
       <c r="I37" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J37" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="K37" t="n">
-        <v>1.408</v>
+        <v>1.364</v>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>Wallace's L30 of 10.4 pts sits 3.9 above the 6.5 line — marginally supports the OVER. H2H avg 2.6 pts below season L30; Minutes down 3.2 recently (L10=24.1 vs L30=27.3). Opponent is average defense (#13) at moderate pace (#18). Mixed signals: 5/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 8.3 pts (1.8 pts above line; 55% blended confidence [T3]). Risk: minutes trending down (24.1 L10 vs 27.3 L30) — role reduction would suppress counting stats.</t>
+          <t>Gilgeous-Alexander averages 33.5 pts in 4 meetings (+3.0 vs line) — marginally supports the OVER. H2H avg 2.4 pts above season L30; TS% shifts -3.7% in this matchup. Opponent is average defense (#13) at moderate pace (#18). Mixed signals: 5/10 agree (Volume, Trend, Context); counter-signals: HR L30, HR L10, Defense. Projection model targets 32.6 pts (2.1 pts above line; 54% blended confidence [T3]). Risk: high variance (σ=9.4) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Shai Gilgeous-Alexander</t>
+          <t>Rui Hachimura</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -9073,16 +9233,16 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>LEAN OVER</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T3_LEAN</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.547</v>
+        <v>0.507</v>
       </c>
       <c r="F38" t="n">
         <v>5</v>
@@ -9091,27 +9251,27 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>32.6</v>
+        <v>8.5</v>
       </c>
       <c r="I38" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="K38" t="n">
-        <v>1.385</v>
+        <v>1.465</v>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>Gilgeous-Alexander averages 33.5 pts in 4 meetings (+3.0 vs line) — marginally supports the OVER. H2H avg 2.4 pts above season L30; TS% shifts -3.7% in this matchup. Opponent is average defense (#13) at moderate pace (#18). Mixed signals: 5/10 agree (Volume, Trend, Context); counter-signals: HR L30, HR L10, Defense. Projection model targets 32.6 pts (2.1 pts above line; 54% blended confidence [T3]). Risk: high variance (σ=9.4) makes the outcome difficult to call with confidence.</t>
+          <t>[Low conviction — lean only] Hachimura averages 11.0 pts in 4 meetings (+2.5 vs line) — marginally supports the lean OVER. FG% +6.2% trending (L10 vs L30); Minutes down 2.1 recently (L10=23.7 vs L30=25.8). Opponent is strong defense (#8) at slow pace (#28). Mixed signals: 5/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 8.5 pts (0.0 pts below line; 50% blended confidence [T3_LEAN]).</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Rui Hachimura</t>
+          <t>Luka Dončić</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -9121,7 +9281,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -9130,36 +9290,36 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.549</v>
+        <v>0.712</v>
       </c>
       <c r="F39" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>8.5</v>
+        <v>23.5</v>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J39" t="n">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="K39" t="n">
-        <v>1.417</v>
+        <v>1.357</v>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>Hachimura averages 11.0 pts in 4 meetings (+3.5 vs line) — supports the OVER. FG% +6.2% trending (L10 vs L30); Minutes down 2.1 recently (L10=23.7 vs L30=25.8). Opponent is strong defense (#8) at slow pace (#28). 6/10 signals agree — Volume, HR L30, HR L10, Context support the OVER; Trend, Defense, Pace dissent. Projection model targets 8.5 pts (1.0 pts above line; 54% blended confidence [T3]).</t>
+          <t>Dončić averages 22.0 pts in 4 meetings (-9.5 vs line) — marginally supports the UNDER. H2H avg 12.4 pts below season L30; TS% shifts -5.2% in this matchup. Opponent is strong defense (#8) at slow pace (#28). Mixed signals: 3/10 agree (Defense, H2H, Pace); counter-signals: Volume, HR L30, HR L10. Projection model targets 23.5 pts (8.0 pts below line; 71% blended confidence [T3]). Risk: L3 has surged to 42.0 after a 25-pt outing (7.6 above L30) — momentum could push over the under line.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Luka Dončić</t>
+          <t>LeBron James</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -9178,7 +9338,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.723</v>
+        <v>0.534</v>
       </c>
       <c r="F40" t="n">
         <v>3</v>
@@ -9187,27 +9347,27 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>23.5</v>
+        <v>16.6</v>
       </c>
       <c r="I40" t="n">
-        <v>9</v>
+        <v>0.9</v>
       </c>
       <c r="J40" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="K40" t="n">
-        <v>1.4</v>
+        <v>1.385</v>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>Dončić averages 22.0 pts in 4 meetings (-10.5 vs line) — marginally supports the UNDER. H2H avg 12.4 pts below season L30; TS% shifts -5.2% in this matchup. Opponent is strong defense (#8) at slow pace (#28). Mixed signals: 3/10 agree (Defense, H2H, Pace); counter-signals: Volume, HR L30, HR L10. Projection model targets 23.5 pts (9.0 pts below line; 72% blended confidence [T3]). Risk: L3 has surged to 42.0 after a 25-pt outing (7.6 above L30) — momentum could push over the under line.</t>
+          <t>Recent scoring trending down 2.5 pts (L5 vs L30) — marginally supports the UNDER. TS% shifts -4.2% in this matchup. Opponent is strong defense (#8) at slow pace (#28). Mixed signals: 3/10 agree (Trend, Defense, Pace); counter-signals: Volume, HR L30, HR L10. Projection model targets 16.6 pts (0.9 pts below line; 53% blended confidence [T3]). Risk: 63% over-rate on L30 suggests scoring tendency that could threaten the under.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>LeBron James</t>
+          <t>Austin Reaves</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -9217,45 +9377,45 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>LEAN OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>T3_LEAN</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.534</v>
+        <v>0.62</v>
       </c>
       <c r="F41" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" t="n">
-        <v>16.2</v>
+        <v>14.8</v>
       </c>
       <c r="I41" t="n">
-        <v>0.3</v>
+        <v>4.7</v>
       </c>
       <c r="J41" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="K41" t="n">
-        <v>1.385</v>
+        <v>1.345</v>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>[Low conviction — lean only] James averages 20.2 pts in 4 meetings (+3.7 vs line) — supports the lean OVER. TS% shifts -4.2% in this matchup. Opponent is strong defense (#8) at slow pace (#28). 7/10 signals agree — Volume, HR L30, HR L10, Context support the OVER; Trend, Defense, Pace dissent. Projection model targets 16.2 pts (0.3 pts below line; 53% blended confidence [T3_LEAN]).</t>
+          <t>Reaves averages 16.8 pts in 5 meetings (-2.7 vs line) — supports the UNDER. H2H avg 3.3 pts below season L30; TS% shifts -7.3% in this matchup. Opponent is strong defense (#6) at slow pace (#28). 6/10 signals agree — HR L30, Context, Defense, H2H support the UNDER; Volume, HR L10, Trend dissent. Projection model targets 14.8 pts (4.7 pts below line; 61% blended confidence [T2]).</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Austin Reaves</t>
+          <t>Deandre Ayton</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -9270,23 +9430,23 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.62</v>
+        <v>0.587</v>
       </c>
       <c r="F42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>14.8</v>
+        <v>5.9</v>
       </c>
       <c r="I42" t="n">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="J42" t="n">
         <v>3.05</v>
@@ -9296,7 +9456,7 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>Reaves averages 16.8 pts in 5 meetings (-2.7 vs line) — supports the UNDER. H2H avg 3.3 pts below season L30; TS% shifts -7.3% in this matchup. Opponent is strong defense (#6) at slow pace (#28). 6/10 signals agree — HR L30, Context, Defense, H2H support the UNDER; Volume, HR L10, Trend dissent. Projection model targets 14.8 pts (4.7 pts below line; 61% blended confidence [T2]).</t>
+          <t>Ayton's L30 average of 10.3 pts vs the 9.5 line — marginally supports the UNDER. H2H avg 1.6 pts below season L30; TS% shifts -6.2% in this matchup. Opponent is strong defense (#8) at slow pace (#28). Mixed signals: 5/10 agree (HR L30, Context, Defense); counter-signals: Volume, HR L10, Trend. Projection model targets 5.9 pts (3.6 pts below line; 58% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
@@ -9337,10 +9497,10 @@
         <v>1.9</v>
       </c>
       <c r="J43" t="n">
-        <v>2.7</v>
+        <v>2.14</v>
       </c>
       <c r="K43" t="n">
-        <v>1.435</v>
+        <v>1.645</v>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
@@ -9385,10 +9545,10 @@
         <v>0.9</v>
       </c>
       <c r="J44" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="K44" t="n">
-        <v>1.435</v>
+        <v>1.465</v>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
@@ -9399,7 +9559,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Deandre Ayton</t>
+          <t>Alex Caruso</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -9409,7 +9569,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9418,7 +9578,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.587</v>
+        <v>0.643</v>
       </c>
       <c r="F45" t="n">
         <v>5</v>
@@ -9427,20 +9587,20 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>5.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>3.6</v>
+        <v>5.2</v>
       </c>
       <c r="J45" t="n">
-        <v>3.05</v>
+        <v>1.725</v>
       </c>
       <c r="K45" t="n">
-        <v>1.357</v>
+        <v>2.05</v>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>Ayton's L30 average of 10.3 pts vs the 9.5 line — marginally supports the UNDER. H2H avg 1.6 pts below season L30; TS% shifts -6.2% in this matchup. Opponent is strong defense (#8) at slow pace (#28). Mixed signals: 5/10 agree (HR L30, Context, Defense); counter-signals: Volume, HR L10, Trend. Projection model targets 5.9 pts (3.6 pts below line; 58% blended confidence [T3]).</t>
+          <t>Caruso averages 10.8 pts in 4 meetings (+6.3 vs line) — marginally supports the OVER. H2H avg 4.5 pts above season L30; TS% shifts +11.0% in this matchup. Opponent is average defense (#13) at moderate pace (#18). Mixed signals: 5/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 9.7 pts (5.2 pts above line; 64% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
@@ -9466,29 +9626,29 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.621</v>
+        <v>0.64</v>
       </c>
       <c r="F46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="I46" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="J46" t="n">
-        <v>1.901</v>
+        <v>2.8</v>
       </c>
       <c r="K46" t="n">
-        <v>1.862</v>
+        <v>1.408</v>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>Low scoring variance (σ=4.6) — highly predictable output near line — marginally supports the UNDER. FG% +5.8% trending (L10 vs L30). Opponent is below-average defense (#16) at above-average pace (#10). Mixed signals: 1/10 agree (Context); counter-signals: Volume, HR L30, HR L10. Projection model targets 4.2 pts (4.3 pts below line; 62% blended confidence [T3]).</t>
+          <t>Low scoring variance (σ=4.6) — highly predictable output near line — marginally supports the UNDER. FG% +5.8% trending (L10 vs L30). Opponent is below-average defense (#16) at above-average pace (#10). Mixed signals: 3/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 4.0 pts (5.5 pts below line; 64% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
@@ -9529,10 +9689,10 @@
         <v>3.1</v>
       </c>
       <c r="J47" t="n">
-        <v>1.917</v>
+        <v>3.05</v>
       </c>
       <c r="K47" t="n">
-        <v>1.84</v>
+        <v>1.357</v>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
@@ -9577,10 +9737,10 @@
         <v>1</v>
       </c>
       <c r="J48" t="n">
-        <v>1.917</v>
+        <v>2.9</v>
       </c>
       <c r="K48" t="n">
-        <v>1.84</v>
+        <v>1.385</v>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
@@ -9625,10 +9785,10 @@
         <v>5.4</v>
       </c>
       <c r="J49" t="n">
-        <v>1.862</v>
+        <v>3</v>
       </c>
       <c r="K49" t="n">
-        <v>1.901</v>
+        <v>1.364</v>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
@@ -9673,10 +9833,10 @@
         <v>2.5</v>
       </c>
       <c r="J50" t="n">
-        <v>1.813</v>
+        <v>2.6</v>
       </c>
       <c r="K50" t="n">
-        <v>1.952</v>
+        <v>1.465</v>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
@@ -9721,10 +9881,10 @@
         <v>4.4</v>
       </c>
       <c r="J51" t="n">
-        <v>1.877</v>
+        <v>2.9</v>
       </c>
       <c r="K51" t="n">
-        <v>1.877</v>
+        <v>1.385</v>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
@@ -9769,10 +9929,10 @@
         <v>1.1</v>
       </c>
       <c r="J52" t="n">
-        <v>1.877</v>
+        <v>3.1</v>
       </c>
       <c r="K52" t="n">
-        <v>1.877</v>
+        <v>1.345</v>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
@@ -9802,10 +9962,10 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.668</v>
       </c>
       <c r="F53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -9814,17 +9974,17 @@
         <v>2.8</v>
       </c>
       <c r="I53" t="n">
-        <v>7.7</v>
+        <v>6.7</v>
       </c>
       <c r="J53" t="n">
-        <v>1.813</v>
+        <v>3.05</v>
       </c>
       <c r="K53" t="n">
-        <v>1.952</v>
+        <v>1.357</v>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>Strus's L30 average of 11.0 pts vs the 10.5 line — marginally supports the UNDER. Opponent is below-average defense (#16) at moderate pace (#13). Mixed signals: 2/10 agree (Context, Min Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 2.8 pts (7.7 pts below line; 68% blended confidence [T3]). Risk: L3 has surged to 17.0 after a 10-pt outing (6.0 above L30) — momentum could push over the under line.</t>
+          <t>Strus's L30 average of 11.0 pts vs the 9.5 line — marginally supports the UNDER. Opponent is below-average defense (#16) at moderate pace (#13). Mixed signals: 1/10 agree (Min Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 2.8 pts (6.7 pts below line; 66% blended confidence [T3]). Risk: L3 has surged to 17.0 after a 10-pt outing (6.0 above L30) — momentum could push over the under line.</t>
         </is>
       </c>
     </row>
@@ -9865,10 +10025,10 @@
         <v>0.1</v>
       </c>
       <c r="J54" t="n">
-        <v>1.98</v>
+        <v>3.1</v>
       </c>
       <c r="K54" t="n">
-        <v>1.787</v>
+        <v>1.345</v>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
@@ -9913,10 +10073,10 @@
         <v>4.4</v>
       </c>
       <c r="J55" t="n">
-        <v>1.98</v>
+        <v>2.75</v>
       </c>
       <c r="K55" t="n">
-        <v>1.787</v>
+        <v>1.417</v>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
@@ -9927,17 +10087,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Saddiq Bey</t>
+          <t>De'Anthony Melton</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NOP @ POR</t>
+          <t>CLE @ GSW</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9946,41 +10106,41 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.619</v>
+        <v>0.545</v>
       </c>
       <c r="F56" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>21.4</v>
+        <v>11.6</v>
       </c>
       <c r="I56" t="n">
-        <v>3.9</v>
+        <v>1.9</v>
       </c>
       <c r="J56" t="n">
-        <v>1.893</v>
+        <v>1.877</v>
       </c>
       <c r="K56" t="n">
-        <v>1.826</v>
+        <v>1.877</v>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>Bey's L30 of 20.4 pts sits 2.9 above the 17.5 line — marginally supports the OVER. Opponent is below-average defense (#20) at moderate pace (#20). Mixed signals: 5/10 agree (Volume, HR L30, HR L10); counter-signals: Trend, H2H, Pace. Projection model targets 21.4 pts (3.9 pts above line; 61% blended confidence [T3]).</t>
+          <t>Recent scoring trending down 4.7 pts (L5 vs L30) — marginally supports the UNDER. FG% -5.4% trending (L10 vs L30). Opponent is average defense (#12) at above-average pace (#10). Mixed signals: 4/10 agree (Trend, Context, Defense); counter-signals: Volume, HR L30, HR L10. Projection model targets 11.6 pts (1.9 pts below line; 54% blended confidence [T3]). Risk: high variance (σ=9.6) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Herbert Jones</t>
+          <t>Gui Santos</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NOP @ POR</t>
+          <t>CLE @ GSW</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -9994,36 +10154,36 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.583</v>
+        <v>0.511</v>
       </c>
       <c r="F57" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>6.2</v>
+        <v>13.8</v>
       </c>
       <c r="I57" t="n">
-        <v>3.3</v>
+        <v>0.7</v>
       </c>
       <c r="J57" t="n">
-        <v>2</v>
+        <v>1.917</v>
       </c>
       <c r="K57" t="n">
-        <v>1.746</v>
+        <v>1.84</v>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>Jones averages 7.0 pts in 5 meetings (-2.5 vs line) — marginally supports the UNDER. H2H avg 1.7 pts below season L30; TS% shifts -3.4% in this matchup. Opponent is below-average defense (#20) at moderate pace (#20). Mixed signals: 5/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 6.2 pts (3.3 pts below line; 58% blended confidence [T3]).</t>
+          <t>Santos averages 5.7 pts in 3 meetings (-8.8 vs line) — marginally supports the UNDER. H2H avg 9.1 pts below season L30; TS% shifts +6.4% in this matchup. Opponent is below-average defense (#16) at above-average pace (#10). Mixed signals: 3/10 agree (Context, H2H, FG Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 13.8 pts (0.7 pts below line; 51% blended confidence [T3]). Risk: L3 has surged to 22.3 after a 17-pt outing (7.5 above L30) — momentum could push over the under line.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Scoot Henderson</t>
+          <t>Saddiq Bey</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -10033,7 +10193,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -10042,7 +10202,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.672</v>
+        <v>0.619</v>
       </c>
       <c r="F58" t="n">
         <v>5</v>
@@ -10051,27 +10211,27 @@
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>11.7</v>
+        <v>21.4</v>
       </c>
       <c r="I58" t="n">
-        <v>5.8</v>
+        <v>3.9</v>
       </c>
       <c r="J58" t="n">
-        <v>2.01</v>
+        <v>3.05</v>
       </c>
       <c r="K58" t="n">
-        <v>1.746</v>
+        <v>1.357</v>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>Henderson averages 10.5 pts in 4 meetings (-7.0 vs line) — marginally supports the UNDER. H2H avg 3.0 pts below season L30; TS% shifts -6.0% in this matchup. Opponent is weak defense (#23) at above-average pace (#7). Mixed signals: 5/10 agree (Volume, HR L30, HR L10); counter-signals: Trend, Defense, Pace. Projection model targets 11.7 pts (5.8 pts below line; 67% blended confidence [T3]).</t>
+          <t>Bey's L30 of 20.4 pts sits 2.9 above the 17.5 line — marginally supports the OVER. Opponent is below-average defense (#20) at moderate pace (#20). Mixed signals: 5/10 agree (Volume, HR L30, HR L10); counter-signals: Trend, H2H, Pace. Projection model targets 21.4 pts (3.9 pts above line; 61% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Deni Avdija</t>
+          <t>Herbert Jones</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -10086,40 +10246,40 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>T1_PREMIUM</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.7</v>
+        <v>0.583</v>
       </c>
       <c r="F59" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>20.4</v>
+        <v>6.2</v>
       </c>
       <c r="I59" t="n">
-        <v>6.1</v>
+        <v>3.3</v>
       </c>
       <c r="J59" t="n">
-        <v>1.847</v>
+        <v>2.65</v>
       </c>
       <c r="K59" t="n">
-        <v>1.885</v>
+        <v>1.455</v>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>Avdija averages 18.3 pts in 7 meetings (-8.2 vs line) — supports the UNDER. H2H avg 3.8 pts below season L30. Opponent is below-average defense (#22) at above-average pace (#7). 7/10 signals agree — Volume, HR L30, HR L10, Trend support the UNDER; Defense, Pace, Min Trend dissent. Projection model targets 20.4 pts (6.1 pts below line; 69% blended confidence [T1_PREMIUM]).</t>
+          <t>Jones averages 7.0 pts in 5 meetings (-2.5 vs line) — marginally supports the UNDER. H2H avg 1.7 pts below season L30; TS% shifts -3.4% in this matchup. Opponent is below-average defense (#20) at moderate pace (#20). Mixed signals: 5/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 6.2 pts (3.3 pts below line; 58% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Yves Missi</t>
+          <t>Scoot Henderson</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -10138,7 +10298,7 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.579</v>
+        <v>0.646</v>
       </c>
       <c r="F60" t="n">
         <v>5</v>
@@ -10147,27 +10307,27 @@
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>2.8</v>
+        <v>11.5</v>
       </c>
       <c r="I60" t="n">
-        <v>2.7</v>
+        <v>5</v>
       </c>
       <c r="J60" t="n">
-        <v>1.758</v>
+        <v>2.65</v>
       </c>
       <c r="K60" t="n">
-        <v>2</v>
+        <v>1.455</v>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>Low scoring variance (σ=2.8) — highly predictable output near line — marginally supports the UNDER. H2H avg 1.7 pts below season L30; FG% -5.2% trending (L10 vs L30). Opponent is weak defense (#28) at moderate pace (#20). Mixed signals: 5/10 agree (Trend, Context, H2H); counter-signals: Volume, HR L30, HR L10. Projection model targets 2.8 pts (2.7 pts below line; 57% blended confidence [T3]).</t>
+          <t>Henderson averages 10.5 pts in 4 meetings (-6.0 vs line) — marginally supports the UNDER. H2H avg 3.0 pts below season L30; TS% shifts -6.0% in this matchup. Opponent is weak defense (#23) at above-average pace (#7). Mixed signals: 5/10 agree (Volume, HR L30, HR L10); counter-signals: Trend, Defense, Pace. Projection model targets 11.5 pts (5.0 pts below line; 64% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Donovan Clingan</t>
+          <t>Deni Avdija</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -10182,40 +10342,40 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1_PREMIUM</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.58</v>
+        <v>0.7</v>
       </c>
       <c r="F61" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H61" t="n">
-        <v>10.2</v>
+        <v>20.4</v>
       </c>
       <c r="I61" t="n">
-        <v>3.3</v>
+        <v>6.1</v>
       </c>
       <c r="J61" t="n">
-        <v>1.855</v>
+        <v>3</v>
       </c>
       <c r="K61" t="n">
-        <v>1.87</v>
+        <v>1.364</v>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>Clingan averages 7.4 pts in 5 meetings (-6.1 vs line) — supports the UNDER. H2H avg 5.8 pts below season L30. Opponent is weak defense (#25) at above-average pace (#7). 6/10 signals agree — Volume, Trend, Context, H2H support the UNDER; HR L30, HR L10, Defense dissent. Projection model targets 10.2 pts (3.3 pts below line; 58% blended confidence [T2]). Risk: high variance (σ=7.7) makes the outcome difficult to call with confidence.</t>
+          <t>Avdija averages 18.3 pts in 7 meetings (-8.2 vs line) — supports the UNDER. H2H avg 3.8 pts below season L30. Opponent is below-average defense (#22) at above-average pace (#7). 7/10 signals agree — Volume, HR L30, HR L10, Trend support the UNDER; Defense, Pace, Min Trend dissent. Projection model targets 20.4 pts (6.1 pts below line; 69% blended confidence [T1_PREMIUM]).</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Derik Queen</t>
+          <t>Yves Missi</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -10225,45 +10385,45 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.727</v>
+        <v>0.579</v>
       </c>
       <c r="F62" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>17.2</v>
+        <v>2.8</v>
       </c>
       <c r="I62" t="n">
-        <v>8.699999999999999</v>
+        <v>2.7</v>
       </c>
       <c r="J62" t="n">
-        <v>1.833</v>
+        <v>3</v>
       </c>
       <c r="K62" t="n">
-        <v>1.893</v>
+        <v>1.364</v>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>Low scoring variance (σ=4.8) — highly predictable output near line — supports the OVER. FG% -3.8% trending (L10 vs L30); Minutes down 3.9 recently (L10=18.2 vs L30=22.1). Opponent is weak defense (#28) at moderate pace (#20). 6/10 signals agree — Volume, HR L30, HR L10, Trend support the OVER; H2H, Pace, FG Trend dissent. Projection model targets 17.2 pts (8.7 pts above line; 72% blended confidence [T2]). Risk: minutes trending down (18.2 L10 vs 22.1 L30) — role reduction would suppress counting stats.</t>
+          <t>Low scoring variance (σ=2.8) — highly predictable output near line — marginally supports the UNDER. H2H avg 1.7 pts below season L30; FG% -5.2% trending (L10 vs L30). Opponent is weak defense (#28) at moderate pace (#20). Mixed signals: 5/10 agree (Trend, Context, H2H); counter-signals: Volume, HR L30, HR L10. Projection model targets 2.8 pts (2.7 pts below line; 57% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Jrue Holiday</t>
+          <t>Donovan Clingan</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -10282,36 +10442,36 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.668</v>
+        <v>0.58</v>
       </c>
       <c r="F63" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G63" t="n">
         <v>1</v>
       </c>
       <c r="H63" t="n">
-        <v>11.3</v>
+        <v>10.2</v>
       </c>
       <c r="I63" t="n">
-        <v>6.2</v>
+        <v>3.3</v>
       </c>
       <c r="J63" t="n">
-        <v>1.952</v>
+        <v>2.9</v>
       </c>
       <c r="K63" t="n">
-        <v>1.8</v>
+        <v>1.385</v>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>Holiday averages 9.7 pts in 3 meetings (-7.8 vs line) — supports the UNDER. H2H avg 6.9 pts below season L30; FG% -5.0% trending (L10 vs L30). Opponent is weak defense (#23) at above-average pace (#7). 7/10 signals agree — Volume, HR L30, HR L10, Context support the UNDER; Trend, Defense, Pace dissent. Projection model targets 11.3 pts (6.2 pts below line; 66% blended confidence [T2]). Risk: L3 has surged to 21.3 after a 6-pt outing (4.7 above L30) — momentum could push over the under line.</t>
+          <t>Clingan averages 7.4 pts in 5 meetings (-6.1 vs line) — supports the UNDER. H2H avg 5.8 pts below season L30. Opponent is weak defense (#25) at above-average pace (#7). 6/10 signals agree — Volume, Trend, Context, H2H support the UNDER; HR L30, HR L10, Defense dissent. Projection model targets 10.2 pts (3.3 pts below line; 58% blended confidence [T2]). Risk: high variance (σ=7.7) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Robert Williams III</t>
+          <t>Derik Queen</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -10321,45 +10481,45 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>LEAN OVER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>T3_LEAN</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.532</v>
+        <v>0.727</v>
       </c>
       <c r="F64" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H64" t="n">
-        <v>5.4</v>
+        <v>17.2</v>
       </c>
       <c r="I64" t="n">
-        <v>0.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J64" t="n">
-        <v>1.8</v>
+        <v>2.75</v>
       </c>
       <c r="K64" t="n">
-        <v>1.943</v>
+        <v>1.417</v>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>[Low conviction — lean only] Low scoring variance (σ=4.4) — highly predictable output near line — supports the lean OVER. H2H avg 2.7 pts below season L30; TS% shifts -7.0% in this matchup. Opponent is weak defense (#25) at above-average pace (#7). 7/10 signals agree — Volume, HR L30, HR L10, Context support the OVER; Trend, H2H, FG Trend dissent. Projection model targets 5.4 pts (0.1 pts below line; 53% blended confidence [T3_LEAN]).</t>
+          <t>Low scoring variance (σ=4.8) — highly predictable output near line — supports the OVER. FG% -3.8% trending (L10 vs L30); Minutes down 3.9 recently (L10=18.2 vs L30=22.1). Opponent is weak defense (#28) at moderate pace (#20). 6/10 signals agree — Volume, HR L30, HR L10, Trend support the OVER; H2H, Pace, FG Trend dissent. Projection model targets 17.2 pts (8.7 pts above line; 72% blended confidence [T2]). Risk: minutes trending down (18.2 L10 vs 22.1 L30) — role reduction would suppress counting stats.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Trey Murphy III</t>
+          <t>Jrue Holiday</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -10369,7 +10529,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10378,36 +10538,36 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.668</v>
       </c>
       <c r="F65" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G65" t="n">
         <v>1</v>
       </c>
       <c r="H65" t="n">
-        <v>22.2</v>
+        <v>11.3</v>
       </c>
       <c r="I65" t="n">
-        <v>1.7</v>
+        <v>6.2</v>
       </c>
       <c r="J65" t="n">
-        <v>1.787</v>
+        <v>1.87</v>
       </c>
       <c r="K65" t="n">
-        <v>1.943</v>
+        <v>1.87</v>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending down 4.2 pts (L5 vs L30) — supports the OVER. Opponent is below-average defense (#20) at moderate pace (#20). 6/10 signals agree — Volume, HR L30, HR L10, Context support the OVER; Trend, H2H, Pace dissent. Projection model targets 22.2 pts (1.7 pts above line; 56% blended confidence [T2]). Risk: L3 has dropped to 17.7 (5.1 below L30) — deepening slump makes the over vulnerable.</t>
+          <t>Holiday averages 9.7 pts in 3 meetings (-7.8 vs line) — supports the UNDER. H2H avg 6.9 pts below season L30; FG% -5.0% trending (L10 vs L30). Opponent is weak defense (#23) at above-average pace (#7). 7/10 signals agree — Volume, HR L30, HR L10, Context support the UNDER; Trend, Defense, Pace dissent. Projection model targets 11.3 pts (6.2 pts below line; 66% blended confidence [T2]). Risk: L3 has surged to 21.3 after a 6-pt outing (4.7 above L30) — momentum could push over the under line.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Zion Williamson</t>
+          <t>Robert Williams III</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -10426,36 +10586,36 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.574</v>
+        <v>0.53</v>
       </c>
       <c r="F66" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>18.2</v>
+        <v>5.4</v>
       </c>
       <c r="I66" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J66" t="n">
-        <v>1.877</v>
+        <v>2.9</v>
       </c>
       <c r="K66" t="n">
-        <v>1.855</v>
+        <v>1.385</v>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>Low scoring variance (σ=4.1) — highly predictable output near line — marginally supports the UNDER. H2H avg 1.6 pts above season L30; TS% shifts -14.6% in this matchup. Opponent is below-average defense (#20) at moderate pace (#20). Mixed signals: 3/10 agree (Volume, Context, Pace); counter-signals: HR L30, HR L10, Trend. Projection model targets 18.2 pts (2.3 pts below line; 57% blended confidence [T3]).</t>
+          <t>Low scoring variance (σ=4.4) — highly predictable output near line — supports the UNDER. H2H avg 2.7 pts below season L30; TS% shifts -7.0% in this matchup. Opponent is weak defense (#25) at above-average pace (#7). 6/10 signals agree — HR L30, HR L10, Trend, Context support the UNDER; Volume, Defense, Pace dissent. Projection model targets 5.4 pts (1.1 pts below line; 53% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Dejounte Murray</t>
+          <t>Trey Murphy III</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -10470,40 +10630,40 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.518</v>
+        <v>0.592</v>
       </c>
       <c r="F67" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H67" t="n">
-        <v>17.7</v>
+        <v>22.2</v>
       </c>
       <c r="I67" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="J67" t="n">
-        <v>1.87</v>
+        <v>2.9</v>
       </c>
       <c r="K67" t="n">
-        <v>1.87</v>
+        <v>1.385</v>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending down 4.6 pts (L5 vs L30) — marginally supports the OVER. FG% +3.9% trending (L10 vs L30). Opponent is below-average defense (#20) at moderate pace (#20). Mixed signals: 5/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, H2H. Projection model targets 17.7 pts (1.2 pts above line; 51% blended confidence [T3]). Risk: L3 has dropped to 12.7 (5.3 below L30) — deepening slump makes the over vulnerable.</t>
+          <t>III's L30 of 22.8 pts sits 3.3 above the 19.5 line — supports the OVER. Opponent is below-average defense (#20) at moderate pace (#20). 6/10 signals agree — Volume, HR L30, HR L10, Context support the OVER; Trend, H2H, Pace dissent. Projection model targets 22.2 pts (2.7 pts above line; 59% blended confidence [T2]). Risk: L3 has dropped to 17.7 (5.1 below L30) — deepening slump makes the over vulnerable.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Toumani Camara</t>
+          <t>Zion Williamson</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -10522,36 +10682,36 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.526</v>
+        <v>0.574</v>
       </c>
       <c r="F68" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>12.8</v>
+        <v>18.2</v>
       </c>
       <c r="I68" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J68" t="n">
-        <v>1.758</v>
+        <v>2.9</v>
       </c>
       <c r="K68" t="n">
-        <v>1.98</v>
+        <v>1.385</v>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending up 5.5 pts (L5 vs L30) — marginally supports the UNDER. TS% shifts +7.1% in this matchup; FG% +8.8% trending (L10 vs L30). Opponent is below-average defense (#22) at above-average pace (#7). Mixed signals: 5/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 12.8 pts (0.7 pts below line; 52% blended confidence [T3]). Risk: high variance (σ=8.8) makes the outcome difficult to call with confidence.</t>
+          <t>Low scoring variance (σ=4.1) — highly predictable output near line — marginally supports the UNDER. H2H avg 1.6 pts above season L30; TS% shifts -14.6% in this matchup. Opponent is below-average defense (#20) at moderate pace (#20). Mixed signals: 3/10 agree (Volume, Context, Pace); counter-signals: HR L30, HR L10, Trend. Projection model targets 18.2 pts (2.3 pts below line; 57% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Matisse Thybulle</t>
+          <t>Dejounte Murray</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -10561,7 +10721,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -10570,7 +10730,7 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.548</v>
+        <v>0.518</v>
       </c>
       <c r="F69" t="n">
         <v>5</v>
@@ -10579,80 +10739,80 @@
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>5.7</v>
+        <v>17.7</v>
       </c>
       <c r="I69" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J69" t="n">
-        <v>2.02</v>
+        <v>3.05</v>
       </c>
       <c r="K69" t="n">
-        <v>1.735</v>
+        <v>1.357</v>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>Low scoring variance (σ=3.5) — highly predictable output near line — marginally supports the UNDER. Opponent is weak defense (#23) at above-average pace (#7). Mixed signals: 5/10 agree (Volume, HR L30, HR L10); counter-signals: Trend, Defense, H2H. Projection model targets 5.7 pts (1.8 pts below line; 54% blended confidence [T3]).</t>
+          <t>Recent scoring trending down 4.6 pts (L5 vs L30) — marginally supports the OVER. FG% +3.9% trending (L10 vs L30). Opponent is below-average defense (#20) at moderate pace (#20). Mixed signals: 5/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, H2H. Projection model targets 17.7 pts (1.2 pts above line; 51% blended confidence [T3]). Risk: L3 has dropped to 12.7 (5.3 below L30) — deepening slump makes the over vulnerable.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Keldon Johnson</t>
+          <t>Toumani Camara</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SAS @ LAC</t>
+          <t>NOP @ POR</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>LEAN OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>T3_LEAN</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.516</v>
+        <v>0.526</v>
       </c>
       <c r="F70" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>11.4</v>
+        <v>12.8</v>
       </c>
       <c r="I70" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="J70" t="n">
-        <v>1.98</v>
+        <v>2.8</v>
       </c>
       <c r="K70" t="n">
-        <v>1.758</v>
+        <v>1.408</v>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>[Low conviction — lean only] Recent scoring trending up 3.3 pts (L5 vs L30) — supports the lean OVER. FG% +5.4% trending (L10 vs L30). Opponent is elite defense (#4) at slow pace (#26). 7/10 signals agree — Volume, HR L30, HR L10, Trend support the OVER; Defense, H2H, Pace dissent. Projection model targets 11.4 pts (0.1 pts below line; 51% blended confidence [T3_LEAN]).</t>
+          <t>Recent scoring trending up 5.5 pts (L5 vs L30) — marginally supports the UNDER. TS% shifts +7.1% in this matchup; FG% +8.8% trending (L10 vs L30). Opponent is below-average defense (#22) at above-average pace (#7). Mixed signals: 5/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 12.8 pts (0.7 pts below line; 52% blended confidence [T3]). Risk: high variance (σ=8.8) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Devin Vassell</t>
+          <t>Matisse Thybulle</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SAS @ LAC</t>
+          <t>NOP @ POR</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -10666,7 +10826,7 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.577</v>
+        <v>0.521</v>
       </c>
       <c r="F71" t="n">
         <v>5</v>
@@ -10675,27 +10835,27 @@
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>9.4</v>
+        <v>5.7</v>
       </c>
       <c r="I71" t="n">
-        <v>3.1</v>
+        <v>0.8</v>
       </c>
       <c r="J71" t="n">
-        <v>3</v>
+        <v>2.12</v>
       </c>
       <c r="K71" t="n">
-        <v>1.364</v>
+        <v>1.658</v>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>Vassell's L30 average of 12.7 pts vs the 12.5 line — marginally supports the UNDER. TS% shifts -7.8% in this matchup. Opponent is below-average defense (#20) at slow pace (#26). Mixed signals: 5/10 agree (HR L30, Trend, Context); counter-signals: Volume, HR L10, Defense. Projection model targets 9.4 pts (3.1 pts below line; 57% blended confidence [T3]).</t>
+          <t>Low scoring variance (σ=3.5) — highly predictable output near line — marginally supports the UNDER. Opponent is weak defense (#23) at above-average pace (#7). Mixed signals: 5/10 agree (Volume, HR L30, HR L10); counter-signals: Trend, Defense, H2H. Projection model targets 5.7 pts (0.8 pts below line; 52% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Dylan Harper</t>
+          <t>Keldon Johnson</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -10705,45 +10865,45 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>LEAN OVER</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T3_LEAN</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.622</v>
+        <v>0.516</v>
       </c>
       <c r="F72" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>7.5</v>
+        <v>11.4</v>
       </c>
       <c r="I72" t="n">
-        <v>4</v>
+        <v>0.1</v>
       </c>
       <c r="J72" t="n">
-        <v>3.1</v>
+        <v>1.98</v>
       </c>
       <c r="K72" t="n">
-        <v>1.345</v>
+        <v>1.787</v>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>Harper's L30 average of 12.6 pts vs the 11.5 line — marginally supports the UNDER. Opponent is below-average defense (#20) at slow pace (#26). Mixed signals: 1/10 agree (Pace); counter-signals: Volume, HR L30, HR L10. Projection model targets 7.5 pts (4.0 pts below line; 62% blended confidence [T3]). Risk: 60% over-rate on L30 suggests scoring tendency that could threaten the under.</t>
+          <t>[Low conviction — lean only] Recent scoring trending up 3.3 pts (L5 vs L30) — supports the lean OVER. FG% +5.4% trending (L10 vs L30). Opponent is elite defense (#4) at slow pace (#26). 7/10 signals agree — Volume, HR L30, HR L10, Trend support the OVER; Defense, H2H, Pace dissent. Projection model targets 11.4 pts (0.1 pts below line; 51% blended confidence [T3_LEAN]).</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>De'Aaron Fox</t>
+          <t>Devin Vassell</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -10753,7 +10913,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10762,19 +10922,19 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.551</v>
+        <v>0.577</v>
       </c>
       <c r="F73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>17.2</v>
+        <v>9.4</v>
       </c>
       <c r="I73" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="J73" t="n">
         <v>3.05</v>
@@ -10784,14 +10944,14 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>Fox averages 24.2 pts in 4 meetings (+8.7 vs line) — marginally supports the OVER. H2H avg 8.1 pts above season L30; TS% shifts +4.0% in this matchup. Opponent is below-average defense (#20) at slow pace (#26). Mixed signals: 4/10 agree (Volume, Context, Defense); counter-signals: HR L30, HR L10, Trend. Projection model targets 17.2 pts (1.7 pts above line; 55% blended confidence [T3]). Risk: L3 has dropped to 10.0 (6.1 below L30) — deepening slump makes the over vulnerable.</t>
+          <t>Vassell's L30 average of 12.7 pts vs the 12.5 line — marginally supports the UNDER. TS% shifts -7.8% in this matchup. Opponent is below-average defense (#20) at slow pace (#26). Mixed signals: 5/10 agree (HR L30, Trend, Context); counter-signals: Volume, HR L10, Defense. Projection model targets 9.4 pts (3.1 pts below line; 57% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Stephon Castle</t>
+          <t>Dylan Harper</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -10801,7 +10961,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10810,36 +10970,36 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.526</v>
+        <v>0.622</v>
       </c>
       <c r="F74" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>15.8</v>
+        <v>7.5</v>
       </c>
       <c r="I74" t="n">
-        <v>0.3</v>
+        <v>4</v>
       </c>
       <c r="J74" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="K74" t="n">
-        <v>1.4</v>
+        <v>1.345</v>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending up 2.3 pts (L5 vs L30) — supports the OVER. TS% shifts +4.6% in this matchup. Opponent is below-average defense (#20) at slow pace (#26). 8/10 signals agree — Volume, HR L30, HR L10, Trend support the OVER; Pace, FG Trend dissent. Projection model targets 15.8 pts (0.3 pts above line; 52% blended confidence [T3]).</t>
+          <t>Harper's L30 average of 12.6 pts vs the 11.5 line — marginally supports the UNDER. Opponent is below-average defense (#20) at slow pace (#26). Mixed signals: 1/10 agree (Pace); counter-signals: Volume, HR L30, HR L10. Projection model targets 7.5 pts (4.0 pts below line; 62% blended confidence [T3]). Risk: 60% over-rate on L30 suggests scoring tendency that could threaten the under.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Harrison Barnes</t>
+          <t>De'Aaron Fox</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -10858,36 +11018,36 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.579</v>
+        <v>0.551</v>
       </c>
       <c r="F75" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>10.4</v>
+        <v>17.2</v>
       </c>
       <c r="I75" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="J75" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="K75" t="n">
-        <v>1.408</v>
+        <v>1.357</v>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>Barnes averages 12.4 pts in 5 meetings (+4.9 vs line) — marginally supports the OVER. H2H avg 3.7 pts above season L30; TS% shifts +13.8% in this matchup. Opponent is elite defense (#4) at slow pace (#26). Mixed signals: 5/10 agree (Volume, HR L30, HR L10); counter-signals: Trend, Defense, Pace. Projection model targets 10.4 pts (2.9 pts above line; 57% blended confidence [T3]).</t>
+          <t>Fox averages 24.2 pts in 4 meetings (+8.7 vs line) — marginally supports the OVER. H2H avg 8.1 pts above season L30; TS% shifts +4.0% in this matchup. Opponent is below-average defense (#20) at slow pace (#26). Mixed signals: 4/10 agree (Volume, Context, Defense); counter-signals: HR L30, HR L10, Trend. Projection model targets 17.2 pts (1.7 pts above line; 55% blended confidence [T3]). Risk: L3 has dropped to 10.0 (6.1 below L30) — deepening slump makes the over vulnerable.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Bennedict Mathurin</t>
+          <t>Stephon Castle</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -10897,7 +11057,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10906,36 +11066,36 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.526</v>
       </c>
       <c r="F76" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>14.5</v>
+        <v>15.8</v>
       </c>
       <c r="I76" t="n">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="J76" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K76" t="n">
-        <v>1.364</v>
+        <v>1.345</v>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>Mathurin averages 12.6 pts in 5 meetings (-3.9 vs line) — marginally supports the UNDER. H2H avg 5.7 pts below season L30; TS% shifts -4.3% in this matchup. Opponent is strong defense (#8) at above-average pace (#9). Mixed signals: 3/10 agree (Trend, Defense, H2H); counter-signals: Volume, HR L30, HR L10. Projection model targets 14.5 pts (2.0 pts below line; 55% blended confidence [T3]). Risk: high variance (σ=7.2) makes the outcome difficult to call with confidence.</t>
+          <t>Recent scoring trending up 2.3 pts (L5 vs L30) — supports the OVER. TS% shifts +4.6% in this matchup. Opponent is below-average defense (#20) at slow pace (#26). 8/10 signals agree — Volume, HR L30, HR L10, Trend support the OVER; Pace, FG Trend dissent. Projection model targets 15.8 pts (0.3 pts above line; 52% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>John Collins</t>
+          <t>Harrison Barnes</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -10954,7 +11114,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.521</v>
+        <v>0.579</v>
       </c>
       <c r="F77" t="n">
         <v>5</v>
@@ -10963,27 +11123,27 @@
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>11.9</v>
+        <v>10.4</v>
       </c>
       <c r="I77" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="J77" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="K77" t="n">
-        <v>1.4</v>
+        <v>1.417</v>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>Collins averages 15.6 pts in 5 meetings (+4.1 vs line) — marginally supports the OVER. TS% shifts -3.6% in this matchup; FG% -9.9% trending (L10 vs L30). Opponent is strong defense (#8) at above-average pace (#9). Mixed signals: 5/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 11.9 pts (0.4 pts above line; 52% blended confidence [T3]).</t>
+          <t>Barnes averages 12.4 pts in 5 meetings (+4.9 vs line) — marginally supports the OVER. H2H avg 3.7 pts above season L30; TS% shifts +13.8% in this matchup. Opponent is elite defense (#4) at slow pace (#26). Mixed signals: 5/10 agree (Volume, HR L30, HR L10); counter-signals: Trend, Defense, Pace. Projection model targets 10.4 pts (2.9 pts above line; 57% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Julian Champagnie</t>
+          <t>Bennedict Mathurin</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -10993,7 +11153,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -11002,36 +11162,36 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.523</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="F78" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>10.1</v>
+        <v>14.5</v>
       </c>
       <c r="I78" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J78" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="K78" t="n">
-        <v>1.435</v>
+        <v>1.357</v>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>Low scoring variance (σ=4.1) — highly predictable output near line — supports the OVER. Opponent is elite defense (#4) at slow pace (#26). 8/10 signals agree — Volume, HR L30, HR L10, Trend support the OVER; Defense, Pace dissent. Projection model targets 10.1 pts (0.6 pts above line; 52% blended confidence [T3]).</t>
+          <t>Mathurin averages 12.6 pts in 5 meetings (-3.9 vs line) — marginally supports the UNDER. H2H avg 5.7 pts below season L30; TS% shifts -4.3% in this matchup. Opponent is strong defense (#8) at above-average pace (#9). Mixed signals: 3/10 agree (Trend, Defense, H2H); counter-signals: Volume, HR L30, HR L10. Projection model targets 14.5 pts (2.0 pts below line; 55% blended confidence [T3]). Risk: high variance (σ=7.2) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Brook Lopez</t>
+          <t>John Collins</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -11046,40 +11206,40 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.609</v>
+        <v>0.521</v>
       </c>
       <c r="F79" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>14.1</v>
+        <v>11.9</v>
       </c>
       <c r="I79" t="n">
-        <v>3.6</v>
+        <v>0.4</v>
       </c>
       <c r="J79" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="K79" t="n">
-        <v>1.345</v>
+        <v>1.417</v>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending up 4.5 pts (L5 vs L30) — supports the OVER. H2H avg 3.7 pts above season L30; TS% shifts +4.3% in this matchup. Opponent is below-average defense (#18) at above-average pace (#9). 7/10 signals agree — Trend, Context, Defense, H2H support the OVER; Volume, HR L30, HR L10 dissent. Projection model targets 14.1 pts (3.6 pts above line; 60% blended confidence [T2]).</t>
+          <t>Collins averages 15.6 pts in 5 meetings (+4.1 vs line) — marginally supports the OVER. TS% shifts -3.6% in this matchup; FG% -9.9% trending (L10 vs L30). Opponent is strong defense (#8) at above-average pace (#9). Mixed signals: 5/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 11.9 pts (0.4 pts above line; 52% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Darius Garland</t>
+          <t>Julian Champagnie</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -11089,7 +11249,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -11098,36 +11258,36 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.572</v>
+        <v>0.523</v>
       </c>
       <c r="F80" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>16.5</v>
+        <v>10.1</v>
       </c>
       <c r="I80" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J80" t="n">
-        <v>3.1</v>
+        <v>2.35</v>
       </c>
       <c r="K80" t="n">
-        <v>1.345</v>
+        <v>1.556</v>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>Garland averages 17.2 pts in 4 meetings (-2.3 vs line) — marginally supports the UNDER. H2H avg 3.5 pts below season L30; TS% shifts -11.0% in this matchup. Opponent is strong defense (#8) at above-average pace (#9). Mixed signals: 3/10 agree (Defense, H2H, Min Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 16.5 pts (3.0 pts below line; 57% blended confidence [T3]). Risk: high variance (σ=8.3) makes the outcome difficult to call with confidence.</t>
+          <t>Low scoring variance (σ=4.1) — highly predictable output near line — supports the OVER. Opponent is elite defense (#4) at slow pace (#26). 8/10 signals agree — Volume, HR L30, HR L10, Trend support the OVER; Defense, Pace dissent. Projection model targets 10.1 pts (0.6 pts above line; 52% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Victor Wembanyama</t>
+          <t>Brook Lopez</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -11142,40 +11302,40 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.514</v>
+        <v>0.609</v>
       </c>
       <c r="F81" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H81" t="n">
-        <v>25.4</v>
+        <v>14.1</v>
       </c>
       <c r="I81" t="n">
-        <v>0.9</v>
+        <v>3.6</v>
       </c>
       <c r="J81" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="K81" t="n">
-        <v>1.408</v>
+        <v>1.345</v>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending up 5.0 pts (L5 vs L30) — marginally supports the OVER. TS% shifts -3.1% in this matchup. Opponent is elite defense (#4) at slow pace (#26). Mixed signals: 5/10 agree (Volume, HR L30, Trend); counter-signals: HR L10, Defense, H2H. Projection model targets 25.4 pts (0.9 pts above line; 51% blended confidence [T3]). Risk: high variance (σ=8.9) makes the outcome difficult to call with confidence.</t>
+          <t>Recent scoring trending up 4.5 pts (L5 vs L30) — supports the OVER. H2H avg 3.7 pts above season L30; TS% shifts +4.3% in this matchup. Opponent is below-average defense (#18) at above-average pace (#9). 7/10 signals agree — Trend, Context, Defense, H2H support the OVER; Volume, HR L30, HR L10 dissent. Projection model targets 14.1 pts (3.6 pts above line; 60% blended confidence [T2]).</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Kris Dunn</t>
+          <t>Darius Garland</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -11185,7 +11345,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11194,36 +11354,36 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.542</v>
+        <v>0.572</v>
       </c>
       <c r="F82" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>5.9</v>
+        <v>16.5</v>
       </c>
       <c r="I82" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="J82" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="K82" t="n">
-        <v>1.385</v>
+        <v>1.357</v>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>Dunn averages 7.4 pts in 5 meetings (+2.9 vs line) — supports the OVER. FG% -6.7% trending (L10 vs L30). Opponent is strong defense (#8) at above-average pace (#9). 6/10 signals agree — Volume, HR L30, HR L10, Context support the OVER; Trend, Defense, FG Trend dissent. Projection model targets 5.9 pts (1.4 pts above line; 54% blended confidence [T3]).</t>
+          <t>Garland averages 17.2 pts in 4 meetings (-2.3 vs line) — marginally supports the UNDER. H2H avg 3.5 pts below season L30; TS% shifts -11.0% in this matchup. Opponent is strong defense (#8) at above-average pace (#9). Mixed signals: 3/10 agree (Defense, H2H, Min Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 16.5 pts (3.0 pts below line; 57% blended confidence [T3]). Risk: high variance (σ=8.3) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Kawhi Leonard</t>
+          <t>Victor Wembanyama</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -11233,7 +11393,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11242,36 +11402,36 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.539</v>
+        <v>0.501</v>
       </c>
       <c r="F83" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>29.1</v>
+        <v>25.2</v>
       </c>
       <c r="I83" t="n">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="J83" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="K83" t="n">
-        <v>1.364</v>
+        <v>1.385</v>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending down 2.7 pts (L5 vs L30) — supports the OVER. Opponent is strong defense (#8) at above-average pace (#9). 6/10 signals agree — Volume, HR L30, HR L10, Context support the OVER; Trend, Defense, H2H dissent. Projection model targets 29.1 pts (1.6 pts above line; 53% blended confidence [T3]). Risk: L3 has dropped to 23.7 (4.2 below L30) — deepening slump makes the over vulnerable.</t>
+          <t>Recent scoring trending up 5.0 pts (L5 vs L30) — supports the UNDER. TS% shifts -3.1% in this matchup. Opponent is elite defense (#4) at slow pace (#26). 7/10 signals agree — Volume, HR L30, Context, Defense support the UNDER; HR L10, Trend, FG Trend dissent. Projection model targets 25.2 pts (0.3 pts below line; 50% blended confidence [T3]). Risk: L3 has surged to 35.0 after a 28-pt outing (10.0 above L30) — momentum could push over the under line.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Derrick Jones Jr.</t>
+          <t>Kawhi Leonard</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -11290,29 +11450,125 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.529</v>
+        <v>0.539</v>
       </c>
       <c r="F84" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
       </c>
       <c r="H84" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="I84" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J84" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="K84" t="n">
+        <v>1.385</v>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>Recent scoring trending down 2.7 pts (L5 vs L30) — supports the OVER. Opponent is strong defense (#8) at above-average pace (#9). 6/10 signals agree — Volume, HR L30, HR L10, Context support the OVER; Trend, Defense, H2H dissent. Projection model targets 29.1 pts (1.6 pts above line; 53% blended confidence [T3]). Risk: L3 has dropped to 23.7 (4.2 below L30) — deepening slump makes the over vulnerable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Derrick Jones Jr.</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>SAS @ LAC</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>LEAN UNDER</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>T3_LEAN</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="F85" t="n">
+        <v>5</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" t="n">
         <v>9.6</v>
       </c>
-      <c r="I84" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J84" t="n">
-        <v>3</v>
-      </c>
-      <c r="K84" t="n">
-        <v>1.364</v>
-      </c>
-      <c r="L84" s="2" t="inlineStr">
-        <is>
-          <t>Recent scoring trending down 5.4 pts (L5 vs L30) — marginally supports the OVER. TS% shifts -14.5% in this matchup; FG% -10.0% trending (L10 vs L30). Opponent is strong defense (#8) at above-average pace (#9). Mixed signals: 5/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 9.6 pts (1.1 pts above line; 52% blended confidence [T3]). Risk: L3 has dropped to 6.0 (4.8 below L30) — deepening slump makes the over vulnerable.</t>
+      <c r="I85" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J85" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K85" t="n">
+        <v>1.408</v>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>[Low conviction — lean only] Recent scoring trending down 5.4 pts (L5 vs L30) — marginally supports the lean UNDER. TS% shifts -14.5% in this matchup; FG% -10.0% trending (L10 vs L30). Opponent is strong defense (#8) at above-average pace (#9). Mixed signals: 5/10 agree (HR L10, Trend, Defense); counter-signals: Volume, HR L30, Context. Projection model targets 9.6 pts (0.1 pts above line; 51% blended confidence [T3_LEAN]). Risk: 60% over-rate on L30 suggests scoring tendency that could threaten the under.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Kris Dunn</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>SAS @ LAC</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>0.542</v>
+      </c>
+      <c r="F86" t="n">
+        <v>6</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="I86" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J86" t="n">
+        <v>1.893</v>
+      </c>
+      <c r="K86" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>Dunn averages 7.4 pts in 5 meetings (+2.9 vs line) — supports the OVER. FG% -6.7% trending (L10 vs L30). Opponent is strong defense (#8) at above-average pace (#9). 6/10 signals agree — Volume, HR L30, HR L10, Context support the OVER; Trend, Defense, FG Trend dissent. Projection model targets 5.9 pts (1.4 pts above line; 54% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
@@ -11327,7 +11583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J84"/>
+  <dimension ref="A1:J86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11425,7 +11681,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Grayson Allen</t>
+          <t>LaMelo Ball</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -11439,13 +11695,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.5</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LaMelo Ball</t>
+          <t>Devin Booker</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -11459,13 +11715,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>19.5</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Jalen Green</t>
+          <t>Ryan Kalkbrenner</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -11475,17 +11731,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Devin Booker</t>
+          <t>Moussa Diabaté</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -11495,17 +11751,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>25.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ryan Kalkbrenner</t>
+          <t>Coby White</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -11519,13 +11775,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>5.5</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Moussa Diabaté</t>
+          <t>Kon Knueppel</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -11539,13 +11795,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>8.5</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Coby White</t>
+          <t>Brandon Miller</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -11559,13 +11815,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.5</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Kon Knueppel</t>
+          <t>Royce O'Neale</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -11579,13 +11835,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Brandon Miller</t>
+          <t>Collin Gillespie</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -11595,17 +11851,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>19.5</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Dillon Brooks</t>
+          <t>Miles Bridges</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -11615,17 +11871,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Royce O'Neale</t>
+          <t>Grayson Allen</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -11635,17 +11891,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>7.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Collin Gillespie</t>
+          <t>Jalen Green</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -11655,17 +11911,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10.5</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Miles Bridges</t>
+          <t>Dillon Brooks</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -11675,11 +11931,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="17">
@@ -11799,7 +12055,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="23">
@@ -11919,7 +12175,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>26.5</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="29">
@@ -11999,7 +12255,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="33">
@@ -12025,7 +12281,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Alex Caruso</t>
+          <t>Ajay Mitchell</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -12035,17 +12291,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>4.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Ajay Mitchell</t>
+          <t>Jalen Williams</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -12059,13 +12315,13 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Jalen Williams</t>
+          <t>Cason Wallace</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -12075,17 +12331,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>18.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cason Wallace</t>
+          <t>Shai Gilgeous-Alexander</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -12099,13 +12355,13 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>6.5</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Shai Gilgeous-Alexander</t>
+          <t>Rui Hachimura</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -12115,17 +12371,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>LEAN OVER</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>30.5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Rui Hachimura</t>
+          <t>Luka Dončić</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -12135,17 +12391,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>7.5</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Luka Dončić</t>
+          <t>LeBron James</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -12159,13 +12415,13 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>32.5</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>LeBron James</t>
+          <t>Austin Reaves</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -12175,17 +12431,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>LEAN OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Austin Reaves</t>
+          <t>Deandre Ayton</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -12199,7 +12455,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>19.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="43">
@@ -12245,7 +12501,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Deandre Ayton</t>
+          <t>Alex Caruso</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -12255,11 +12511,11 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>9.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="46">
@@ -12279,7 +12535,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="47">
@@ -12419,7 +12675,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>10.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="54">
@@ -12465,32 +12721,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Saddiq Bey</t>
+          <t>De'Anthony Melton</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NOP @ POR</t>
+          <t>CLE @ GSW</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>17.5</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Herbert Jones</t>
+          <t>Gui Santos</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NOP @ POR</t>
+          <t>CLE @ GSW</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -12499,13 +12755,13 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>9.5</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Scoot Henderson</t>
+          <t>Saddiq Bey</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -12515,7 +12771,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -12525,7 +12781,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Deni Avdija</t>
+          <t>Herbert Jones</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -12539,13 +12795,13 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>26.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Yves Missi</t>
+          <t>Scoot Henderson</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -12559,13 +12815,13 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>5.5</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Donovan Clingan</t>
+          <t>Deni Avdija</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -12579,13 +12835,13 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>13.5</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Derik Queen</t>
+          <t>Yves Missi</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -12595,17 +12851,17 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>8.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Jrue Holiday</t>
+          <t>Donovan Clingan</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -12619,13 +12875,13 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>17.5</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Robert Williams III</t>
+          <t>Derik Queen</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -12635,17 +12891,17 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>LEAN OVER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>5.5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Trey Murphy III</t>
+          <t>Jrue Holiday</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -12655,17 +12911,17 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>20.5</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Zion Williamson</t>
+          <t>Robert Williams III</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -12679,13 +12935,13 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>20.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Dejounte Murray</t>
+          <t>Trey Murphy III</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -12699,13 +12955,13 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Toumani Camara</t>
+          <t>Zion Williamson</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -12719,13 +12975,13 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>13.5</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Matisse Thybulle</t>
+          <t>Dejounte Murray</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -12735,42 +12991,42 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>7.5</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Keldon Johnson</t>
+          <t>Toumani Camara</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SAS @ LAC</t>
+          <t>NOP @ POR</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>LEAN OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Devin Vassell</t>
+          <t>Matisse Thybulle</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SAS @ LAC</t>
+          <t>NOP @ POR</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -12779,13 +13035,13 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>12.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Dylan Harper</t>
+          <t>Keldon Johnson</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -12795,7 +13051,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>LEAN OVER</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -12805,7 +13061,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>De'Aaron Fox</t>
+          <t>Devin Vassell</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -12815,17 +13071,17 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Stephon Castle</t>
+          <t>Dylan Harper</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -12835,17 +13091,17 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Harrison Barnes</t>
+          <t>De'Aaron Fox</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -12859,13 +13115,13 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>7.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Bennedict Mathurin</t>
+          <t>Stephon Castle</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -12875,17 +13131,17 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>John Collins</t>
+          <t>Harrison Barnes</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -12899,13 +13155,13 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Julian Champagnie</t>
+          <t>Bennedict Mathurin</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -12915,17 +13171,17 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>9.5</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Brook Lopez</t>
+          <t>John Collins</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -12939,13 +13195,13 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Darius Garland</t>
+          <t>Julian Champagnie</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -12955,17 +13211,17 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>19.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Victor Wembanyama</t>
+          <t>Brook Lopez</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -12979,13 +13235,13 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>24.5</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Kris Dunn</t>
+          <t>Darius Garland</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -12995,17 +13251,17 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>4.5</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Kawhi Leonard</t>
+          <t>Victor Wembanyama</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -13015,31 +13271,71 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>27.5</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
+          <t>Kawhi Leonard</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>SAS @ LAC</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
           <t>Derrick Jones Jr.</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>SAS @ LAC</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>LEAN UNDER</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Kris Dunn</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>SAS @ LAC</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D84" t="n">
-        <v>8.5</v>
+      <c r="D86" t="n">
+        <v>4.5</v>
       </c>
     </row>
   </sheetData>

--- a/daily/2026-04-02.xlsx
+++ b/daily/2026-04-02.xlsx
@@ -32,7 +32,7 @@
       <color rgb="00E0E0E0"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +42,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001E1E2E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EF4444"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0022C55E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F59E0B"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,7 +72,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -65,6 +80,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -628,7 +646,6 @@
       <c r="V2" t="n">
         <v>19</v>
       </c>
-      <c r="W2" t="inlineStr"/>
       <c r="X2" t="n">
         <v>0</v>
       </c>
@@ -706,7 +723,6 @@
       <c r="V3" t="n">
         <v>21</v>
       </c>
-      <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
         <v>54</v>
       </c>
@@ -948,7 +964,6 @@
       <c r="V6" t="n">
         <v>21</v>
       </c>
-      <c r="W6" t="inlineStr"/>
       <c r="X6" t="n">
         <v>-11</v>
       </c>
@@ -1026,7 +1041,6 @@
       <c r="V7" t="n">
         <v>21</v>
       </c>
-      <c r="W7" t="inlineStr"/>
       <c r="X7" t="n">
         <v>-35.6</v>
       </c>
@@ -1186,7 +1200,6 @@
       <c r="V9" t="n">
         <v>21</v>
       </c>
-      <c r="W9" t="inlineStr"/>
       <c r="X9" t="n">
         <v>-9.199999999999999</v>
       </c>
@@ -1346,7 +1359,6 @@
       <c r="V11" t="n">
         <v>19</v>
       </c>
-      <c r="W11" t="inlineStr"/>
       <c r="X11" t="n">
         <v>-13.4</v>
       </c>
@@ -1424,7 +1436,6 @@
       <c r="V12" t="n">
         <v>19</v>
       </c>
-      <c r="W12" t="inlineStr"/>
       <c r="X12" t="n">
         <v>16.1</v>
       </c>
@@ -1584,7 +1595,6 @@
       <c r="V14" t="n">
         <v>19</v>
       </c>
-      <c r="W14" t="inlineStr"/>
       <c r="X14" t="n">
         <v>12.8</v>
       </c>
@@ -1744,7 +1754,6 @@
       <c r="V16" t="n">
         <v>19</v>
       </c>
-      <c r="W16" t="inlineStr"/>
       <c r="X16" t="n">
         <v>-38</v>
       </c>
@@ -1904,7 +1913,6 @@
       <c r="V18" t="n">
         <v>16</v>
       </c>
-      <c r="W18" t="inlineStr"/>
       <c r="X18" t="n">
         <v>-9.4</v>
       </c>
@@ -2064,7 +2072,6 @@
       <c r="V20" t="n">
         <v>16</v>
       </c>
-      <c r="W20" t="inlineStr"/>
       <c r="X20" t="n">
         <v>0.8</v>
       </c>
@@ -2470,7 +2477,6 @@
       <c r="V25" t="n">
         <v>17</v>
       </c>
-      <c r="W25" t="inlineStr"/>
       <c r="X25" t="n">
         <v>-27.8</v>
       </c>
@@ -2630,7 +2636,6 @@
       <c r="V27" t="n">
         <v>16</v>
       </c>
-      <c r="W27" t="inlineStr"/>
       <c r="X27" t="n">
         <v>8.699999999999999</v>
       </c>
@@ -2708,7 +2713,6 @@
       <c r="V28" t="n">
         <v>17</v>
       </c>
-      <c r="W28" t="inlineStr"/>
       <c r="X28" t="n">
         <v>7.9</v>
       </c>
@@ -3196,7 +3200,6 @@
       <c r="V34" t="n">
         <v>18</v>
       </c>
-      <c r="W34" t="inlineStr"/>
       <c r="X34" t="n">
         <v>-7.3</v>
       </c>
@@ -4176,7 +4179,6 @@
       <c r="V46" t="n">
         <v>10</v>
       </c>
-      <c r="W46" t="inlineStr"/>
       <c r="X46" t="n">
         <v>-30.4</v>
       </c>
@@ -4336,7 +4338,6 @@
       <c r="V48" t="n">
         <v>13</v>
       </c>
-      <c r="W48" t="inlineStr"/>
       <c r="X48" t="n">
         <v>-1</v>
       </c>
@@ -4660,7 +4661,6 @@
       <c r="V52" t="n">
         <v>10</v>
       </c>
-      <c r="W52" t="inlineStr"/>
       <c r="X52" t="n">
         <v>0.5</v>
       </c>
@@ -4738,7 +4738,6 @@
       <c r="V53" t="n">
         <v>13</v>
       </c>
-      <c r="W53" t="inlineStr"/>
       <c r="X53" t="n">
         <v>-34.3</v>
       </c>
@@ -4898,7 +4897,6 @@
       <c r="V55" t="n">
         <v>13</v>
       </c>
-      <c r="W55" t="inlineStr"/>
       <c r="X55" t="n">
         <v>-3.4</v>
       </c>
@@ -4976,7 +4974,6 @@
       <c r="V56" t="n">
         <v>10</v>
       </c>
-      <c r="W56" t="inlineStr"/>
       <c r="X56" t="n">
         <v>-2.9</v>
       </c>
@@ -5136,7 +5133,6 @@
       <c r="V58" t="n">
         <v>20</v>
       </c>
-      <c r="W58" t="inlineStr"/>
       <c r="X58" t="n">
         <v>0.7</v>
       </c>
@@ -5624,7 +5620,6 @@
       <c r="V64" t="n">
         <v>20</v>
       </c>
-      <c r="W64" t="inlineStr"/>
       <c r="X64" t="n">
         <v>14.2</v>
       </c>
@@ -5866,7 +5861,6 @@
       <c r="V67" t="n">
         <v>20</v>
       </c>
-      <c r="W67" t="inlineStr"/>
       <c r="X67" t="n">
         <v>5</v>
       </c>
@@ -6026,7 +6020,6 @@
       <c r="V69" t="n">
         <v>20</v>
       </c>
-      <c r="W69" t="inlineStr"/>
       <c r="X69" t="n">
         <v>15.6</v>
       </c>
@@ -6186,7 +6179,6 @@
       <c r="V71" t="n">
         <v>7</v>
       </c>
-      <c r="W71" t="inlineStr"/>
       <c r="X71" t="n">
         <v>0</v>
       </c>
@@ -6428,7 +6420,6 @@
       <c r="V74" t="n">
         <v>26</v>
       </c>
-      <c r="W74" t="inlineStr"/>
       <c r="X74" t="n">
         <v>8</v>
       </c>
@@ -6981,7 +6972,7 @@
         <v>47</v>
       </c>
       <c r="Q81" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
         <v>4.5</v>
@@ -7244,7 +7235,6 @@
       <c r="V84" t="n">
         <v>9</v>
       </c>
-      <c r="W84" t="inlineStr"/>
       <c r="X84" t="n">
         <v>2.4</v>
       </c>
@@ -11639,1703 +11629,3877 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Mark Williams</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>PHX @ CHA</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>LEAN UNDER</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="3" t="n">
         <v>7.5</v>
       </c>
+      <c r="E2" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Williams scored 12 pts vs 7.5 line (+4.5), UNDER missed by 4.5 pts. Minutes were as expected: 20 played vs L10 avg 21.4. Shooting efficiency was hot: 85.7% FG (+32.9% vs L10 avg of 52.8%). 6/7 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Context. Signals that were wrong: Trend, Defense, Pace. Projection model targeted 7.7 pts — actual 12 was 4.3 pts off (wrong direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Grant Williams</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>PHX @ CHA</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="3" t="n">
         <v>5.5</v>
       </c>
+      <c r="E3" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Williams scored 10 pts vs 5.5 line (+4.5), UNDER missed by 4.5 pts. Minutes were as expected: 21 played vs L10 avg 18.7. Shooting efficiency was cold: 30.0% FG (-12.1% vs L10 avg of 42.1%). 3/10 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Context. Signals that were wrong: Trend, Defense, Pace. Projection model targeted 4.9 pts — actual 10 was 5.1 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>LaMelo Ball</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>PHX @ CHA</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="3" t="n">
         <v>20.5</v>
       </c>
+      <c r="E4" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Ball scored 15 pts vs 20.5 line (-5.5), OVER missed by 5.5 pts. Ball played 25 min (-3.3 vs L10 avg of 28.5) — 12% less than expected. Shooting was in line with averages: 46.2% FG (6/13, L10 avg 43.4%). Counter-signals that proved correct: Volume, HR L30, HR L10, Trend. Signals that were wrong: Context, H2H, FG Trend. Projection model targeted 20.9 pts — actual 15 was 5.9 pts off (correct direction). Loss classification: MODEL_FAILURE. Note: Model signals were misleading for this matchup — review Ball's recent role and usage for pattern shifts.</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Devin Booker</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>PHX @ CHA</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="3" t="n">
         <v>25.5</v>
       </c>
+      <c r="E5" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Booker scored 22 pts vs 25.5 line (-3.5), OVER missed by 3.5 pts. Minutes were as expected: 36 played vs L10 avg 33.0. Shooting efficiency was cold: 40.9% FG (-7.5% vs L10 avg of 48.4%). 9/22 from the field. Counter-signals that proved correct: Defense, Pace. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 34.7 pts — actual 22 was 12.7 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Ryan Kalkbrenner</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>PHX @ CHA</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="4" t="n">
         <v>5.5</v>
       </c>
+      <c r="E6" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Kalkbrenner scored 8 pts vs 5.5 line (+2.5), OVER hit by 2.5 pts. Kalkbrenner played 23 min (+5.7 vs L10 avg of 17.6) — 32% more than expected. Shooting efficiency was hot: 100.0% FG (+17.0% vs L10 avg of 83.0%). 3/3 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, Defense (6/10 aligned). Counter-signals that were wrong: Trend, H2H, Pace. Projection model targeted 6.3 pts — actual 8 was 1.7 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Kalkbrenner in this role.</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Moussa Diabaté</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>PHX @ CHA</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="4" t="n">
         <v>7.5</v>
       </c>
+      <c r="E7" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Diabaté scored 4 pts vs 7.5 line (-3.5), UNDER hit by 3.5 pts. Minutes were as expected: 25 played vs L10 avg 27.4. Shooting efficiency was hot: 100.0% FG (+39.5% vs L10 avg of 60.5%). 2/2 from the field. Signals that called it correctly: Context, Defense, Pace, FG Trend, Min Trend (5/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 2.8 pts — actual 4 was 1.2 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Diabaté in this role.</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Coby White</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>PHX @ CHA</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="4" t="n">
         <v>13.5</v>
       </c>
+      <c r="E8" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>WIN — White scored 19 pts vs 13.5 line (+5.5), OVER hit by 5.5 pts. Minutes were as expected: 20 played vs L10 avg 20.9. Shooting was in line with averages: 46.2% FG (6/13, L10 avg 47.7%). Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (7/10 aligned). Counter-signals that were wrong: Defense, Pace, Min Trend. Projection model targeted 13.9 pts — actual 19 was 5.1 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms White's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Kon Knueppel</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>PHX @ CHA</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="3" t="n">
         <v>16.5</v>
       </c>
+      <c r="E9" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Knueppel scored 20 pts vs 16.5 line (+3.5), UNDER missed by 3.5 pts. Knueppel played 32 min (+3.8 vs L10 avg of 28.7) — 13% more than expected. Shooting efficiency was hot: 50.0% FG (+6.8% vs L10 avg of 43.2%). 7/14 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Context. Signals that were wrong: Trend, Defense, Pace. Projection model targeted 9.2 pts — actual 20 was 10.8 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Brandon Miller</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>PHX @ CHA</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="4" t="n">
         <v>19.5</v>
       </c>
+      <c r="E10" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Miller scored 17 pts vs 19.5 line (-2.5), UNDER hit by 2.5 pts. Minutes were as expected: 31 played vs L10 avg 30.5. Shooting was in line with averages: 50.0% FG (7/14, L10 avg 45.6%). Signals that called it correctly: Trend, Defense, H2H, Pace, FG Trend (5/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 13.5 pts — actual 17 was 3.5 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Miller's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Royce O'Neale</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>PHX @ CHA</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="4" t="n">
         <v>7.5</v>
       </c>
+      <c r="E11" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>WIN — O'Neale scored 3 pts vs 7.5 line (-4.5), UNDER hit by 4.5 pts. O'Neale played 17 min (-10.7 vs L10 avg of 27.3) — 39% less than expected. Shooting efficiency was hot: 50.0% FG (+6.1% vs L10 avg of 43.9%). 1/2 from the field. Signals that called it correctly: Defense, Pace, Min Trend (3/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 4.0 pts — actual 3 was 1.0 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for O'Neale in this role.</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Collin Gillespie</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>PHX @ CHA</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="3" t="n">
         <v>10.5</v>
       </c>
+      <c r="E12" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Gillespie scored 6 pts vs 10.5 line (-4.5), OVER missed by 4.5 pts. Gillespie played 24 min (-5.2 vs L10 avg of 28.9) — 18% less than expected. Shooting was in line with averages: 28.6% FG (2/7, L10 avg 32.1%). Counter-signals that proved correct: Trend, Defense, H2H, Pace. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 17.3 pts — actual 6 was 11.3 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Gillespie for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Miles Bridges</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>PHX @ CHA</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="4" t="n">
         <v>13.5</v>
       </c>
+      <c r="E13" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Bridges scored 25 pts vs 13.5 line (+11.5), OVER hit by 11.5 pts. Minutes were as expected: 27 played vs L10 avg 28.4. Shooting efficiency was hot: 62.5% FG (+7.1% vs L10 avg of 55.4%). 10/16 from the field. Signals that called it correctly: Volume, HR L10, Context, H2H, FG Trend (5/10 aligned). Counter-signals that were wrong: HR L30, Trend, Defense. Projection model targeted 14.4 pts — actual 25 was 10.6 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Bridges's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Grayson Allen</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>PHX @ CHA</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E14" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Allen scored 13 pts vs 12.5 line (+0.5), OVER hit by 0.5 pts. Minutes were as expected: 24 played vs L10 avg 27.1. Shooting was in line with averages: 40.0% FG (4/10, L10 avg 39.9%). Signals that called it correctly: Volume, HR L30, HR L10, Context, FG Trend (5/10 aligned). Counter-signals that were wrong: Trend, Defense, H2H. Projection model targeted 14.4 pts — actual 13 was 1.4 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Allen in this role.</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Jalen Green</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>PHX @ CHA</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="3" t="n">
         <v>16.5</v>
       </c>
+      <c r="E15" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Green scored 25 pts vs 16.5 line (+8.5), UNDER missed by 8.5 pts. Green played 34 min (+5.3 vs L10 avg of 29.0) — 18% more than expected. Shooting efficiency was hot: 52.6% FG (+9.0% vs L10 avg of 43.6%). 10/19 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Trend. Signals that were wrong: Context, Defense, Pace. Projection model targeted 14.3 pts — actual 25 was 10.7 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Dillon Brooks</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>PHX @ CHA</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="4" t="n">
         <v>14.5</v>
       </c>
+      <c r="E16" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Brooks scored 13 pts vs 14.5 line (-1.5), UNDER hit by 1.5 pts. Minutes were as expected: 29 played vs L10 avg 27.8. Shooting was in line with averages: 41.7% FG (5/12, L10 avg 41.6%). Signals that called it correctly: Trend, Defense, Pace, FG Trend, Min Trend (5/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 1.9 pts — actual 13 was 11.1 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms Brooks's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Jalen Duren</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>MIN @ DET</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="4" t="n">
         <v>22.5</v>
       </c>
+      <c r="E17" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Duren scored 22 pts vs 22.5 line (-0.5), UNDER hit by 0.5 pts. Duren played 36 min (+4.3 vs L10 avg of 31.2) — 14% more than expected. Shooting efficiency was cold: 53.3% FG (-17.1% vs L10 avg of 70.4%). 8/15 from the field. Signals that called it correctly: Volume, Context, Defense, H2H, Pace (5/10 aligned). Counter-signals that were wrong: HR L30, HR L10, Trend. Projection model targeted 15.8 pts — actual 22 was 6.2 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms Duren's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>Paul Reed</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>MIN @ DET</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="3" t="n">
         <v>7.5</v>
       </c>
+      <c r="E18" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Reed scored 4 pts vs 7.5 line (-3.5), OVER missed by 3.5 pts. Minutes were as expected: 16 played vs L10 avg 17.3. Shooting efficiency was cold: 50.0% FG (-13.8% vs L10 avg of 63.8%). 2/4 from the field. Counter-signals that proved correct: Defense, H2H, Pace. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 7.4 pts — actual 4 was 3.4 pts off (wrong direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Ausar Thompson</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>MIN @ DET</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E19" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Thompson scored 7 pts vs 9.5 line (-2.5), UNDER hit by 2.5 pts. Thompson played 31 min (+3.2 vs L10 avg of 27.8) — 12% more than expected. Shooting was in line with averages: 50.0% FG (3/6, L10 avg 50.3%). Signals that called it correctly: Volume, HR L30, HR L10, Context, Defense (7/10 aligned). Counter-signals that were wrong: Trend, H2H, Min Trend. Projection model targeted 7.8 pts — actual 7 was 0.8 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Thompson in this role.</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>Daniss Jenkins</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>MIN @ DET</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="3" t="n">
         <v>16.5</v>
       </c>
+      <c r="E20" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Jenkins scored 26 pts vs 16.5 line (+9.5), UNDER missed by 9.5 pts. Jenkins played 37 min (+3.7 vs L10 avg of 33.1) — 11% more than expected. Shooting was in line with averages: 47.4% FG (9/19, L10 avg 43.8%). Counter-signals that proved correct: HR L10, Trend, H2H, FG Trend. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 13.3 pts — actual 26 was 12.7 pts off (correct direction). Loss classification: BLOWOUT_EFFECT. Note: Game script invalidated the prop. Consider blowout probability when DET is involved.</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>BLOWOUT_EFFECT</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>Rudy Gobert</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>MIN @ DET</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="3" t="n">
         <v>10.5</v>
       </c>
+      <c r="E21" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Gobert scored 6 pts vs 10.5 line (-4.5), OVER missed by 4.5 pts. Gobert played 27 min (-3.7 vs L10 avg of 30.9) — 12% less than expected. Shooting was in line with averages: 66.7% FG (2/3, L10 avg 63.8%). Counter-signals that proved correct: HR L30, Defense, Pace, FG Trend. Signals that were wrong: Volume, HR L10, Trend. Projection model targeted 12.2 pts — actual 6 was 6.2 pts off (correct direction). Loss classification: MODEL_FAILURE. Note: Model signals were misleading for this matchup — review Gobert's recent role and usage for pattern shifts.</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Donte DiVincenzo</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>MIN @ DET</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E22" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>WIN — DiVincenzo scored 5 pts vs 11.5 line (-6.5), UNDER hit by 6.5 pts. Minutes were as expected: 30 played vs L10 avg 30.2. Shooting efficiency was cold: 25.0% FG (-12.2% vs L10 avg of 37.2%). 2/8 from the field. Signals that called it correctly: Volume, HR L30, Context, Defense, H2H (7/10 aligned). Counter-signals that were wrong: HR L10, Trend, Min Trend. Projection model targeted 9.9 pts — actual 5 was 4.9 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms DiVincenzo's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>Duncan Robinson</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>MIN @ DET</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="3" t="n">
         <v>11.5</v>
       </c>
+      <c r="E23" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Robinson scored 15 pts vs 11.5 line (+3.5), UNDER missed by 3.5 pts. Minutes were as expected: 29 played vs L10 avg 26.8. Shooting was in line with averages: 45.5% FG (5/11, L10 avg 47.9%). Counter-signals that proved correct: Volume, HR L30, HR L10, Trend. Signals that were wrong: Context, Defense, H2H. Projection model targeted 10.5 pts — actual 15 was 4.5 pts off (correct direction). Loss classification: MODEL_FAILURE. Note: Model signals were misleading for this matchup — review Robinson's recent role and usage for pattern shifts.</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>Julius Randle</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>MIN @ DET</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="D24" s="3" t="n">
         <v>19.5</v>
       </c>
+      <c r="E24" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Randle scored 27 pts vs 19.5 line (+7.5), UNDER missed by 7.5 pts. Minutes were as expected: 35 played vs L10 avg 32.0. Shooting efficiency was hot: 60.0% FG (+15.5% vs L10 avg of 44.5%). 9/15 from the field. Counter-signals that proved correct: HR L10, FG Trend. Signals that were wrong: Volume, HR L30, Trend. Projection model targeted 15.6 pts — actual 27 was 11.4 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>Bones Hyland</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>MIN @ DET</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" s="4" t="n">
         <v>10.5</v>
       </c>
+      <c r="E25" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Hyland scored 6 pts vs 10.5 line (-4.5), UNDER hit by 4.5 pts. Hyland played 19 min (-3.2 vs L10 avg of 22.4) — 14% less than expected. Shooting efficiency was cold: 25.0% FG (-21.0% vs L10 avg of 46.0%). 3/12 from the field. Signals that called it correctly: Volume, HR L30, Context, Defense, Pace (5/10 aligned). Counter-signals that were wrong: HR L10, Trend, H2H. Projection model targeted 5.0 pts — actual 6 was 1.0 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Hyland in this role.</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>Kevin Huerter</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>MIN @ DET</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" s="3" t="n">
         <v>7.5</v>
       </c>
+      <c r="E26" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Huerter scored 12 pts vs 7.5 line (+4.5), UNDER missed by 4.5 pts. Minutes were as expected: 22 played vs L10 avg 23.9. Shooting efficiency was hot: 66.7% FG (+21.4% vs L10 avg of 45.3%). 4/6 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Trend. Signals that were wrong: Context, Defense, H2H. Projection model targeted 3.9 pts — actual 12 was 8.1 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>Tobias Harris</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>MIN @ DET</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="D27" s="3" t="n">
         <v>14.5</v>
       </c>
+      <c r="E27" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Harris scored 2 pts vs 14.5 line (-12.5), OVER missed by 12.5 pts. Harris played 6 min (-22.2 vs L10 avg of 28.3) — 78% less than expected. Shooting efficiency was hot: 100.0% FG (+49.6% vs L10 avg of 50.4%). 1/1 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Context. Signals that were wrong: Trend, FG Trend. Projection model targeted 14.9 pts — actual 2 was 12.9 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Harris for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>Anthony Edwards</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>MIN @ DET</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="D28" s="5" t="n">
         <v>25.5</v>
       </c>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="5" t="inlineStr"/>
+      <c r="I28" s="5" t="n"/>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>Ayo Dosunmu</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>MIN @ DET</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" s="4" t="n">
         <v>15.5</v>
       </c>
+      <c r="E29" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Dosunmu scored 19 pts vs 15.5 line (+3.5), OVER hit by 3.5 pts. Minutes were as expected: 32 played vs L10 avg 29.6. Shooting efficiency was cold: 46.7% FG (-7.5% vs L10 avg of 54.2%). 7/15 from the field. Signals that called it correctly: HR L10, Trend, Context, FG Trend, Min Trend (5/10 aligned). Counter-signals that were wrong: Volume, HR L30, Defense. Projection model targeted 15.3 pts — actual 19 was 3.7 pts off (wrong direction). Result classification: MODEL_CORRECT. Note: Result confirms Dosunmu's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>Naz Reid</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>MIN @ DET</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="D30" s="3" t="n">
         <v>12.5</v>
       </c>
+      <c r="E30" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Reid scored 19 pts vs 12.5 line (+6.5), UNDER missed by 6.5 pts. Reid played 30 min (+4.9 vs L10 avg of 25.6) — 19% more than expected. Shooting was in line with averages: 37.5% FG (6/16, L10 avg 42.1%). Counter-signals that proved correct: FG Trend, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 4.8 pts — actual 19 was 14.2 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>Isaiah Hartenstein</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>LAL @ OKC</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>LEAN UNDER</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" s="3" t="n">
         <v>6.5</v>
       </c>
+      <c r="E31" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Hartenstein scored 7 pts vs 6.5 line (+0.5), UNDER missed by 0.5 pts. Minutes were as expected: 20 played vs L10 avg 22.2. Shooting efficiency was hot: 75.0% FG (+37.7% vs L10 avg of 37.3%). 3/4 from the field. Counter-signals that proved correct: Volume, HR L30, Context, H2H. Signals that were wrong: HR L10, Trend, Defense. Projection model targeted 6.7 pts — actual 7 was 0.3 pts close (wrong direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>Chet Holmgren</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>LAL @ OKC</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D32" t="n">
+      <c r="D32" s="4" t="n">
         <v>15.5</v>
       </c>
+      <c r="E32" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Holmgren scored 7 pts vs 15.5 line (-8.5), UNDER hit by 8.5 pts. Holmgren played 18 min (-11.5 vs L10 avg of 29.2) — 39% less than expected. Shooting efficiency was cold: 42.9% FG (-10.7% vs L10 avg of 53.6%). 3/7 from the field. Signals that called it correctly: Trend, Context, Defense, H2H, Pace (6/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 13.0 pts — actual 7 was 6.0 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Holmgren's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>Luguentz Dort</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>LAL @ OKC</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D33" t="n">
+      <c r="D33" s="4" t="n">
         <v>6.5</v>
       </c>
+      <c r="E33" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Dort scored 14 pts vs 6.5 line (+7.5), OVER hit by 7.5 pts. Minutes were as expected: 21 played vs L10 avg 24.0. Shooting efficiency was hot: 62.5% FG (+34.9% vs L10 avg of 27.6%). 5/8 from the field. Signals that called it correctly: Volume, HR L30, Context, H2H (4/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 9.2 pts — actual 14 was 4.8 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Dort's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>Ajay Mitchell</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>LAL @ OKC</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D34" t="n">
+      <c r="D34" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E34" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Mitchell scored 10 pts vs 12.5 line (-2.5), UNDER hit by 2.5 pts. Mitchell played 16 min (-10.2 vs L10 avg of 26.3) — 39% less than expected. Shooting efficiency was hot: 57.1% FG (+7.2% vs L10 avg of 49.9%). 4/7 from the field. Signals that called it correctly: Trend, Context, Defense, Pace, FG Trend (5/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 9.5 pts — actual 10 was 0.5 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Mitchell in this role.</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>Jalen Williams</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>LAL @ OKC</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D35" t="n">
+      <c r="D35" s="4" t="n">
         <v>18.5</v>
       </c>
+      <c r="E35" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Williams scored 10 pts vs 18.5 line (-8.5), UNDER hit by 8.5 pts. Minutes were as expected: 23 played vs L10 avg 24.7. Shooting efficiency was cold: 40.0% FG (-12.7% vs L10 avg of 52.7%). 4/10 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, Defense (7/10 aligned). Counter-signals that were wrong: Trend, H2H, FG Trend. Projection model targeted 16.3 pts — actual 10 was 6.3 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Williams's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>Cason Wallace</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>LAL @ OKC</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D36" t="n">
+      <c r="D36" s="4" t="n">
         <v>6.5</v>
       </c>
+      <c r="E36" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Wallace scored 8 pts vs 6.5 line (+1.5), OVER hit by 1.5 pts. Minutes were as expected: 21 played vs L10 avg 24.1. Shooting was in line with averages: 42.9% FG (3/7, L10 avg 44.7%). Signals that called it correctly: Volume, HR L30, Context, H2H, FG Trend (5/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 8.3 pts — actual 8 was 0.3 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Wallace in this role.</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>Shai Gilgeous-Alexander</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>LAL @ OKC</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D37" t="n">
+      <c r="D37" s="3" t="n">
         <v>30.5</v>
       </c>
+      <c r="E37" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Gilgeous-Alexander scored 28 pts vs 30.5 line (-2.5), OVER missed by 2.5 pts. Gilgeous-Alexander played 30 min (-4.1 vs L10 avg of 33.9) — 12% less than expected. Shooting efficiency was cold: 48.0% FG (-12.1% vs L10 avg of 60.1%). 12/25 from the field. Counter-signals that proved correct: HR L30, HR L10, Defense, Pace. Signals that were wrong: Volume, Trend, Context. Projection model targeted 32.6 pts — actual 28 was 4.6 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Gilgeous-Alexander for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>Rui Hachimura</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>LAL @ OKC</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D38" t="n">
+      <c r="D38" s="3" t="n">
         <v>8.5</v>
       </c>
+      <c r="E38" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Hachimura scored 4 pts vs 8.5 line (-4.5), OVER missed by 4.5 pts. Hachimura played 18 min (-5.4 vs L10 avg of 23.7) — 23% less than expected. Shooting efficiency was cold: 22.2% FG (-34.8% vs L10 avg of 57.0%). 2/9 from the field. Counter-signals that proved correct: HR L10, Trend, Defense, Pace. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 8.5 pts — actual 4 was 4.5 pts off (wrong direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Hachimura for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>Luka Dončić</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>LAL @ OKC</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D39" t="n">
+      <c r="D39" s="4" t="n">
         <v>31.5</v>
       </c>
+      <c r="E39" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>-19.5</v>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Dončić scored 12 pts vs 31.5 line (-19.5), UNDER hit by 19.5 pts. Dončić played 26 min (-12.6 vs L10 avg of 38.3) — 33% less than expected. Shooting efficiency was cold: 30.0% FG (-19.1% vs L10 avg of 49.1%). 3/10 from the field. Signals that called it correctly: Defense, H2H, Pace (3/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 23.5 pts — actual 12 was 11.5 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Dončić's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>LeBron James</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>LAL @ OKC</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D40" t="n">
+      <c r="D40" s="4" t="n">
         <v>17.5</v>
       </c>
+      <c r="E40" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>WIN — James scored 13 pts vs 17.5 line (-4.5), UNDER hit by 4.5 pts. James played 26 min (-9.4 vs L10 avg of 35.4) — 27% less than expected. Shooting efficiency was cold: 42.9% FG (-11.5% vs L10 avg of 54.4%). 3/7 from the field. Signals that called it correctly: Trend, Defense, Pace (3/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 16.6 pts — actual 13 was 3.6 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms James's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>Austin Reaves</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>LAL @ OKC</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D41" t="n">
+      <c r="D41" s="4" t="n">
         <v>19.5</v>
       </c>
+      <c r="E41" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Reaves scored 15 pts vs 19.5 line (-4.5), UNDER hit by 4.5 pts. Reaves played 27 min (-12.1 vs L10 avg of 38.7) — 31% less than expected. Shooting efficiency was hot: 55.6% FG (+11.7% vs L10 avg of 43.9%). 5/9 from the field. Signals that called it correctly: HR L30, Context, Defense, H2H, Pace (6/10 aligned). Counter-signals that were wrong: Volume, HR L10, Trend. Projection model targeted 14.8 pts — actual 15 was 0.2 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Reaves in this role.</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>Deandre Ayton</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>LAL @ OKC</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D42" t="n">
+      <c r="D42" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E42" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Ayton scored 8 pts vs 9.5 line (-1.5), UNDER hit by 1.5 pts. Ayton played 20 min (-8.5 vs L10 avg of 28.2) — 30% less than expected. Shooting efficiency was cold: 57.1% FG (-18.2% vs L10 avg of 75.3%). 4/7 from the field. Signals that called it correctly: HR L30, Context, Defense, H2H, Pace (5/10 aligned). Counter-signals that were wrong: Volume, HR L10, Trend. Projection model targeted 5.9 pts — actual 8 was 2.1 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms Ayton's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>Jake LaRavia</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>LAL @ OKC</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D43" t="n">
+      <c r="D43" s="4" t="n">
         <v>6.5</v>
       </c>
+      <c r="E43" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>WIN — LaRavia scored 6 pts vs 6.5 line (-0.5), UNDER hit by 0.5 pts. LaRavia played 32 min (+11.7 vs L10 avg of 20.8) — 56% more than expected. Shooting efficiency was cold: 30.0% FG (-30.8% vs L10 avg of 60.8%). 3/10 from the field. Signals that called it correctly: HR L30, HR L10, Trend, Context, Defense (7/10 aligned). Counter-signals that were wrong: Volume, H2H, FG Trend. Projection model targeted 4.6 pts — actual 6 was 1.4 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for LaRavia in this role.</t>
+        </is>
+      </c>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t>Jaxson Hayes</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>LAL @ OKC</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D44" t="n">
+      <c r="D44" s="4" t="n">
         <v>5.5</v>
       </c>
+      <c r="E44" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Hayes scored 12 pts vs 5.5 line (+6.5), OVER hit by 6.5 pts. Minutes were as expected: 21 played vs L10 avg 20.7. Shooting efficiency was hot: 100.0% FG (+41.8% vs L10 avg of 58.2%). 3/3 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (7/10 aligned). Counter-signals that were wrong: Defense, Pace, FG Trend. Projection model targeted 6.4 pts — actual 12 was 5.6 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Hayes's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>Alex Caruso</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="5" t="inlineStr">
         <is>
           <t>LAL @ OKC</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="5" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D45" t="n">
+      <c r="D45" s="5" t="n">
         <v>4.5</v>
       </c>
+      <c r="E45" s="5" t="n"/>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="n"/>
+      <c r="H45" s="5" t="inlineStr"/>
+      <c r="I45" s="5" t="n"/>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="4" t="inlineStr">
         <is>
           <t>Draymond Green</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>CLE @ GSW</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D46" t="n">
+      <c r="D46" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E46" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Green scored 8 pts vs 9.5 line (-1.5), UNDER hit by 1.5 pts. Green played 35 min (+6.0 vs L10 avg of 29.2) — 21% more than expected. Shooting efficiency was cold: 27.3% FG (-17.2% vs L10 avg of 44.5%). 3/11 from the field. Signals that called it correctly: Volume, HR L30, Context (3/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 4.0 pts — actual 8 was 4.0 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms Green's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>Donovan Mitchell</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>CLE @ GSW</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D47" t="n">
+      <c r="D47" s="3" t="n">
         <v>24.5</v>
       </c>
+      <c r="E47" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Mitchell scored 25 pts vs 24.5 line (+0.5), UNDER missed by 0.5 pts. Minutes were as expected: 34 played vs L10 avg 33.6. Shooting efficiency was hot: 50.0% FG (+6.1% vs L10 avg of 43.9%). 7/14 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Context. Signals that were wrong: Trend, H2H, FG Trend. Projection model targeted 21.4 pts — actual 25 was 3.6 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="4" t="inlineStr">
         <is>
           <t>Jarrett Allen</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>CLE @ GSW</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D48" t="n">
+      <c r="D48" s="4" t="n">
         <v>13.5</v>
       </c>
+      <c r="E48" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Allen scored 16 pts vs 13.5 line (+2.5), OVER hit by 2.5 pts. Minutes were as expected: 24 played vs L10 avg 26.7. Shooting efficiency was cold: 50.0% FG (-21.7% vs L10 avg of 71.7%). 5/10 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (8/10 aligned). Counter-signals that were wrong: H2H, Min Trend. Projection model targeted 14.5 pts — actual 16 was 1.5 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Strong signal alignment (8/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>Dennis Schröder</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>CLE @ GSW</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D49" t="n">
+      <c r="D49" s="4" t="n">
         <v>6.5</v>
       </c>
+      <c r="E49" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Schröder scored 12 pts vs 6.5 line (+5.5), OVER hit by 5.5 pts. Minutes were as expected: 20 played vs L10 avg 19.2. Shooting efficiency was hot: 57.1% FG (+18.8% vs L10 avg of 38.3%). 4/7 from the field. Signals that called it correctly: Volume, HR L30, Context, Defense, H2H (7/10 aligned). Counter-signals that were wrong: HR L10, Trend, Min Trend. Projection model targeted 11.9 pts — actual 12 was 0.1 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Schröder in this role.</t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="4" t="inlineStr">
         <is>
           <t>Evan Mobley</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>CLE @ GSW</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D50" t="n">
+      <c r="D50" s="4" t="n">
         <v>17.5</v>
       </c>
+      <c r="E50" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Mobley scored 12 pts vs 17.5 line (-5.5), UNDER hit by 5.5 pts. Minutes were as expected: 32 played vs L10 avg 30.2. Shooting efficiency was cold: 54.5% FG (-11.8% vs L10 avg of 66.3%). 6/11 from the field. Signals that called it correctly: Trend, H2H, Min Trend (3/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 15.0 pts — actual 12 was 3.0 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Mobley's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="4" t="inlineStr">
         <is>
           <t>Kristaps Porziņģis</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>CLE @ GSW</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D51" t="n">
+      <c r="D51" s="4" t="n">
         <v>19.5</v>
       </c>
+      <c r="E51" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Porziņģis scored 16 pts vs 19.5 line (-3.5), UNDER hit by 3.5 pts. Porziņģis played 28 min (+4.0 vs L10 avg of 23.9) — 17% more than expected. Shooting was in line with averages: 46.2% FG (6/13, L10 avg 42.0%). Signals that called it correctly: Volume, HR L30, Context, H2H, FG Trend (6/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 15.1 pts — actual 16 was 0.9 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Porziņģis in this role.</t>
+        </is>
+      </c>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="3" t="inlineStr">
         <is>
           <t>Brandin Podziemski</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t>CLE @ GSW</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D52" t="n">
+      <c r="D52" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E52" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Podziemski scored 25 pts vs 15.5 line (+9.5), UNDER missed by 9.5 pts. Podziemski played 35 min (+4.8 vs L10 avg of 30.4) — 16% more than expected. Shooting efficiency was hot: 60.0% FG (+17.2% vs L10 avg of 42.8%). 9/15 from the field. Counter-signals that proved correct: HR L10, Trend, H2H, Pace. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 14.4 pts — actual 25 was 10.6 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>Max Strus</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t>CLE @ GSW</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D53" t="n">
+      <c r="D53" s="3" t="n">
         <v>9.5</v>
       </c>
+      <c r="E53" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Strus scored 24 pts vs 9.5 line (+14.5), UNDER missed by 14.5 pts. Minutes were as expected: 28 played vs L10 avg 25.6. Shooting efficiency was hot: 64.3% FG (+17.4% vs L10 avg of 46.9%). 9/14 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Trend. Signals that were wrong: Min Trend. Projection model targeted 2.8 pts — actual 24 was 21.2 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>James Harden</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="3" t="inlineStr">
         <is>
           <t>CLE @ GSW</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D54" t="n">
+      <c r="D54" s="3" t="n">
         <v>19.5</v>
       </c>
+      <c r="E54" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Harden scored 19 pts vs 19.5 line (-0.5), OVER missed by 0.5 pts. Minutes were as expected: 37 played vs L10 avg 34.9. Shooting efficiency was hot: 63.6% FG (+17.1% vs L10 avg of 46.5%). 7/11 from the field. Counter-signals that proved correct: HR L10, Trend. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 19.4 pts — actual 19 was 0.4 pts close (wrong direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>Sam Merrill</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>CLE @ GSW</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D55" t="n">
+      <c r="D55" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E55" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Merrill scored 3 pts vs 11.5 line (-8.5), UNDER hit by 8.5 pts. Minutes were as expected: 28 played vs L10 avg 28.8. Shooting efficiency was cold: 16.7% FG (-24.4% vs L10 avg of 41.1%). 1/6 from the field. Signals that called it correctly: FG Trend (1/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 7.1 pts — actual 3 was 4.1 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Merrill's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="4" t="inlineStr">
         <is>
           <t>De'Anthony Melton</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>CLE @ GSW</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D56" t="n">
+      <c r="D56" s="4" t="n">
         <v>13.5</v>
       </c>
+      <c r="E56" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Melton scored 5 pts vs 13.5 line (-8.5), UNDER hit by 8.5 pts. Minutes were as expected: 26 played vs L10 avg 24.8. Shooting efficiency was cold: 16.7% FG (-17.6% vs L10 avg of 34.3%). 2/12 from the field. Signals that called it correctly: Trend, Context, Defense, FG Trend (4/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 11.6 pts — actual 5 was 6.6 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Melton's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>Gui Santos</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>CLE @ GSW</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D57" t="n">
+      <c r="D57" s="3" t="n">
         <v>14.5</v>
       </c>
+      <c r="E57" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Santos scored 25 pts vs 14.5 line (+10.5), UNDER missed by 10.5 pts. Minutes were as expected: 31 played vs L10 avg 31.3. Shooting efficiency was hot: 64.3% FG (+17.4% vs L10 avg of 46.9%). 9/14 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Trend. Signals that were wrong: Context, H2H, FG Trend. Projection model targeted 13.8 pts — actual 25 was 11.2 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="3" t="inlineStr">
         <is>
           <t>Saddiq Bey</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t>NOP @ POR</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D58" t="n">
+      <c r="D58" s="3" t="n">
         <v>17.5</v>
       </c>
+      <c r="E58" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Bey scored 15 pts vs 17.5 line (-2.5), OVER missed by 2.5 pts. Minutes were as expected: 35 played vs L10 avg 32.0. Shooting was in line with averages: 42.9% FG (6/14, L10 avg 43.1%). Counter-signals that proved correct: Trend, H2H, Pace, FG Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 21.4 pts — actual 15 was 6.4 pts off (correct direction). Loss classification: MODEL_FAILURE. Note: Model signals were misleading for this matchup — review Bey's recent role and usage for pattern shifts.</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="4" t="inlineStr">
         <is>
           <t>Herbert Jones</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>NOP @ POR</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D59" t="n">
+      <c r="D59" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E59" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Jones scored 9 pts vs 9.5 line (-0.5), UNDER hit by 0.5 pts. Jones played 26 min (-5.0 vs L10 avg of 30.9) — 16% less than expected. Shooting efficiency was cold: 33.3% FG (-7.2% vs L10 avg of 40.5%). 3/9 from the field. Signals that called it correctly: Volume, HR L30, Context, H2H, Pace (5/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 6.2 pts — actual 9 was 2.8 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms Jones's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="4" t="inlineStr">
         <is>
           <t>Scoot Henderson</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>NOP @ POR</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C60" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D60" t="n">
+      <c r="D60" s="4" t="n">
         <v>16.5</v>
       </c>
+      <c r="E60" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Henderson scored 14 pts vs 16.5 line (-2.5), UNDER hit by 2.5 pts. Henderson played 20 min (-4.0 vs L10 avg of 24.5) — 16% less than expected. Shooting efficiency was hot: 50.0% FG (+8.8% vs L10 avg of 41.2%). 6/12 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, H2H (5/10 aligned). Counter-signals that were wrong: Trend, Defense, Pace. Projection model targeted 11.5 pts — actual 14 was 2.5 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Henderson's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="4" t="inlineStr">
         <is>
           <t>Deni Avdija</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>NOP @ POR</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D61" t="n">
+      <c r="D61" s="4" t="n">
         <v>26.5</v>
       </c>
+      <c r="E61" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Avdija scored 26 pts vs 26.5 line (-0.5), UNDER hit by 0.5 pts. Avdija played 37 min (+5.4 vs L10 avg of 31.8) — 17% more than expected. Shooting efficiency was cold: 35.0% FG (-8.7% vs L10 avg of 43.7%). 7/20 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (7/10 aligned). Counter-signals that were wrong: Defense, Pace, Min Trend. Projection model targeted 20.4 pts — actual 26 was 5.6 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms Avdija's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I61" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t>Yves Missi</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="3" t="inlineStr">
         <is>
           <t>NOP @ POR</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C62" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D62" t="n">
+      <c r="D62" s="3" t="n">
         <v>5.5</v>
       </c>
+      <c r="E62" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Missi scored 6 pts vs 5.5 line (+0.5), UNDER missed by 0.5 pts. Minutes were as expected: 20 played vs L10 avg 22.5. Shooting was in line with averages: 50.0% FG (3/6, L10 avg 48.6%). Counter-signals that proved correct: Volume, HR L30, HR L10, Defense. Signals that were wrong: Trend, Context, H2H. Projection model targeted 2.8 pts — actual 6 was 3.2 pts off (correct direction). Loss classification: CLOSE_CALL. Note: Within 2 pts — direction was sound. Small execution variance, no model adjustment needed.</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="4" t="inlineStr">
         <is>
           <t>Donovan Clingan</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="4" t="inlineStr">
         <is>
           <t>NOP @ POR</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C63" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D63" t="n">
+      <c r="D63" s="4" t="n">
         <v>13.5</v>
       </c>
+      <c r="E63" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Clingan scored 4 pts vs 13.5 line (-9.5), UNDER hit by 9.5 pts. Clingan played 22 min (-4.1 vs L10 avg of 26.3) — 16% less than expected. Shooting was in line with averages: 50.0% FG (2/4, L10 avg 49.0%). Signals that called it correctly: Volume, Trend, Context, H2H, FG Trend (6/10 aligned). Counter-signals that were wrong: HR L30, HR L10, Defense. Projection model targeted 10.2 pts — actual 4 was 6.2 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Clingan's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I63" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="4" t="inlineStr">
         <is>
           <t>Derik Queen</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="4" t="inlineStr">
         <is>
           <t>NOP @ POR</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D64" t="n">
+      <c r="D64" s="4" t="n">
         <v>8.5</v>
       </c>
+      <c r="E64" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Queen scored 12 pts vs 8.5 line (+3.5), OVER hit by 3.5 pts. Queen played 28 min (+9.5 vs L10 avg of 18.2) — 52% more than expected. Shooting was in line with averages: 40.0% FG (4/10, L10 avg 38.4%). Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (6/10 aligned). Counter-signals that were wrong: H2H, Pace, FG Trend. Projection model targeted 17.2 pts — actual 12 was 5.2 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Queen's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I64" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="3" t="inlineStr">
         <is>
           <t>Jrue Holiday</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="3" t="inlineStr">
         <is>
           <t>NOP @ POR</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C65" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D65" t="n">
+      <c r="D65" s="3" t="n">
         <v>17.5</v>
       </c>
+      <c r="E65" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Holiday scored 27 pts vs 17.5 line (+9.5), UNDER missed by 9.5 pts. Holiday played 37 min (+8.8 vs L10 avg of 28.6) — 31% more than expected. Shooting was in line with averages: 45.5% FG (10/22, L10 avg 40.7%). Counter-signals that proved correct: Trend, Defense, Pace. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 11.3 pts — actual 27 was 15.7 pts off (correct direction). Loss classification: BLOWOUT_EFFECT. Note: Game script invalidated the prop. Consider blowout probability when POR is involved.</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>BLOWOUT_EFFECT</t>
+        </is>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="4" t="inlineStr">
         <is>
           <t>Robert Williams III</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="4" t="inlineStr">
         <is>
           <t>NOP @ POR</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C66" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D66" t="n">
+      <c r="D66" s="4" t="n">
         <v>6.5</v>
       </c>
+      <c r="E66" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>WIN — III scored 6 pts vs 6.5 line (-0.5), UNDER hit by 0.5 pts. III played 23 min (+5.6 vs L10 avg of 17.5) — 32% more than expected. Shooting was in line with averages: 60.0% FG (3/5, L10 avg 61.6%). Signals that called it correctly: HR L30, HR L10, Trend, Context, H2H (6/10 aligned). Counter-signals that were wrong: Volume, Defense, Pace. Projection model targeted 5.4 pts — actual 6 was 0.6 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for III in this role.</t>
+        </is>
+      </c>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="3" t="inlineStr">
         <is>
           <t>Trey Murphy III</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>NOP @ POR</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D67" t="n">
+      <c r="D67" s="3" t="n">
         <v>19.5</v>
       </c>
+      <c r="E67" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — III scored 19 pts vs 19.5 line (-0.5), OVER missed by 0.5 pts. Minutes were as expected: 36 played vs L10 avg 35.8. Shooting was in line with averages: 41.2% FG (7/17, L10 avg 44.6%). Counter-signals that proved correct: Trend, H2H, Pace, FG Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 22.2 pts — actual 19 was 3.2 pts off (correct direction). Loss classification: CLOSE_CALL. Note: Within 2 pts — direction was sound. Small execution variance, no model adjustment needed.</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="4" t="inlineStr">
         <is>
           <t>Zion Williamson</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B68" s="4" t="inlineStr">
         <is>
           <t>NOP @ POR</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C68" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D68" t="n">
+      <c r="D68" s="4" t="n">
         <v>20.5</v>
       </c>
+      <c r="E68" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Williamson scored 15 pts vs 20.5 line (-5.5), UNDER hit by 5.5 pts. Minutes were as expected: 29 played vs L10 avg 30.9. Shooting efficiency was cold: 57.1% FG (-14.5% vs L10 avg of 71.6%). 4/7 from the field. Signals that called it correctly: Volume, Context, Pace (3/10 aligned). Counter-signals that were wrong: HR L30, HR L10, Trend. Projection model targeted 18.2 pts — actual 15 was 3.2 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Williamson's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t>Dejounte Murray</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="3" t="inlineStr">
         <is>
           <t>NOP @ POR</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C69" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D69" t="n">
+      <c r="D69" s="3" t="n">
         <v>16.5</v>
       </c>
+      <c r="E69" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Murray scored 9 pts vs 16.5 line (-7.5), OVER missed by 7.5 pts. Minutes were as expected: 28 played vs L10 avg 28.9. Shooting efficiency was cold: 40.0% FG (-7.8% vs L10 avg of 47.8%). 4/10 from the field. Counter-signals that proved correct: HR L10, Trend, H2H, Pace. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 17.7 pts — actual 9 was 8.7 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="3" t="inlineStr">
         <is>
           <t>Toumani Camara</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B70" s="3" t="inlineStr">
         <is>
           <t>NOP @ POR</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D70" t="n">
+      <c r="D70" s="3" t="n">
         <v>13.5</v>
       </c>
+      <c r="E70" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Camara scored 23 pts vs 13.5 line (+9.5), UNDER missed by 9.5 pts. Camara played 39 min (+8.5 vs L10 avg of 30.9) — 28% more than expected. Shooting was in line with averages: 53.3% FG (8/15, L10 avg 53.0%). Counter-signals that proved correct: HR L10, Trend, Defense, Pace. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 12.8 pts — actual 23 was 10.2 pts off (correct direction). Loss classification: BLOWOUT_EFFECT. Note: Game script invalidated the prop. Consider blowout probability when POR is involved.</t>
+        </is>
+      </c>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>BLOWOUT_EFFECT</t>
+        </is>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="3" t="inlineStr">
         <is>
           <t>Matisse Thybulle</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B71" s="3" t="inlineStr">
         <is>
           <t>NOP @ POR</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C71" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D71" t="n">
+      <c r="D71" s="3" t="n">
         <v>6.5</v>
       </c>
+      <c r="E71" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Thybulle scored 13 pts vs 6.5 line (+6.5), UNDER missed by 6.5 pts. Thybulle played 31 min (+12.3 vs L10 avg of 18.6) — 66% more than expected. Shooting was in line with averages: 44.4% FG (4/9, L10 avg 43.1%). Counter-signals that proved correct: Trend, Defense, H2H, Pace. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 5.7 pts — actual 13 was 7.3 pts off (correct direction). Loss classification: MODEL_FAILURE. Note: Model signals were misleading for this matchup — review Thybulle's recent role and usage for pattern shifts.</t>
+        </is>
+      </c>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="4" t="inlineStr">
         <is>
           <t>Keldon Johnson</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B72" s="4" t="inlineStr">
         <is>
           <t>SAS @ LAC</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C72" s="4" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D72" t="n">
+      <c r="D72" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E72" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Johnson scored 13 pts vs 11.5 line (+1.5), OVER hit by 1.5 pts. Johnson played 27 min (+3.8 vs L10 avg of 23.0) — 17% more than expected. Shooting was in line with averages: 54.5% FG (6/11, L10 avg 52.8%). Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (7/10 aligned). Counter-signals that were wrong: Defense, H2H, Pace. Projection model targeted 11.4 pts — actual 13 was 1.6 pts close (wrong direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Johnson in this role.</t>
+        </is>
+      </c>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="3" t="inlineStr">
         <is>
           <t>Devin Vassell</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B73" s="3" t="inlineStr">
         <is>
           <t>SAS @ LAC</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C73" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D73" t="n">
+      <c r="D73" s="3" t="n">
         <v>12.5</v>
       </c>
+      <c r="E73" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Vassell scored 14 pts vs 12.5 line (+1.5), UNDER missed by 1.5 pts. Minutes were as expected: 29 played vs L10 avg 29.6. Shooting was in line with averages: 41.7% FG (5/12, L10 avg 43.4%). Counter-signals that proved correct: Volume, HR L10, Defense, H2H. Signals that were wrong: HR L30, Trend, Context. Projection model targeted 9.4 pts — actual 14 was 4.6 pts off (correct direction). Loss classification: CLOSE_CALL. Note: Within 2 pts — direction was sound. Small execution variance, no model adjustment needed.</t>
+        </is>
+      </c>
+      <c r="I73" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="3" t="inlineStr">
         <is>
           <t>Dylan Harper</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B74" s="3" t="inlineStr">
         <is>
           <t>SAS @ LAC</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C74" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D74" t="n">
+      <c r="D74" s="3" t="n">
         <v>11.5</v>
       </c>
+      <c r="E74" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Harper scored 19 pts vs 11.5 line (+7.5), UNDER missed by 7.5 pts. Minutes were as expected: 25 played vs L10 avg 24.0. Shooting efficiency was hot: 66.7% FG (+10.3% vs L10 avg of 56.4%). 8/12 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Trend. Signals that were wrong: Pace. Projection model targeted 7.5 pts — actual 19 was 11.5 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="4" t="inlineStr">
         <is>
           <t>De'Aaron Fox</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="4" t="inlineStr">
         <is>
           <t>SAS @ LAC</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C75" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D75" t="n">
+      <c r="D75" s="4" t="n">
         <v>15.5</v>
       </c>
+      <c r="E75" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Fox scored 22 pts vs 15.5 line (+6.5), OVER hit by 6.5 pts. Minutes were as expected: 29 played vs L10 avg 27.8. Shooting efficiency was hot: 69.2% FG (+21.7% vs L10 avg of 47.5%). 9/13 from the field. Signals that called it correctly: Volume, Context, Defense, H2H (4/10 aligned). Counter-signals that were wrong: HR L30, HR L10, Trend. Projection model targeted 17.2 pts — actual 22 was 4.8 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Fox's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I75" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="4" t="inlineStr">
         <is>
           <t>Stephon Castle</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B76" s="4" t="inlineStr">
         <is>
           <t>SAS @ LAC</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C76" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D76" t="n">
+      <c r="D76" s="4" t="n">
         <v>15.5</v>
       </c>
+      <c r="E76" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Castle scored 20 pts vs 15.5 line (+4.5), OVER hit by 4.5 pts. Castle played 33 min (+3.3 vs L10 avg of 30.1) — 11% more than expected. Shooting efficiency was hot: 53.3% FG (+5.0% vs L10 avg of 48.3%). 8/15 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (8/10 aligned). Counter-signals that were wrong: Pace, FG Trend. Projection model targeted 15.8 pts — actual 20 was 4.2 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Strong signal alignment (8/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I76" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="3" t="inlineStr">
         <is>
           <t>Harrison Barnes</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B77" s="3" t="inlineStr">
         <is>
           <t>SAS @ LAC</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C77" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D77" t="n">
+      <c r="D77" s="3" t="n">
         <v>7.5</v>
       </c>
+      <c r="E77" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Barnes scored 3 pts vs 7.5 line (-4.5), OVER missed by 4.5 pts. Minutes were as expected: 21 played vs L10 avg 21.5. Shooting efficiency was hot: 50.0% FG (+5.4% vs L10 avg of 44.6%). 1/2 from the field. Counter-signals that proved correct: Trend, Defense, Pace, FG Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 10.4 pts — actual 3 was 7.4 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="3" t="inlineStr">
         <is>
           <t>Bennedict Mathurin</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B78" s="3" t="inlineStr">
         <is>
           <t>SAS @ LAC</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C78" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D78" t="n">
+      <c r="D78" s="3" t="n">
         <v>16.5</v>
       </c>
+      <c r="E78" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Mathurin scored 18 pts vs 16.5 line (+1.5), UNDER missed by 1.5 pts. Mathurin played 27 min (-3.0 vs L10 avg of 29.9) — 10% less than expected. Shooting efficiency was hot: 50.0% FG (+5.0% vs L10 avg of 45.0%). 5/10 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Context. Signals that were wrong: Trend, Defense, H2H. Projection model targeted 14.5 pts — actual 18 was 3.5 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I78" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="A79" s="4" t="inlineStr">
         <is>
           <t>John Collins</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B79" s="4" t="inlineStr">
         <is>
           <t>SAS @ LAC</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C79" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D79" t="n">
+      <c r="D79" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E79" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Collins scored 15 pts vs 11.5 line (+3.5), OVER hit by 3.5 pts. Minutes were as expected: 25 played vs L10 avg 26.1. Shooting efficiency was hot: 75.0% FG (+28.7% vs L10 avg of 46.3%). 6/8 from the field. Signals that called it correctly: Volume, HR L30, Context, H2H, Pace (5/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 11.9 pts — actual 15 was 3.1 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Collins's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I79" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="A80" s="4" t="inlineStr">
         <is>
           <t>Julian Champagnie</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B80" s="4" t="inlineStr">
         <is>
           <t>SAS @ LAC</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C80" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D80" t="n">
+      <c r="D80" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E80" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Champagnie scored 13 pts vs 9.5 line (+3.5), OVER hit by 3.5 pts. Minutes were as expected: 28 played vs L10 avg 27.1. Shooting efficiency was cold: 38.5% FG (-7.4% vs L10 avg of 45.9%). 5/13 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (8/10 aligned). Counter-signals that were wrong: Defense, Pace. Projection model targeted 10.1 pts — actual 13 was 2.9 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Strong signal alignment (8/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I80" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="A81" s="3" t="inlineStr">
         <is>
           <t>Brook Lopez</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B81" s="3" t="inlineStr">
         <is>
           <t>SAS @ LAC</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C81" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D81" t="n">
+      <c r="D81" s="3" t="n">
         <v>10.5</v>
       </c>
+      <c r="E81" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Lopez scored 6 pts vs 10.5 line (-4.5), OVER missed by 4.5 pts. Lopez played 24 min (-4.3 vs L10 avg of 28.3) — 15% less than expected. Shooting efficiency was cold: 25.0% FG (-20.7% vs L10 avg of 45.7%). 3/12 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10. Signals that were wrong: Trend, Context, Defense. Projection model targeted 14.1 pts — actual 6 was 8.1 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Lopez for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I81" s="3" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="A82" s="4" t="inlineStr">
         <is>
           <t>Darius Garland</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B82" s="4" t="inlineStr">
         <is>
           <t>SAS @ LAC</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C82" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D82" t="n">
+      <c r="D82" s="4" t="n">
         <v>19.5</v>
       </c>
+      <c r="E82" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Garland scored 11 pts vs 19.5 line (-8.5), UNDER hit by 8.5 pts. Minutes were as expected: 29 played vs L10 avg 29.9. Shooting efficiency was cold: 29.4% FG (-24.5% vs L10 avg of 53.9%). 5/17 from the field. Signals that called it correctly: Defense, H2H, Min Trend (3/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 16.5 pts — actual 11 was 5.5 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Garland's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I82" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="A83" s="5" t="inlineStr">
         <is>
           <t>Victor Wembanyama</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B83" s="5" t="inlineStr">
         <is>
           <t>SAS @ LAC</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C83" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D83" t="n">
+      <c r="D83" s="5" t="n">
         <v>25.5</v>
       </c>
+      <c r="E83" s="5" t="n"/>
+      <c r="F83" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="n"/>
+      <c r="H83" s="5" t="inlineStr"/>
+      <c r="I83" s="5" t="n"/>
+      <c r="J83" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="A84" s="3" t="inlineStr">
         <is>
           <t>Kawhi Leonard</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B84" s="3" t="inlineStr">
         <is>
           <t>SAS @ LAC</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="C84" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D84" t="n">
+      <c r="D84" s="3" t="n">
         <v>27.5</v>
       </c>
+      <c r="E84" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Leonard scored 24 pts vs 27.5 line (-3.5), OVER missed by 3.5 pts. Minutes were as expected: 32 played vs L10 avg 30.4. Shooting efficiency was hot: 62.5% FG (+8.9% vs L10 avg of 53.6%). 10/16 from the field. Counter-signals that proved correct: Trend, Defense, H2H, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 29.1 pts — actual 24 was 5.1 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I84" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="A85" s="4" t="inlineStr">
         <is>
           <t>Derrick Jones Jr.</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B85" s="4" t="inlineStr">
         <is>
           <t>SAS @ LAC</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C85" s="4" t="inlineStr">
         <is>
           <t>LEAN UNDER</t>
         </is>
       </c>
-      <c r="D85" t="n">
+      <c r="D85" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E85" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G85" s="4" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H85" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Jr. scored 4 pts vs 9.5 line (-5.5), UNDER hit by 5.5 pts. Jr. played 24 min (-4.4 vs L10 avg of 28.2) — 16% less than expected. Shooting efficiency was cold: 33.3% FG (-6.7% vs L10 avg of 40.0%). 2/6 from the field. Signals that called it correctly: HR L10, Trend, Defense, FG Trend, Min Trend (5/10 aligned). Counter-signals that were wrong: Volume, HR L30, Context. Projection model targeted 9.6 pts — actual 4 was 5.6 pts off (wrong direction). Result classification: MODEL_CORRECT. Note: Result confirms Jr.'s consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I85" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="A86" s="3" t="inlineStr">
         <is>
           <t>Kris Dunn</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B86" s="3" t="inlineStr">
         <is>
           <t>SAS @ LAC</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C86" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D86" t="n">
+      <c r="D86" s="3" t="n">
         <v>4.5</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Dunn scored 3 pts vs 4.5 line (-1.5), OVER missed by 1.5 pts. Dunn played 21 min (-5.2 vs L10 avg of 26.1) — 20% less than expected. Shooting efficiency was cold: 25.0% FG (-15.6% vs L10 avg of 40.6%). 1/4 from the field. Counter-signals that proved correct: Trend, Defense, FG Trend, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 5.9 pts — actual 3 was 2.9 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Dunn for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I86" s="3" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
       </c>
     </row>
   </sheetData>
